--- a/Capstone/Fase 1/Grupales/Carta Gantt.xlsx
+++ b/Capstone/Fase 1/Grupales/Carta Gantt.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A74BEA8-43AE-4E82-85D6-D2D8312E01B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B94A89-79E5-46F0-B1C8-6CAA1A02CF22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1058,7 +1058,7 @@
     <xf numFmtId="0" fontId="7" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1264,56 +1264,14 @@
     <xf numFmtId="171" fontId="9" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="8">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="8" applyBorder="1">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="8" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="8" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="3" xfId="9">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="12" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="0" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="9" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="9" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="41" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1325,32 +1283,71 @@
     <xf numFmtId="0" fontId="0" fillId="41" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="41" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="9" fillId="41" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="42" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="42" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="43" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="43" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="41" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="171" fontId="9" fillId="41" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="12" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="41" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="8">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="8" applyBorder="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="8" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="8" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="3" xfId="9">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="54">
     <cellStyle name="20% - Énfasis1" xfId="31" builtinId="30" customBuiltin="1"/>
@@ -2041,171 +2038,171 @@
         <v>1</v>
       </c>
       <c r="B2" s="28"/>
-      <c r="C2" s="73" t="s">
+      <c r="C2" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="74"/>
-      <c r="E2" s="77">
+      <c r="D2" s="99"/>
+      <c r="E2" s="102">
         <f>DATE(2025,8,12)</f>
         <v>45881</v>
       </c>
-      <c r="F2" s="77"/>
+      <c r="F2" s="102"/>
     </row>
     <row r="3" spans="1:121" s="26" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="75" t="s">
+      <c r="C3" s="100" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="76"/>
+      <c r="D3" s="101"/>
       <c r="E3" s="61">
         <v>1</v>
       </c>
       <c r="H3" s="62"/>
-      <c r="I3" s="86">
+      <c r="I3" s="88">
         <f>I4</f>
         <v>45880</v>
       </c>
-      <c r="J3" s="86"/>
-      <c r="K3" s="86"/>
-      <c r="L3" s="86"/>
-      <c r="M3" s="86"/>
-      <c r="N3" s="86">
+      <c r="J3" s="88"/>
+      <c r="K3" s="88"/>
+      <c r="L3" s="88"/>
+      <c r="M3" s="88"/>
+      <c r="N3" s="88">
         <f>N4</f>
         <v>45887</v>
       </c>
-      <c r="O3" s="86"/>
-      <c r="P3" s="86"/>
-      <c r="Q3" s="86"/>
-      <c r="R3" s="86"/>
-      <c r="S3" s="86">
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88">
         <f>S4</f>
         <v>45894</v>
       </c>
-      <c r="T3" s="86"/>
-      <c r="U3" s="86"/>
-      <c r="V3" s="86"/>
-      <c r="W3" s="86"/>
-      <c r="X3" s="86">
+      <c r="T3" s="88"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="W3" s="88"/>
+      <c r="X3" s="88">
         <f>X4</f>
         <v>45901</v>
       </c>
-      <c r="Y3" s="86"/>
-      <c r="Z3" s="86"/>
-      <c r="AA3" s="86"/>
-      <c r="AB3" s="86"/>
-      <c r="AC3" s="86">
+      <c r="Y3" s="88"/>
+      <c r="Z3" s="88"/>
+      <c r="AA3" s="88"/>
+      <c r="AB3" s="88"/>
+      <c r="AC3" s="88">
         <f t="shared" ref="AC3" si="0">AC4</f>
         <v>45908</v>
       </c>
-      <c r="AD3" s="86"/>
-      <c r="AE3" s="86"/>
-      <c r="AF3" s="86"/>
-      <c r="AG3" s="86"/>
-      <c r="AH3" s="86">
+      <c r="AD3" s="88"/>
+      <c r="AE3" s="88"/>
+      <c r="AF3" s="88"/>
+      <c r="AG3" s="88"/>
+      <c r="AH3" s="88">
         <f t="shared" ref="AH3" si="1">AH4</f>
         <v>45915</v>
       </c>
-      <c r="AI3" s="86"/>
-      <c r="AJ3" s="86"/>
-      <c r="AK3" s="86"/>
-      <c r="AL3" s="86"/>
-      <c r="AM3" s="86">
+      <c r="AI3" s="88"/>
+      <c r="AJ3" s="88"/>
+      <c r="AK3" s="88"/>
+      <c r="AL3" s="88"/>
+      <c r="AM3" s="88">
         <f t="shared" ref="AM3" si="2">AM4</f>
         <v>45922</v>
       </c>
-      <c r="AN3" s="86"/>
-      <c r="AO3" s="86"/>
-      <c r="AP3" s="86"/>
-      <c r="AQ3" s="86"/>
-      <c r="AR3" s="86">
+      <c r="AN3" s="88"/>
+      <c r="AO3" s="88"/>
+      <c r="AP3" s="88"/>
+      <c r="AQ3" s="88"/>
+      <c r="AR3" s="88">
         <f>AR4</f>
         <v>45929</v>
       </c>
-      <c r="AS3" s="86"/>
-      <c r="AT3" s="86"/>
-      <c r="AU3" s="86"/>
-      <c r="AV3" s="86"/>
-      <c r="AW3" s="86">
+      <c r="AS3" s="88"/>
+      <c r="AT3" s="88"/>
+      <c r="AU3" s="88"/>
+      <c r="AV3" s="88"/>
+      <c r="AW3" s="88">
         <f t="shared" ref="AW3" si="3">AW4</f>
         <v>45936</v>
       </c>
-      <c r="AX3" s="86"/>
-      <c r="AY3" s="86"/>
-      <c r="AZ3" s="86"/>
-      <c r="BA3" s="86"/>
-      <c r="BB3" s="86">
+      <c r="AX3" s="88"/>
+      <c r="AY3" s="88"/>
+      <c r="AZ3" s="88"/>
+      <c r="BA3" s="88"/>
+      <c r="BB3" s="88">
         <f t="shared" ref="BB3" si="4">BB4</f>
         <v>45943</v>
       </c>
-      <c r="BC3" s="86"/>
-      <c r="BD3" s="86"/>
-      <c r="BE3" s="86"/>
-      <c r="BF3" s="86"/>
-      <c r="BG3" s="86">
+      <c r="BC3" s="88"/>
+      <c r="BD3" s="88"/>
+      <c r="BE3" s="88"/>
+      <c r="BF3" s="88"/>
+      <c r="BG3" s="88">
         <f t="shared" ref="BG3" si="5">BG4</f>
         <v>45950</v>
       </c>
-      <c r="BH3" s="86"/>
-      <c r="BI3" s="86"/>
-      <c r="BJ3" s="86"/>
-      <c r="BK3" s="86"/>
-      <c r="BL3" s="86">
+      <c r="BH3" s="88"/>
+      <c r="BI3" s="88"/>
+      <c r="BJ3" s="88"/>
+      <c r="BK3" s="88"/>
+      <c r="BL3" s="88">
         <f t="shared" ref="BL3" si="6">BL4</f>
         <v>45957</v>
       </c>
-      <c r="BM3" s="86"/>
-      <c r="BN3" s="86"/>
-      <c r="BO3" s="86"/>
-      <c r="BP3" s="86"/>
-      <c r="BQ3" s="86">
+      <c r="BM3" s="88"/>
+      <c r="BN3" s="88"/>
+      <c r="BO3" s="88"/>
+      <c r="BP3" s="88"/>
+      <c r="BQ3" s="88">
         <f t="shared" ref="BQ3" si="7">BQ4</f>
         <v>45964</v>
       </c>
-      <c r="BR3" s="86"/>
-      <c r="BS3" s="86"/>
-      <c r="BT3" s="86"/>
-      <c r="BU3" s="86"/>
-      <c r="BV3" s="86">
+      <c r="BR3" s="88"/>
+      <c r="BS3" s="88"/>
+      <c r="BT3" s="88"/>
+      <c r="BU3" s="88"/>
+      <c r="BV3" s="88">
         <f t="shared" ref="BV3" si="8">BV4</f>
         <v>45971</v>
       </c>
-      <c r="BW3" s="86"/>
-      <c r="BX3" s="86"/>
-      <c r="BY3" s="86"/>
-      <c r="BZ3" s="86"/>
-      <c r="CA3" s="86">
+      <c r="BW3" s="88"/>
+      <c r="BX3" s="88"/>
+      <c r="BY3" s="88"/>
+      <c r="BZ3" s="88"/>
+      <c r="CA3" s="88">
         <f t="shared" ref="CA3" si="9">CA4</f>
         <v>45978</v>
       </c>
-      <c r="CB3" s="86"/>
-      <c r="CC3" s="86"/>
-      <c r="CD3" s="86"/>
-      <c r="CE3" s="86"/>
-      <c r="CF3" s="86">
+      <c r="CB3" s="88"/>
+      <c r="CC3" s="88"/>
+      <c r="CD3" s="88"/>
+      <c r="CE3" s="88"/>
+      <c r="CF3" s="88">
         <f t="shared" ref="CF3" si="10">CF4</f>
         <v>45985</v>
       </c>
-      <c r="CG3" s="86"/>
-      <c r="CH3" s="86"/>
-      <c r="CI3" s="86"/>
-      <c r="CJ3" s="86"/>
-      <c r="CK3" s="86">
+      <c r="CG3" s="88"/>
+      <c r="CH3" s="88"/>
+      <c r="CI3" s="88"/>
+      <c r="CJ3" s="88"/>
+      <c r="CK3" s="88">
         <f t="shared" ref="CK3" si="11">CK4</f>
         <v>45992</v>
       </c>
-      <c r="CL3" s="86"/>
-      <c r="CM3" s="86"/>
-      <c r="CN3" s="86"/>
+      <c r="CL3" s="88"/>
+      <c r="CM3" s="88"/>
+      <c r="CN3" s="88"/>
       <c r="CO3" s="89"/>
-      <c r="CP3" s="100"/>
-      <c r="CQ3" s="87"/>
-      <c r="CR3" s="87"/>
-      <c r="CS3" s="87"/>
-      <c r="CT3" s="87"/>
-      <c r="CU3" s="87"/>
-      <c r="CV3" s="87"/>
+      <c r="CP3" s="84"/>
+      <c r="CQ3" s="74"/>
+      <c r="CR3" s="74"/>
+      <c r="CS3" s="74"/>
+      <c r="CT3" s="74"/>
+      <c r="CU3" s="74"/>
+      <c r="CV3" s="74"/>
     </row>
     <row r="4" spans="1:121" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
@@ -2557,13 +2554,13 @@
         <f t="shared" ref="CO4" si="21">WORKDAY(Inicio_del_proyecto-1, (Semana_para_mostrar-1)*5 + COLUMN(CG1)-1)</f>
         <v>45996</v>
       </c>
-      <c r="CP4" s="101"/>
-      <c r="CQ4" s="88"/>
-      <c r="CR4" s="88"/>
-      <c r="CS4" s="88"/>
-      <c r="CT4" s="88"/>
-      <c r="CU4" s="88"/>
-      <c r="CV4" s="88"/>
+      <c r="CP4" s="85"/>
+      <c r="CQ4" s="75"/>
+      <c r="CR4" s="75"/>
+      <c r="CS4" s="75"/>
+      <c r="CT4" s="75"/>
+      <c r="CU4" s="75"/>
+      <c r="CV4" s="75"/>
     </row>
     <row r="5" spans="1:121" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="24" t="s">
@@ -2924,11 +2921,11 @@
         <f t="shared" si="24"/>
         <v>j</v>
       </c>
-      <c r="CO5" s="98" t="str">
+      <c r="CO5" s="82" t="str">
         <f t="shared" si="24"/>
         <v>v</v>
       </c>
-      <c r="CP5" s="102"/>
+      <c r="CP5" s="86"/>
     </row>
     <row r="6" spans="1:121" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="23" t="s">
@@ -3017,9 +3014,9 @@
       <c r="CE6" s="20"/>
       <c r="CF6" s="20"/>
       <c r="CG6" s="20"/>
-      <c r="CP6" s="102"/>
+      <c r="CP6" s="86"/>
     </row>
-    <row r="7" spans="1:121" s="93" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:121" s="79" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="53"/>
       <c r="B7" s="54" t="s">
         <v>19</v>
@@ -3033,128 +3030,128 @@
         <f t="shared" ref="H7:H28" si="25">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v/>
       </c>
-      <c r="I7" s="94"/>
-      <c r="J7" s="95"/>
-      <c r="K7" s="95"/>
-      <c r="L7" s="95"/>
-      <c r="M7" s="95"/>
-      <c r="N7" s="95"/>
-      <c r="O7" s="95"/>
-      <c r="P7" s="95"/>
-      <c r="Q7" s="95"/>
-      <c r="R7" s="95"/>
-      <c r="S7" s="95"/>
-      <c r="T7" s="95"/>
-      <c r="U7" s="95"/>
-      <c r="V7" s="95"/>
-      <c r="W7" s="95"/>
-      <c r="X7" s="95"/>
-      <c r="Y7" s="95"/>
-      <c r="Z7" s="95"/>
-      <c r="AA7" s="95"/>
-      <c r="AB7" s="95"/>
-      <c r="AC7" s="95"/>
-      <c r="AD7" s="95"/>
-      <c r="AE7" s="95"/>
-      <c r="AF7" s="95"/>
-      <c r="AG7" s="95"/>
-      <c r="AH7" s="95"/>
-      <c r="AI7" s="95"/>
-      <c r="AJ7" s="95"/>
-      <c r="AK7" s="95"/>
-      <c r="AL7" s="95"/>
-      <c r="AM7" s="95"/>
-      <c r="AN7" s="95"/>
-      <c r="AO7" s="95"/>
-      <c r="AP7" s="95"/>
-      <c r="AQ7" s="95"/>
-      <c r="AR7" s="95"/>
-      <c r="AS7" s="95"/>
-      <c r="AT7" s="95"/>
-      <c r="AU7" s="95"/>
-      <c r="AV7" s="95"/>
-      <c r="AW7" s="95"/>
-      <c r="AX7" s="95"/>
-      <c r="AY7" s="95"/>
-      <c r="AZ7" s="95"/>
-      <c r="BA7" s="95"/>
-      <c r="BB7" s="95"/>
-      <c r="BC7" s="95"/>
-      <c r="BD7" s="95"/>
-      <c r="BE7" s="95"/>
-      <c r="BF7" s="95"/>
-      <c r="BG7" s="95"/>
-      <c r="BH7" s="95"/>
-      <c r="BI7" s="95"/>
-      <c r="BJ7" s="95"/>
-      <c r="BK7" s="95"/>
-      <c r="BL7" s="95"/>
-      <c r="BM7" s="95"/>
-      <c r="BN7" s="95"/>
-      <c r="BO7" s="95"/>
-      <c r="BP7" s="95"/>
-      <c r="BQ7" s="95"/>
-      <c r="BR7" s="95"/>
-      <c r="BS7" s="95"/>
-      <c r="BT7" s="95"/>
-      <c r="BU7" s="95"/>
-      <c r="BV7" s="95"/>
-      <c r="BW7" s="95"/>
-      <c r="BX7" s="95"/>
-      <c r="BY7" s="95"/>
-      <c r="BZ7" s="95"/>
-      <c r="CA7" s="95"/>
-      <c r="CB7" s="95"/>
-      <c r="CC7" s="95"/>
-      <c r="CD7" s="95"/>
-      <c r="CE7" s="95"/>
-      <c r="CF7" s="95"/>
-      <c r="CG7" s="95"/>
-      <c r="CH7" s="95"/>
-      <c r="CI7" s="95"/>
-      <c r="CJ7" s="95"/>
-      <c r="CK7" s="95"/>
-      <c r="CL7" s="95"/>
-      <c r="CM7" s="95"/>
-      <c r="CN7" s="95"/>
-      <c r="CO7" s="95"/>
-      <c r="CP7" s="103"/>
-      <c r="CQ7" s="92"/>
-      <c r="CR7" s="92"/>
-      <c r="CS7" s="92"/>
-      <c r="CT7" s="92"/>
-      <c r="CU7" s="92"/>
-      <c r="CV7" s="92"/>
-      <c r="CW7" s="92"/>
-      <c r="CX7" s="92"/>
-      <c r="CY7" s="92"/>
-      <c r="CZ7" s="92"/>
-      <c r="DA7" s="92"/>
-      <c r="DB7" s="92"/>
-      <c r="DC7" s="92"/>
-      <c r="DD7" s="92"/>
-      <c r="DE7" s="92"/>
-      <c r="DF7" s="92"/>
-      <c r="DG7" s="92"/>
-      <c r="DH7" s="92"/>
-      <c r="DI7" s="92"/>
-      <c r="DJ7" s="92"/>
-      <c r="DK7" s="92"/>
-      <c r="DL7" s="92"/>
-      <c r="DM7" s="92"/>
-      <c r="DN7" s="92"/>
-      <c r="DO7" s="92"/>
-      <c r="DP7" s="92"/>
-      <c r="DQ7" s="92"/>
+      <c r="I7" s="90"/>
+      <c r="J7" s="91"/>
+      <c r="K7" s="91"/>
+      <c r="L7" s="91"/>
+      <c r="M7" s="91"/>
+      <c r="N7" s="91"/>
+      <c r="O7" s="91"/>
+      <c r="P7" s="91"/>
+      <c r="Q7" s="91"/>
+      <c r="R7" s="91"/>
+      <c r="S7" s="91"/>
+      <c r="T7" s="91"/>
+      <c r="U7" s="91"/>
+      <c r="V7" s="91"/>
+      <c r="W7" s="91"/>
+      <c r="X7" s="91"/>
+      <c r="Y7" s="91"/>
+      <c r="Z7" s="91"/>
+      <c r="AA7" s="91"/>
+      <c r="AB7" s="91"/>
+      <c r="AC7" s="91"/>
+      <c r="AD7" s="91"/>
+      <c r="AE7" s="91"/>
+      <c r="AF7" s="91"/>
+      <c r="AG7" s="91"/>
+      <c r="AH7" s="91"/>
+      <c r="AI7" s="91"/>
+      <c r="AJ7" s="91"/>
+      <c r="AK7" s="91"/>
+      <c r="AL7" s="91"/>
+      <c r="AM7" s="91"/>
+      <c r="AN7" s="91"/>
+      <c r="AO7" s="91"/>
+      <c r="AP7" s="91"/>
+      <c r="AQ7" s="91"/>
+      <c r="AR7" s="91"/>
+      <c r="AS7" s="91"/>
+      <c r="AT7" s="91"/>
+      <c r="AU7" s="91"/>
+      <c r="AV7" s="91"/>
+      <c r="AW7" s="91"/>
+      <c r="AX7" s="91"/>
+      <c r="AY7" s="91"/>
+      <c r="AZ7" s="91"/>
+      <c r="BA7" s="91"/>
+      <c r="BB7" s="91"/>
+      <c r="BC7" s="91"/>
+      <c r="BD7" s="91"/>
+      <c r="BE7" s="91"/>
+      <c r="BF7" s="91"/>
+      <c r="BG7" s="91"/>
+      <c r="BH7" s="91"/>
+      <c r="BI7" s="91"/>
+      <c r="BJ7" s="91"/>
+      <c r="BK7" s="91"/>
+      <c r="BL7" s="91"/>
+      <c r="BM7" s="91"/>
+      <c r="BN7" s="91"/>
+      <c r="BO7" s="91"/>
+      <c r="BP7" s="91"/>
+      <c r="BQ7" s="91"/>
+      <c r="BR7" s="91"/>
+      <c r="BS7" s="91"/>
+      <c r="BT7" s="91"/>
+      <c r="BU7" s="91"/>
+      <c r="BV7" s="91"/>
+      <c r="BW7" s="91"/>
+      <c r="BX7" s="91"/>
+      <c r="BY7" s="91"/>
+      <c r="BZ7" s="91"/>
+      <c r="CA7" s="91"/>
+      <c r="CB7" s="91"/>
+      <c r="CC7" s="91"/>
+      <c r="CD7" s="91"/>
+      <c r="CE7" s="91"/>
+      <c r="CF7" s="91"/>
+      <c r="CG7" s="91"/>
+      <c r="CH7" s="91"/>
+      <c r="CI7" s="91"/>
+      <c r="CJ7" s="91"/>
+      <c r="CK7" s="91"/>
+      <c r="CL7" s="91"/>
+      <c r="CM7" s="91"/>
+      <c r="CN7" s="91"/>
+      <c r="CO7" s="91"/>
+      <c r="CP7" s="87"/>
+      <c r="CQ7" s="78"/>
+      <c r="CR7" s="78"/>
+      <c r="CS7" s="78"/>
+      <c r="CT7" s="78"/>
+      <c r="CU7" s="78"/>
+      <c r="CV7" s="78"/>
+      <c r="CW7" s="78"/>
+      <c r="CX7" s="78"/>
+      <c r="CY7" s="78"/>
+      <c r="CZ7" s="78"/>
+      <c r="DA7" s="78"/>
+      <c r="DB7" s="78"/>
+      <c r="DC7" s="78"/>
+      <c r="DD7" s="78"/>
+      <c r="DE7" s="78"/>
+      <c r="DF7" s="78"/>
+      <c r="DG7" s="78"/>
+      <c r="DH7" s="78"/>
+      <c r="DI7" s="78"/>
+      <c r="DJ7" s="78"/>
+      <c r="DK7" s="78"/>
+      <c r="DL7" s="78"/>
+      <c r="DM7" s="78"/>
+      <c r="DN7" s="78"/>
+      <c r="DO7" s="78"/>
+      <c r="DP7" s="78"/>
+      <c r="DQ7" s="78"/>
     </row>
     <row r="8" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="85" t="s">
+      <c r="B8" s="92" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="85"/>
+      <c r="C8" s="92"/>
       <c r="D8" s="13">
         <v>1</v>
       </c>
@@ -3189,16 +3186,16 @@
       <c r="Z8" s="20"/>
       <c r="AA8" s="20"/>
       <c r="AB8" s="20"/>
-      <c r="AC8" s="84"/>
-      <c r="AD8" s="84"/>
+      <c r="AC8" s="20"/>
+      <c r="AD8" s="20"/>
       <c r="AE8" s="20"/>
       <c r="AF8" s="20"/>
       <c r="AG8" s="20"/>
       <c r="AH8" s="20"/>
       <c r="AI8" s="20"/>
       <c r="AJ8" s="20"/>
-      <c r="AK8" s="96"/>
-      <c r="AL8" s="96"/>
+      <c r="AK8" s="80"/>
+      <c r="AL8" s="80"/>
       <c r="AM8" s="20"/>
       <c r="AN8" s="20"/>
       <c r="AO8" s="20"/>
@@ -3228,7 +3225,7 @@
       <c r="BM8" s="20"/>
       <c r="BN8" s="20"/>
       <c r="BO8" s="20"/>
-      <c r="BP8" s="96"/>
+      <c r="BP8" s="80"/>
       <c r="BQ8" s="43"/>
       <c r="BR8" s="43"/>
       <c r="BS8" s="43"/>
@@ -3245,16 +3242,16 @@
       <c r="CD8" s="43"/>
       <c r="CE8" s="43"/>
       <c r="CF8" s="43"/>
-      <c r="CG8" s="90"/>
+      <c r="CG8" s="76"/>
       <c r="CH8" s="43"/>
-      <c r="CI8" s="90"/>
-      <c r="CJ8" s="90"/>
-      <c r="CK8" s="90"/>
-      <c r="CL8" s="90"/>
-      <c r="CM8" s="90"/>
-      <c r="CN8" s="90"/>
-      <c r="CO8" s="90"/>
-      <c r="CP8" s="102"/>
+      <c r="CI8" s="76"/>
+      <c r="CJ8" s="76"/>
+      <c r="CK8" s="76"/>
+      <c r="CL8" s="76"/>
+      <c r="CM8" s="76"/>
+      <c r="CN8" s="76"/>
+      <c r="CO8" s="76"/>
+      <c r="CP8" s="86"/>
       <c r="CQ8"/>
       <c r="CR8"/>
       <c r="CS8"/>
@@ -3285,10 +3282,10 @@
     </row>
     <row r="9" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="24"/>
-      <c r="B9" s="85" t="s">
+      <c r="B9" s="92" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="85"/>
+      <c r="C9" s="92"/>
       <c r="D9" s="13">
         <v>1</v>
       </c>
@@ -3320,16 +3317,16 @@
       <c r="Z9" s="20"/>
       <c r="AA9" s="20"/>
       <c r="AB9" s="20"/>
-      <c r="AC9" s="84"/>
-      <c r="AD9" s="84"/>
+      <c r="AC9" s="20"/>
+      <c r="AD9" s="20"/>
       <c r="AE9" s="20"/>
       <c r="AF9" s="20"/>
       <c r="AG9" s="20"/>
       <c r="AH9" s="20"/>
       <c r="AI9" s="20"/>
       <c r="AJ9" s="20"/>
-      <c r="AK9" s="96"/>
-      <c r="AL9" s="96"/>
+      <c r="AK9" s="80"/>
+      <c r="AL9" s="80"/>
       <c r="AM9" s="20"/>
       <c r="AN9" s="20"/>
       <c r="AO9" s="20"/>
@@ -3359,7 +3356,7 @@
       <c r="BM9" s="20"/>
       <c r="BN9" s="20"/>
       <c r="BO9" s="20"/>
-      <c r="BP9" s="96"/>
+      <c r="BP9" s="80"/>
       <c r="BQ9" s="43"/>
       <c r="BR9" s="43"/>
       <c r="BS9" s="43"/>
@@ -3376,16 +3373,16 @@
       <c r="CD9" s="43"/>
       <c r="CE9" s="43"/>
       <c r="CF9" s="43"/>
-      <c r="CG9" s="90"/>
+      <c r="CG9" s="76"/>
       <c r="CH9" s="43"/>
-      <c r="CI9" s="90"/>
-      <c r="CJ9" s="90"/>
-      <c r="CK9" s="90"/>
-      <c r="CL9" s="90"/>
-      <c r="CM9" s="90"/>
-      <c r="CN9" s="90"/>
-      <c r="CO9" s="90"/>
-      <c r="CP9" s="102"/>
+      <c r="CI9" s="76"/>
+      <c r="CJ9" s="76"/>
+      <c r="CK9" s="76"/>
+      <c r="CL9" s="76"/>
+      <c r="CM9" s="76"/>
+      <c r="CN9" s="76"/>
+      <c r="CO9" s="76"/>
+      <c r="CP9" s="86"/>
       <c r="CQ9"/>
       <c r="CR9"/>
       <c r="CS9"/>
@@ -3416,10 +3413,10 @@
     </row>
     <row r="10" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="23"/>
-      <c r="B10" s="85" t="s">
+      <c r="B10" s="92" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="85"/>
+      <c r="C10" s="92"/>
       <c r="D10" s="13">
         <v>1</v>
       </c>
@@ -3455,16 +3452,16 @@
       <c r="Z10" s="20"/>
       <c r="AA10" s="20"/>
       <c r="AB10" s="20"/>
-      <c r="AC10" s="84"/>
-      <c r="AD10" s="84"/>
+      <c r="AC10" s="20"/>
+      <c r="AD10" s="20"/>
       <c r="AE10" s="20"/>
       <c r="AF10" s="20"/>
       <c r="AG10" s="20"/>
       <c r="AH10" s="20"/>
       <c r="AI10" s="20"/>
       <c r="AJ10" s="20"/>
-      <c r="AK10" s="96"/>
-      <c r="AL10" s="96"/>
+      <c r="AK10" s="80"/>
+      <c r="AL10" s="80"/>
       <c r="AM10" s="20"/>
       <c r="AN10" s="20"/>
       <c r="AO10" s="20"/>
@@ -3494,7 +3491,7 @@
       <c r="BM10" s="20"/>
       <c r="BN10" s="20"/>
       <c r="BO10" s="20"/>
-      <c r="BP10" s="96"/>
+      <c r="BP10" s="80"/>
       <c r="BQ10" s="43"/>
       <c r="BR10" s="43"/>
       <c r="BS10" s="43"/>
@@ -3511,15 +3508,15 @@
       <c r="CD10" s="43"/>
       <c r="CE10" s="43"/>
       <c r="CF10" s="43"/>
-      <c r="CG10" s="90"/>
+      <c r="CG10" s="76"/>
       <c r="CH10" s="43"/>
-      <c r="CJ10" s="90"/>
-      <c r="CK10" s="90"/>
-      <c r="CL10" s="90"/>
-      <c r="CM10" s="90"/>
-      <c r="CN10" s="90"/>
-      <c r="CO10" s="90"/>
-      <c r="CP10" s="102"/>
+      <c r="CJ10" s="76"/>
+      <c r="CK10" s="76"/>
+      <c r="CL10" s="76"/>
+      <c r="CM10" s="76"/>
+      <c r="CN10" s="76"/>
+      <c r="CO10" s="76"/>
+      <c r="CP10" s="86"/>
       <c r="CQ10"/>
       <c r="CR10"/>
       <c r="CS10"/>
@@ -3550,10 +3547,10 @@
     </row>
     <row r="11" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="23"/>
-      <c r="B11" s="85" t="s">
+      <c r="B11" s="92" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="85"/>
+      <c r="C11" s="92"/>
       <c r="D11" s="13">
         <v>1</v>
       </c>
@@ -3585,16 +3582,16 @@
       <c r="Z11" s="20"/>
       <c r="AA11" s="20"/>
       <c r="AB11" s="20"/>
-      <c r="AC11" s="84"/>
-      <c r="AD11" s="84"/>
+      <c r="AC11" s="20"/>
+      <c r="AD11" s="20"/>
       <c r="AE11" s="20"/>
       <c r="AF11" s="20"/>
       <c r="AG11" s="20"/>
       <c r="AH11" s="20"/>
       <c r="AI11" s="20"/>
       <c r="AJ11" s="20"/>
-      <c r="AK11" s="96"/>
-      <c r="AL11" s="96"/>
+      <c r="AK11" s="80"/>
+      <c r="AL11" s="80"/>
       <c r="AM11" s="20"/>
       <c r="AN11" s="20"/>
       <c r="AO11" s="20"/>
@@ -3624,7 +3621,7 @@
       <c r="BM11" s="20"/>
       <c r="BN11" s="20"/>
       <c r="BO11" s="20"/>
-      <c r="BP11" s="96"/>
+      <c r="BP11" s="80"/>
       <c r="BQ11" s="43"/>
       <c r="BR11" s="43"/>
       <c r="BS11" s="43"/>
@@ -3641,16 +3638,16 @@
       <c r="CD11" s="43"/>
       <c r="CE11" s="43"/>
       <c r="CF11" s="43"/>
-      <c r="CG11" s="90"/>
+      <c r="CG11" s="76"/>
       <c r="CH11" s="43"/>
-      <c r="CI11" s="90"/>
-      <c r="CJ11" s="90"/>
-      <c r="CK11" s="90"/>
-      <c r="CL11" s="90"/>
-      <c r="CM11" s="90"/>
-      <c r="CN11" s="90"/>
-      <c r="CO11" s="90"/>
-      <c r="CP11" s="102"/>
+      <c r="CI11" s="76"/>
+      <c r="CJ11" s="76"/>
+      <c r="CK11" s="76"/>
+      <c r="CL11" s="76"/>
+      <c r="CM11" s="76"/>
+      <c r="CN11" s="76"/>
+      <c r="CO11" s="76"/>
+      <c r="CP11" s="86"/>
       <c r="CQ11"/>
       <c r="CR11"/>
       <c r="CS11"/>
@@ -3681,10 +3678,10 @@
     </row>
     <row r="12" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="23"/>
-      <c r="B12" s="85" t="s">
+      <c r="B12" s="92" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="85"/>
+      <c r="C12" s="92"/>
       <c r="D12" s="13">
         <v>1</v>
       </c>
@@ -3717,16 +3714,16 @@
       <c r="Z12" s="20"/>
       <c r="AA12" s="20"/>
       <c r="AB12" s="20"/>
-      <c r="AC12" s="84"/>
-      <c r="AD12" s="84"/>
+      <c r="AC12" s="20"/>
+      <c r="AD12" s="20"/>
       <c r="AE12" s="20"/>
       <c r="AF12" s="20"/>
       <c r="AG12" s="20"/>
       <c r="AH12" s="20"/>
       <c r="AI12" s="20"/>
       <c r="AJ12" s="20"/>
-      <c r="AK12" s="96"/>
-      <c r="AL12" s="96"/>
+      <c r="AK12" s="80"/>
+      <c r="AL12" s="80"/>
       <c r="AM12" s="20"/>
       <c r="AN12" s="20"/>
       <c r="AO12" s="20"/>
@@ -3756,7 +3753,7 @@
       <c r="BM12" s="20"/>
       <c r="BN12" s="20"/>
       <c r="BO12" s="20"/>
-      <c r="BP12" s="96"/>
+      <c r="BP12" s="80"/>
       <c r="BQ12" s="43"/>
       <c r="BR12" s="43"/>
       <c r="BS12" s="43"/>
@@ -3773,16 +3770,16 @@
       <c r="CD12" s="43"/>
       <c r="CE12" s="43"/>
       <c r="CF12" s="43"/>
-      <c r="CG12" s="90"/>
+      <c r="CG12" s="76"/>
       <c r="CH12" s="43"/>
-      <c r="CI12" s="90"/>
-      <c r="CJ12" s="90"/>
-      <c r="CK12" s="90"/>
-      <c r="CL12" s="90"/>
-      <c r="CM12" s="90"/>
-      <c r="CN12" s="90"/>
-      <c r="CO12" s="90"/>
-      <c r="CP12" s="102"/>
+      <c r="CI12" s="76"/>
+      <c r="CJ12" s="76"/>
+      <c r="CK12" s="76"/>
+      <c r="CL12" s="76"/>
+      <c r="CM12" s="76"/>
+      <c r="CN12" s="76"/>
+      <c r="CO12" s="76"/>
+      <c r="CP12" s="86"/>
       <c r="CQ12"/>
       <c r="CR12"/>
       <c r="CS12"/>
@@ -3813,10 +3810,10 @@
     </row>
     <row r="13" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="23"/>
-      <c r="B13" s="85" t="s">
+      <c r="B13" s="92" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="85"/>
+      <c r="C13" s="92"/>
       <c r="D13" s="13">
         <v>0.8</v>
       </c>
@@ -3856,8 +3853,8 @@
       <c r="AH13" s="20"/>
       <c r="AI13" s="20"/>
       <c r="AJ13" s="20"/>
-      <c r="AK13" s="96"/>
-      <c r="AL13" s="96"/>
+      <c r="AK13" s="80"/>
+      <c r="AL13" s="80"/>
       <c r="AM13" s="20"/>
       <c r="AN13" s="20"/>
       <c r="AO13" s="20"/>
@@ -3887,7 +3884,7 @@
       <c r="BM13" s="20"/>
       <c r="BN13" s="20"/>
       <c r="BO13" s="20"/>
-      <c r="BP13" s="96"/>
+      <c r="BP13" s="80"/>
       <c r="BQ13" s="20"/>
       <c r="BR13" s="20"/>
       <c r="BS13" s="20"/>
@@ -3904,7 +3901,7 @@
       <c r="CD13" s="20"/>
       <c r="CE13" s="20"/>
       <c r="CF13" s="20"/>
-      <c r="CG13" s="83"/>
+      <c r="CG13" s="73"/>
       <c r="CH13" s="20"/>
       <c r="CI13" s="20"/>
       <c r="CJ13" s="20"/>
@@ -3912,8 +3909,8 @@
       <c r="CL13" s="20"/>
       <c r="CM13" s="20"/>
       <c r="CN13" s="20"/>
-      <c r="CO13" s="83"/>
-      <c r="CP13" s="102"/>
+      <c r="CO13" s="73"/>
+      <c r="CP13" s="86"/>
       <c r="CQ13"/>
       <c r="CR13"/>
       <c r="CS13"/>
@@ -3958,92 +3955,92 @@
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="I14" s="78"/>
-      <c r="J14" s="79"/>
-      <c r="K14" s="79"/>
-      <c r="L14" s="79"/>
-      <c r="M14" s="79"/>
-      <c r="N14" s="79"/>
-      <c r="O14" s="79"/>
-      <c r="P14" s="79"/>
-      <c r="Q14" s="79"/>
-      <c r="R14" s="79"/>
-      <c r="S14" s="79"/>
-      <c r="T14" s="79"/>
-      <c r="U14" s="79"/>
-      <c r="V14" s="79"/>
-      <c r="W14" s="79"/>
-      <c r="X14" s="79"/>
-      <c r="Y14" s="79"/>
-      <c r="Z14" s="79"/>
-      <c r="AA14" s="79"/>
-      <c r="AB14" s="79"/>
-      <c r="AC14" s="79"/>
-      <c r="AD14" s="79"/>
-      <c r="AE14" s="79"/>
-      <c r="AF14" s="79"/>
-      <c r="AG14" s="79"/>
-      <c r="AH14" s="79"/>
-      <c r="AI14" s="79"/>
-      <c r="AJ14" s="79"/>
-      <c r="AK14" s="79"/>
-      <c r="AL14" s="79"/>
-      <c r="AM14" s="79"/>
-      <c r="AN14" s="79"/>
-      <c r="AO14" s="79"/>
-      <c r="AP14" s="79"/>
-      <c r="AQ14" s="79"/>
-      <c r="AR14" s="79"/>
-      <c r="AS14" s="79"/>
-      <c r="AT14" s="79"/>
-      <c r="AU14" s="79"/>
-      <c r="AV14" s="79"/>
-      <c r="AW14" s="79"/>
-      <c r="AX14" s="79"/>
-      <c r="AY14" s="79"/>
-      <c r="AZ14" s="79"/>
-      <c r="BA14" s="79"/>
-      <c r="BB14" s="79"/>
-      <c r="BC14" s="79"/>
-      <c r="BD14" s="79"/>
-      <c r="BE14" s="79"/>
-      <c r="BF14" s="79"/>
-      <c r="BG14" s="79"/>
-      <c r="BH14" s="79"/>
-      <c r="BI14" s="79"/>
-      <c r="BJ14" s="79"/>
-      <c r="BK14" s="79"/>
-      <c r="BL14" s="79"/>
-      <c r="BM14" s="79"/>
-      <c r="BN14" s="79"/>
-      <c r="BO14" s="79"/>
-      <c r="BP14" s="79"/>
-      <c r="BQ14" s="79"/>
-      <c r="BR14" s="79"/>
-      <c r="BS14" s="79"/>
-      <c r="BT14" s="79"/>
-      <c r="BU14" s="79"/>
-      <c r="BV14" s="79"/>
-      <c r="BW14" s="79"/>
-      <c r="BX14" s="79"/>
-      <c r="BY14" s="79"/>
-      <c r="BZ14" s="79"/>
-      <c r="CA14" s="79"/>
-      <c r="CB14" s="79"/>
-      <c r="CC14" s="79"/>
-      <c r="CD14" s="79"/>
-      <c r="CE14" s="79"/>
-      <c r="CF14" s="79"/>
-      <c r="CG14" s="79"/>
-      <c r="CH14" s="79"/>
-      <c r="CI14" s="79"/>
-      <c r="CJ14" s="79"/>
-      <c r="CK14" s="79"/>
-      <c r="CL14" s="79"/>
-      <c r="CM14" s="79"/>
-      <c r="CN14" s="79"/>
-      <c r="CO14" s="80"/>
-      <c r="CP14" s="102"/>
+      <c r="I14" s="95"/>
+      <c r="J14" s="96"/>
+      <c r="K14" s="96"/>
+      <c r="L14" s="96"/>
+      <c r="M14" s="96"/>
+      <c r="N14" s="96"/>
+      <c r="O14" s="96"/>
+      <c r="P14" s="96"/>
+      <c r="Q14" s="96"/>
+      <c r="R14" s="96"/>
+      <c r="S14" s="96"/>
+      <c r="T14" s="96"/>
+      <c r="U14" s="96"/>
+      <c r="V14" s="96"/>
+      <c r="W14" s="96"/>
+      <c r="X14" s="96"/>
+      <c r="Y14" s="96"/>
+      <c r="Z14" s="96"/>
+      <c r="AA14" s="96"/>
+      <c r="AB14" s="96"/>
+      <c r="AC14" s="96"/>
+      <c r="AD14" s="96"/>
+      <c r="AE14" s="96"/>
+      <c r="AF14" s="96"/>
+      <c r="AG14" s="96"/>
+      <c r="AH14" s="96"/>
+      <c r="AI14" s="96"/>
+      <c r="AJ14" s="96"/>
+      <c r="AK14" s="96"/>
+      <c r="AL14" s="96"/>
+      <c r="AM14" s="96"/>
+      <c r="AN14" s="96"/>
+      <c r="AO14" s="96"/>
+      <c r="AP14" s="96"/>
+      <c r="AQ14" s="96"/>
+      <c r="AR14" s="96"/>
+      <c r="AS14" s="96"/>
+      <c r="AT14" s="96"/>
+      <c r="AU14" s="96"/>
+      <c r="AV14" s="96"/>
+      <c r="AW14" s="96"/>
+      <c r="AX14" s="96"/>
+      <c r="AY14" s="96"/>
+      <c r="AZ14" s="96"/>
+      <c r="BA14" s="96"/>
+      <c r="BB14" s="96"/>
+      <c r="BC14" s="96"/>
+      <c r="BD14" s="96"/>
+      <c r="BE14" s="96"/>
+      <c r="BF14" s="96"/>
+      <c r="BG14" s="96"/>
+      <c r="BH14" s="96"/>
+      <c r="BI14" s="96"/>
+      <c r="BJ14" s="96"/>
+      <c r="BK14" s="96"/>
+      <c r="BL14" s="96"/>
+      <c r="BM14" s="96"/>
+      <c r="BN14" s="96"/>
+      <c r="BO14" s="96"/>
+      <c r="BP14" s="96"/>
+      <c r="BQ14" s="96"/>
+      <c r="BR14" s="96"/>
+      <c r="BS14" s="96"/>
+      <c r="BT14" s="96"/>
+      <c r="BU14" s="96"/>
+      <c r="BV14" s="96"/>
+      <c r="BW14" s="96"/>
+      <c r="BX14" s="96"/>
+      <c r="BY14" s="96"/>
+      <c r="BZ14" s="96"/>
+      <c r="CA14" s="96"/>
+      <c r="CB14" s="96"/>
+      <c r="CC14" s="96"/>
+      <c r="CD14" s="96"/>
+      <c r="CE14" s="96"/>
+      <c r="CF14" s="96"/>
+      <c r="CG14" s="96"/>
+      <c r="CH14" s="96"/>
+      <c r="CI14" s="96"/>
+      <c r="CJ14" s="96"/>
+      <c r="CK14" s="96"/>
+      <c r="CL14" s="96"/>
+      <c r="CM14" s="96"/>
+      <c r="CN14" s="96"/>
+      <c r="CO14" s="97"/>
+      <c r="CP14" s="86"/>
       <c r="CQ14"/>
       <c r="CR14"/>
       <c r="CS14"/>
@@ -4109,16 +4106,16 @@
       <c r="Z15" s="20"/>
       <c r="AA15" s="20"/>
       <c r="AB15" s="20"/>
-      <c r="AC15" s="84"/>
-      <c r="AD15" s="84"/>
+      <c r="AC15" s="20"/>
+      <c r="AD15" s="20"/>
       <c r="AE15" s="20"/>
       <c r="AF15" s="20"/>
       <c r="AG15" s="20"/>
       <c r="AH15" s="20"/>
       <c r="AI15" s="20"/>
       <c r="AJ15" s="20"/>
-      <c r="AK15" s="96"/>
-      <c r="AL15" s="96"/>
+      <c r="AK15" s="80"/>
+      <c r="AL15" s="80"/>
       <c r="AM15" s="20"/>
       <c r="AN15" s="20"/>
       <c r="AO15" s="20"/>
@@ -4148,7 +4145,7 @@
       <c r="BM15" s="20"/>
       <c r="BN15" s="20"/>
       <c r="BO15" s="20"/>
-      <c r="BP15" s="96"/>
+      <c r="BP15" s="80"/>
       <c r="BQ15" s="43"/>
       <c r="BR15" s="43"/>
       <c r="BS15" s="43"/>
@@ -4165,7 +4162,7 @@
       <c r="CD15" s="43"/>
       <c r="CE15" s="43"/>
       <c r="CF15" s="43"/>
-      <c r="CG15" s="90"/>
+      <c r="CG15" s="76"/>
       <c r="CH15" s="20"/>
       <c r="CI15" s="20"/>
       <c r="CJ15" s="20"/>
@@ -4173,8 +4170,8 @@
       <c r="CL15" s="20"/>
       <c r="CM15" s="20"/>
       <c r="CN15" s="20"/>
-      <c r="CO15" s="83"/>
-      <c r="CP15" s="102"/>
+      <c r="CO15" s="73"/>
+      <c r="CP15" s="86"/>
       <c r="CQ15"/>
       <c r="CR15"/>
       <c r="CS15"/>
@@ -4240,16 +4237,16 @@
       <c r="Z16" s="20"/>
       <c r="AA16" s="20"/>
       <c r="AB16" s="20"/>
-      <c r="AC16" s="84"/>
-      <c r="AD16" s="84"/>
+      <c r="AC16" s="20"/>
+      <c r="AD16" s="20"/>
       <c r="AE16" s="20"/>
       <c r="AF16" s="20"/>
       <c r="AG16" s="20"/>
       <c r="AH16" s="20"/>
       <c r="AI16" s="20"/>
       <c r="AJ16" s="20"/>
-      <c r="AK16" s="96"/>
-      <c r="AL16" s="96"/>
+      <c r="AK16" s="80"/>
+      <c r="AL16" s="80"/>
       <c r="AM16" s="20"/>
       <c r="AN16" s="20"/>
       <c r="AO16" s="20"/>
@@ -4279,7 +4276,7 @@
       <c r="BM16" s="20"/>
       <c r="BN16" s="20"/>
       <c r="BO16" s="20"/>
-      <c r="BP16" s="96"/>
+      <c r="BP16" s="80"/>
       <c r="BQ16" s="43"/>
       <c r="BR16" s="43"/>
       <c r="BS16" s="43"/>
@@ -4296,7 +4293,7 @@
       <c r="CD16" s="43"/>
       <c r="CE16" s="43"/>
       <c r="CF16" s="43"/>
-      <c r="CG16" s="90"/>
+      <c r="CG16" s="76"/>
       <c r="CH16" s="20"/>
       <c r="CI16" s="20"/>
       <c r="CJ16" s="20"/>
@@ -4304,8 +4301,8 @@
       <c r="CL16" s="20"/>
       <c r="CM16" s="20"/>
       <c r="CN16" s="20"/>
-      <c r="CO16" s="83"/>
-      <c r="CP16" s="102"/>
+      <c r="CO16" s="73"/>
+      <c r="CP16" s="86"/>
       <c r="CQ16"/>
       <c r="CR16"/>
       <c r="CS16"/>
@@ -4341,7 +4338,7 @@
       </c>
       <c r="C17" s="30"/>
       <c r="D17" s="16">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E17" s="42">
         <v>45926</v>
@@ -4371,16 +4368,16 @@
       <c r="Z17" s="20"/>
       <c r="AA17" s="20"/>
       <c r="AB17" s="20"/>
-      <c r="AC17" s="84"/>
-      <c r="AD17" s="84"/>
+      <c r="AC17" s="20"/>
+      <c r="AD17" s="20"/>
       <c r="AE17" s="20"/>
       <c r="AF17" s="20"/>
       <c r="AG17" s="20"/>
       <c r="AH17" s="20"/>
       <c r="AI17" s="20"/>
       <c r="AJ17" s="20"/>
-      <c r="AK17" s="96"/>
-      <c r="AL17" s="96"/>
+      <c r="AK17" s="80"/>
+      <c r="AL17" s="80"/>
       <c r="AM17" s="20"/>
       <c r="AN17" s="20"/>
       <c r="AO17" s="20"/>
@@ -4410,7 +4407,7 @@
       <c r="BM17" s="20"/>
       <c r="BN17" s="20"/>
       <c r="BO17" s="20"/>
-      <c r="BP17" s="96"/>
+      <c r="BP17" s="80"/>
       <c r="BQ17" s="43"/>
       <c r="BR17" s="43"/>
       <c r="BS17" s="43"/>
@@ -4427,7 +4424,7 @@
       <c r="CD17" s="43"/>
       <c r="CE17" s="43"/>
       <c r="CF17" s="43"/>
-      <c r="CG17" s="90"/>
+      <c r="CG17" s="76"/>
       <c r="CH17" s="20"/>
       <c r="CI17" s="20"/>
       <c r="CJ17" s="20"/>
@@ -4435,8 +4432,8 @@
       <c r="CL17" s="20"/>
       <c r="CM17" s="20"/>
       <c r="CN17" s="20"/>
-      <c r="CO17" s="83"/>
-      <c r="CP17" s="102"/>
+      <c r="CO17" s="73"/>
+      <c r="CP17" s="86"/>
       <c r="CQ17"/>
       <c r="CR17"/>
       <c r="CS17"/>
@@ -4502,16 +4499,16 @@
       <c r="Z18" s="20"/>
       <c r="AA18" s="20"/>
       <c r="AB18" s="20"/>
-      <c r="AC18" s="84"/>
-      <c r="AD18" s="84"/>
+      <c r="AC18" s="20"/>
+      <c r="AD18" s="20"/>
       <c r="AE18" s="20"/>
       <c r="AF18" s="20"/>
       <c r="AG18" s="20"/>
       <c r="AH18" s="20"/>
       <c r="AI18" s="20"/>
       <c r="AJ18" s="20"/>
-      <c r="AK18" s="96"/>
-      <c r="AL18" s="96"/>
+      <c r="AK18" s="80"/>
+      <c r="AL18" s="80"/>
       <c r="AM18" s="20"/>
       <c r="AN18" s="20"/>
       <c r="AO18" s="20"/>
@@ -4541,7 +4538,7 @@
       <c r="BM18" s="20"/>
       <c r="BN18" s="20"/>
       <c r="BO18" s="20"/>
-      <c r="BP18" s="96"/>
+      <c r="BP18" s="80"/>
       <c r="BQ18" s="43"/>
       <c r="BR18" s="43"/>
       <c r="BS18" s="43"/>
@@ -4558,7 +4555,7 @@
       <c r="CD18" s="43"/>
       <c r="CE18" s="43"/>
       <c r="CF18" s="43"/>
-      <c r="CG18" s="90"/>
+      <c r="CG18" s="76"/>
       <c r="CH18" s="20"/>
       <c r="CI18" s="20"/>
       <c r="CJ18" s="20"/>
@@ -4566,8 +4563,8 @@
       <c r="CL18" s="20"/>
       <c r="CM18" s="20"/>
       <c r="CN18" s="20"/>
-      <c r="CO18" s="83"/>
-      <c r="CP18" s="102"/>
+      <c r="CO18" s="73"/>
+      <c r="CP18" s="86"/>
       <c r="CQ18"/>
       <c r="CR18"/>
       <c r="CS18"/>
@@ -4633,16 +4630,16 @@
       <c r="Z19" s="20"/>
       <c r="AA19" s="20"/>
       <c r="AB19" s="20"/>
-      <c r="AC19" s="84"/>
-      <c r="AD19" s="84"/>
+      <c r="AC19" s="20"/>
+      <c r="AD19" s="20"/>
       <c r="AE19" s="20"/>
       <c r="AF19" s="20"/>
       <c r="AG19" s="20"/>
       <c r="AH19" s="20"/>
       <c r="AI19" s="20"/>
       <c r="AJ19" s="20"/>
-      <c r="AK19" s="96"/>
-      <c r="AL19" s="96"/>
+      <c r="AK19" s="80"/>
+      <c r="AL19" s="80"/>
       <c r="AM19" s="20"/>
       <c r="AN19" s="20"/>
       <c r="AO19" s="20"/>
@@ -4672,7 +4669,7 @@
       <c r="BM19" s="20"/>
       <c r="BN19" s="20"/>
       <c r="BO19" s="20"/>
-      <c r="BP19" s="96"/>
+      <c r="BP19" s="80"/>
       <c r="BQ19" s="43"/>
       <c r="BR19" s="20"/>
       <c r="BS19" s="43"/>
@@ -4689,7 +4686,7 @@
       <c r="CD19" s="43"/>
       <c r="CE19" s="43"/>
       <c r="CF19" s="43"/>
-      <c r="CG19" s="90"/>
+      <c r="CG19" s="76"/>
       <c r="CH19" s="20"/>
       <c r="CI19" s="20"/>
       <c r="CJ19" s="20"/>
@@ -4697,8 +4694,8 @@
       <c r="CL19" s="20"/>
       <c r="CM19" s="20"/>
       <c r="CN19" s="20"/>
-      <c r="CO19" s="83"/>
-      <c r="CP19" s="102"/>
+      <c r="CO19" s="73"/>
+      <c r="CP19" s="86"/>
       <c r="CQ19"/>
       <c r="CR19"/>
       <c r="CS19"/>
@@ -4764,16 +4761,16 @@
       <c r="Z20" s="20"/>
       <c r="AA20" s="20"/>
       <c r="AB20" s="20"/>
-      <c r="AC20" s="84"/>
-      <c r="AD20" s="84"/>
+      <c r="AC20" s="20"/>
+      <c r="AD20" s="20"/>
       <c r="AE20" s="20"/>
       <c r="AF20" s="20"/>
       <c r="AG20" s="20"/>
       <c r="AH20" s="20"/>
       <c r="AI20" s="20"/>
       <c r="AJ20" s="20"/>
-      <c r="AK20" s="96"/>
-      <c r="AL20" s="96"/>
+      <c r="AK20" s="80"/>
+      <c r="AL20" s="80"/>
       <c r="AM20" s="20"/>
       <c r="AN20" s="20"/>
       <c r="AO20" s="20"/>
@@ -4803,7 +4800,7 @@
       <c r="BM20" s="20"/>
       <c r="BN20" s="20"/>
       <c r="BO20" s="20"/>
-      <c r="BP20" s="96"/>
+      <c r="BP20" s="80"/>
       <c r="BQ20" s="43"/>
       <c r="BR20" s="43"/>
       <c r="BS20" s="43"/>
@@ -4820,7 +4817,7 @@
       <c r="CD20" s="43"/>
       <c r="CE20" s="43"/>
       <c r="CF20" s="43"/>
-      <c r="CG20" s="90"/>
+      <c r="CG20" s="76"/>
       <c r="CH20" s="20"/>
       <c r="CI20" s="20"/>
       <c r="CJ20" s="20"/>
@@ -4828,8 +4825,8 @@
       <c r="CL20" s="20"/>
       <c r="CM20" s="20"/>
       <c r="CN20" s="20"/>
-      <c r="CO20" s="83"/>
-      <c r="CP20" s="102"/>
+      <c r="CO20" s="73"/>
+      <c r="CP20" s="86"/>
       <c r="CQ20"/>
       <c r="CR20"/>
       <c r="CS20"/>
@@ -4895,16 +4892,16 @@
       <c r="Z21" s="20"/>
       <c r="AA21" s="20"/>
       <c r="AB21" s="20"/>
-      <c r="AC21" s="84"/>
-      <c r="AD21" s="84"/>
+      <c r="AC21" s="20"/>
+      <c r="AD21" s="20"/>
       <c r="AE21" s="20"/>
       <c r="AF21" s="20"/>
       <c r="AG21" s="20"/>
       <c r="AH21" s="20"/>
       <c r="AI21" s="20"/>
       <c r="AJ21" s="20"/>
-      <c r="AK21" s="96"/>
-      <c r="AL21" s="96"/>
+      <c r="AK21" s="80"/>
+      <c r="AL21" s="80"/>
       <c r="AM21" s="20"/>
       <c r="AN21" s="20"/>
       <c r="AO21" s="20"/>
@@ -4934,7 +4931,7 @@
       <c r="BM21" s="20"/>
       <c r="BN21" s="20"/>
       <c r="BO21" s="20"/>
-      <c r="BP21" s="96"/>
+      <c r="BP21" s="80"/>
       <c r="BQ21" s="43"/>
       <c r="BR21" s="43"/>
       <c r="BS21" s="43"/>
@@ -4951,7 +4948,7 @@
       <c r="CD21" s="43"/>
       <c r="CE21" s="43"/>
       <c r="CF21" s="43"/>
-      <c r="CG21" s="90"/>
+      <c r="CG21" s="76"/>
       <c r="CH21" s="20"/>
       <c r="CI21" s="20"/>
       <c r="CJ21" s="20"/>
@@ -4959,8 +4956,8 @@
       <c r="CL21" s="20"/>
       <c r="CM21" s="20"/>
       <c r="CN21" s="20"/>
-      <c r="CO21" s="83"/>
-      <c r="CP21" s="102"/>
+      <c r="CO21" s="73"/>
+      <c r="CP21" s="86"/>
       <c r="CQ21"/>
       <c r="CR21"/>
       <c r="CS21"/>
@@ -5005,92 +5002,92 @@
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="I22" s="81"/>
-      <c r="J22" s="82"/>
-      <c r="K22" s="82"/>
-      <c r="L22" s="82"/>
-      <c r="M22" s="82"/>
-      <c r="N22" s="82"/>
-      <c r="O22" s="82"/>
-      <c r="P22" s="82"/>
-      <c r="Q22" s="82"/>
-      <c r="R22" s="82"/>
-      <c r="S22" s="82"/>
-      <c r="T22" s="82"/>
-      <c r="U22" s="82"/>
-      <c r="V22" s="82"/>
-      <c r="W22" s="82"/>
-      <c r="X22" s="82"/>
-      <c r="Y22" s="82"/>
-      <c r="Z22" s="82"/>
-      <c r="AA22" s="82"/>
-      <c r="AB22" s="82"/>
-      <c r="AC22" s="82"/>
-      <c r="AD22" s="82"/>
-      <c r="AE22" s="82"/>
-      <c r="AF22" s="82"/>
-      <c r="AG22" s="82"/>
-      <c r="AH22" s="82"/>
-      <c r="AI22" s="82"/>
-      <c r="AJ22" s="82"/>
-      <c r="AK22" s="82"/>
-      <c r="AL22" s="82"/>
-      <c r="AM22" s="82"/>
-      <c r="AN22" s="82"/>
-      <c r="AO22" s="82"/>
-      <c r="AP22" s="82"/>
-      <c r="AQ22" s="82"/>
-      <c r="AR22" s="82"/>
-      <c r="AS22" s="82"/>
-      <c r="AT22" s="82"/>
-      <c r="AU22" s="82"/>
-      <c r="AV22" s="82"/>
-      <c r="AW22" s="82"/>
-      <c r="AX22" s="82"/>
-      <c r="AY22" s="82"/>
-      <c r="AZ22" s="82"/>
-      <c r="BA22" s="82"/>
-      <c r="BB22" s="82"/>
-      <c r="BC22" s="82"/>
-      <c r="BD22" s="82"/>
-      <c r="BE22" s="82"/>
-      <c r="BF22" s="82"/>
-      <c r="BG22" s="82"/>
-      <c r="BH22" s="82"/>
-      <c r="BI22" s="82"/>
-      <c r="BJ22" s="82"/>
-      <c r="BK22" s="82"/>
-      <c r="BL22" s="82"/>
-      <c r="BM22" s="82"/>
-      <c r="BN22" s="82"/>
-      <c r="BO22" s="82"/>
-      <c r="BP22" s="82"/>
-      <c r="BQ22" s="82"/>
-      <c r="BR22" s="82"/>
-      <c r="BS22" s="82"/>
-      <c r="BT22" s="82"/>
-      <c r="BU22" s="82"/>
-      <c r="BV22" s="82"/>
-      <c r="BW22" s="82"/>
-      <c r="BX22" s="82"/>
-      <c r="BY22" s="82"/>
-      <c r="BZ22" s="82"/>
-      <c r="CA22" s="82"/>
-      <c r="CB22" s="82"/>
-      <c r="CC22" s="82"/>
-      <c r="CD22" s="82"/>
-      <c r="CE22" s="82"/>
-      <c r="CF22" s="82"/>
-      <c r="CG22" s="82"/>
-      <c r="CH22" s="82"/>
-      <c r="CI22" s="82"/>
-      <c r="CJ22" s="82"/>
-      <c r="CK22" s="82"/>
-      <c r="CL22" s="82"/>
-      <c r="CM22" s="82"/>
-      <c r="CN22" s="82"/>
-      <c r="CO22" s="82"/>
-      <c r="CP22" s="102"/>
+      <c r="I22" s="93"/>
+      <c r="J22" s="94"/>
+      <c r="K22" s="94"/>
+      <c r="L22" s="94"/>
+      <c r="M22" s="94"/>
+      <c r="N22" s="94"/>
+      <c r="O22" s="94"/>
+      <c r="P22" s="94"/>
+      <c r="Q22" s="94"/>
+      <c r="R22" s="94"/>
+      <c r="S22" s="94"/>
+      <c r="T22" s="94"/>
+      <c r="U22" s="94"/>
+      <c r="V22" s="94"/>
+      <c r="W22" s="94"/>
+      <c r="X22" s="94"/>
+      <c r="Y22" s="94"/>
+      <c r="Z22" s="94"/>
+      <c r="AA22" s="94"/>
+      <c r="AB22" s="94"/>
+      <c r="AC22" s="94"/>
+      <c r="AD22" s="94"/>
+      <c r="AE22" s="94"/>
+      <c r="AF22" s="94"/>
+      <c r="AG22" s="94"/>
+      <c r="AH22" s="94"/>
+      <c r="AI22" s="94"/>
+      <c r="AJ22" s="94"/>
+      <c r="AK22" s="94"/>
+      <c r="AL22" s="94"/>
+      <c r="AM22" s="94"/>
+      <c r="AN22" s="94"/>
+      <c r="AO22" s="94"/>
+      <c r="AP22" s="94"/>
+      <c r="AQ22" s="94"/>
+      <c r="AR22" s="94"/>
+      <c r="AS22" s="94"/>
+      <c r="AT22" s="94"/>
+      <c r="AU22" s="94"/>
+      <c r="AV22" s="94"/>
+      <c r="AW22" s="94"/>
+      <c r="AX22" s="94"/>
+      <c r="AY22" s="94"/>
+      <c r="AZ22" s="94"/>
+      <c r="BA22" s="94"/>
+      <c r="BB22" s="94"/>
+      <c r="BC22" s="94"/>
+      <c r="BD22" s="94"/>
+      <c r="BE22" s="94"/>
+      <c r="BF22" s="94"/>
+      <c r="BG22" s="94"/>
+      <c r="BH22" s="94"/>
+      <c r="BI22" s="94"/>
+      <c r="BJ22" s="94"/>
+      <c r="BK22" s="94"/>
+      <c r="BL22" s="94"/>
+      <c r="BM22" s="94"/>
+      <c r="BN22" s="94"/>
+      <c r="BO22" s="94"/>
+      <c r="BP22" s="94"/>
+      <c r="BQ22" s="94"/>
+      <c r="BR22" s="94"/>
+      <c r="BS22" s="94"/>
+      <c r="BT22" s="94"/>
+      <c r="BU22" s="94"/>
+      <c r="BV22" s="94"/>
+      <c r="BW22" s="94"/>
+      <c r="BX22" s="94"/>
+      <c r="BY22" s="94"/>
+      <c r="BZ22" s="94"/>
+      <c r="CA22" s="94"/>
+      <c r="CB22" s="94"/>
+      <c r="CC22" s="94"/>
+      <c r="CD22" s="94"/>
+      <c r="CE22" s="94"/>
+      <c r="CF22" s="94"/>
+      <c r="CG22" s="94"/>
+      <c r="CH22" s="94"/>
+      <c r="CI22" s="94"/>
+      <c r="CJ22" s="94"/>
+      <c r="CK22" s="94"/>
+      <c r="CL22" s="94"/>
+      <c r="CM22" s="94"/>
+      <c r="CN22" s="94"/>
+      <c r="CO22" s="94"/>
+      <c r="CP22" s="86"/>
       <c r="CQ22"/>
       <c r="CR22"/>
       <c r="CS22"/>
@@ -5167,8 +5164,8 @@
       <c r="AH23" s="20"/>
       <c r="AI23" s="20"/>
       <c r="AJ23" s="20"/>
-      <c r="AK23" s="96"/>
-      <c r="AL23" s="96"/>
+      <c r="AK23" s="80"/>
+      <c r="AL23" s="80"/>
       <c r="AM23" s="20"/>
       <c r="AN23" s="20"/>
       <c r="AO23" s="20"/>
@@ -5198,7 +5195,7 @@
       <c r="BM23" s="20"/>
       <c r="BN23" s="20"/>
       <c r="BO23" s="20"/>
-      <c r="BP23" s="96"/>
+      <c r="BP23" s="80"/>
       <c r="BQ23" s="43"/>
       <c r="BR23" s="43"/>
       <c r="BS23" s="43"/>
@@ -5215,7 +5212,7 @@
       <c r="CD23" s="43"/>
       <c r="CE23" s="43"/>
       <c r="CF23" s="43"/>
-      <c r="CG23" s="90"/>
+      <c r="CG23" s="76"/>
       <c r="CH23" s="20"/>
       <c r="CI23" s="20"/>
       <c r="CJ23" s="20"/>
@@ -5223,8 +5220,8 @@
       <c r="CL23" s="20"/>
       <c r="CM23" s="20"/>
       <c r="CN23" s="20"/>
-      <c r="CO23" s="83"/>
-      <c r="CP23" s="102"/>
+      <c r="CO23" s="73"/>
+      <c r="CP23" s="86"/>
       <c r="CQ23"/>
       <c r="CR23"/>
       <c r="CS23"/>
@@ -5301,8 +5298,8 @@
       <c r="AH24" s="20"/>
       <c r="AI24" s="20"/>
       <c r="AJ24" s="20"/>
-      <c r="AK24" s="96"/>
-      <c r="AL24" s="96"/>
+      <c r="AK24" s="80"/>
+      <c r="AL24" s="80"/>
       <c r="AM24" s="20"/>
       <c r="AN24" s="20"/>
       <c r="AO24" s="20"/>
@@ -5332,7 +5329,7 @@
       <c r="BM24" s="20"/>
       <c r="BN24" s="20"/>
       <c r="BO24" s="20"/>
-      <c r="BP24" s="96"/>
+      <c r="BP24" s="80"/>
       <c r="BQ24" s="43"/>
       <c r="BR24" s="43"/>
       <c r="BS24" s="43"/>
@@ -5349,7 +5346,7 @@
       <c r="CD24" s="43"/>
       <c r="CE24" s="43"/>
       <c r="CF24" s="43"/>
-      <c r="CG24" s="90"/>
+      <c r="CG24" s="76"/>
       <c r="CH24" s="20"/>
       <c r="CI24" s="20"/>
       <c r="CJ24" s="20"/>
@@ -5357,8 +5354,8 @@
       <c r="CL24" s="20"/>
       <c r="CM24" s="20"/>
       <c r="CN24" s="20"/>
-      <c r="CO24" s="83"/>
-      <c r="CP24" s="102"/>
+      <c r="CO24" s="73"/>
+      <c r="CP24" s="86"/>
       <c r="CQ24"/>
       <c r="CR24"/>
       <c r="CS24"/>
@@ -5432,8 +5429,8 @@
       <c r="AH25" s="20"/>
       <c r="AI25" s="20"/>
       <c r="AJ25" s="20"/>
-      <c r="AK25" s="96"/>
-      <c r="AL25" s="96"/>
+      <c r="AK25" s="80"/>
+      <c r="AL25" s="80"/>
       <c r="AM25" s="20"/>
       <c r="AN25" s="20"/>
       <c r="AO25" s="20"/>
@@ -5463,7 +5460,7 @@
       <c r="BM25" s="20"/>
       <c r="BN25" s="20"/>
       <c r="BO25" s="20"/>
-      <c r="BP25" s="96"/>
+      <c r="BP25" s="80"/>
       <c r="BQ25" s="43"/>
       <c r="BR25" s="43"/>
       <c r="BS25" s="43"/>
@@ -5480,7 +5477,7 @@
       <c r="CD25" s="43"/>
       <c r="CE25" s="43"/>
       <c r="CF25" s="43"/>
-      <c r="CG25" s="90"/>
+      <c r="CG25" s="76"/>
       <c r="CH25" s="20"/>
       <c r="CI25" s="20"/>
       <c r="CJ25" s="20"/>
@@ -5488,8 +5485,8 @@
       <c r="CL25" s="20"/>
       <c r="CM25" s="20"/>
       <c r="CN25" s="20"/>
-      <c r="CO25" s="83"/>
-      <c r="CP25" s="102"/>
+      <c r="CO25" s="73"/>
+      <c r="CP25" s="86"/>
       <c r="CQ25"/>
       <c r="CR25"/>
       <c r="CS25"/>
@@ -5566,8 +5563,8 @@
       <c r="AH26" s="20"/>
       <c r="AI26" s="20"/>
       <c r="AJ26" s="20"/>
-      <c r="AK26" s="96"/>
-      <c r="AL26" s="96"/>
+      <c r="AK26" s="80"/>
+      <c r="AL26" s="80"/>
       <c r="AM26" s="20"/>
       <c r="AN26" s="20"/>
       <c r="AO26" s="20"/>
@@ -5597,7 +5594,7 @@
       <c r="BM26" s="20"/>
       <c r="BN26" s="20"/>
       <c r="BO26" s="20"/>
-      <c r="BP26" s="96"/>
+      <c r="BP26" s="80"/>
       <c r="BQ26" s="43"/>
       <c r="BR26" s="43"/>
       <c r="BS26" s="43"/>
@@ -5614,7 +5611,7 @@
       <c r="CD26" s="43"/>
       <c r="CE26" s="43"/>
       <c r="CF26" s="43"/>
-      <c r="CG26" s="90"/>
+      <c r="CG26" s="76"/>
       <c r="CH26" s="20"/>
       <c r="CI26" s="20"/>
       <c r="CJ26" s="20"/>
@@ -5622,8 +5619,8 @@
       <c r="CL26" s="20"/>
       <c r="CM26" s="20"/>
       <c r="CN26" s="20"/>
-      <c r="CO26" s="83"/>
-      <c r="CP26" s="102"/>
+      <c r="CO26" s="73"/>
+      <c r="CP26" s="86"/>
       <c r="CQ26"/>
       <c r="CR26"/>
       <c r="CS26"/>
@@ -5700,8 +5697,8 @@
       <c r="AH27" s="20"/>
       <c r="AI27" s="20"/>
       <c r="AJ27" s="20"/>
-      <c r="AK27" s="96"/>
-      <c r="AL27" s="96"/>
+      <c r="AK27" s="80"/>
+      <c r="AL27" s="80"/>
       <c r="AM27" s="20"/>
       <c r="AN27" s="20"/>
       <c r="AO27" s="20"/>
@@ -5731,7 +5728,7 @@
       <c r="BM27" s="20"/>
       <c r="BN27" s="20"/>
       <c r="BO27" s="20"/>
-      <c r="BP27" s="96"/>
+      <c r="BP27" s="80"/>
       <c r="BQ27" s="43"/>
       <c r="BR27" s="43"/>
       <c r="BS27" s="43"/>
@@ -5748,7 +5745,7 @@
       <c r="CD27" s="43"/>
       <c r="CE27" s="43"/>
       <c r="CF27" s="43"/>
-      <c r="CG27" s="90"/>
+      <c r="CG27" s="76"/>
       <c r="CH27" s="20"/>
       <c r="CI27" s="20"/>
       <c r="CJ27" s="20"/>
@@ -5756,8 +5753,8 @@
       <c r="CL27" s="20"/>
       <c r="CM27" s="20"/>
       <c r="CN27" s="20"/>
-      <c r="CO27" s="83"/>
-      <c r="CP27" s="102"/>
+      <c r="CO27" s="73"/>
+      <c r="CP27" s="86"/>
       <c r="CQ27"/>
       <c r="CR27"/>
       <c r="CS27"/>
@@ -5834,8 +5831,8 @@
       <c r="AH28" s="69"/>
       <c r="AI28" s="69"/>
       <c r="AJ28" s="69"/>
-      <c r="AK28" s="97"/>
-      <c r="AL28" s="97"/>
+      <c r="AK28" s="81"/>
+      <c r="AL28" s="81"/>
       <c r="AM28" s="69"/>
       <c r="AN28" s="69"/>
       <c r="AO28" s="69"/>
@@ -5865,7 +5862,7 @@
       <c r="BM28" s="69"/>
       <c r="BN28" s="69"/>
       <c r="BO28" s="69"/>
-      <c r="BP28" s="97"/>
+      <c r="BP28" s="81"/>
       <c r="BQ28" s="70"/>
       <c r="BR28" s="70"/>
       <c r="BS28" s="70"/>
@@ -5882,7 +5879,7 @@
       <c r="CD28" s="70"/>
       <c r="CE28" s="70"/>
       <c r="CF28" s="70"/>
-      <c r="CG28" s="91"/>
+      <c r="CG28" s="77"/>
       <c r="CH28" s="69"/>
       <c r="CI28" s="69"/>
       <c r="CJ28" s="69"/>
@@ -5890,8 +5887,8 @@
       <c r="CL28" s="69"/>
       <c r="CM28" s="69"/>
       <c r="CN28" s="69"/>
-      <c r="CO28" s="99"/>
-      <c r="CP28" s="102"/>
+      <c r="CO28" s="83"/>
+      <c r="CP28" s="86"/>
       <c r="CQ28"/>
       <c r="CR28"/>
       <c r="CS28"/>
@@ -6791,6 +6788,21 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="I22:CO22"/>
+    <mergeCell ref="I14:CO14"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="N3:R3"/>
+    <mergeCell ref="S3:W3"/>
+    <mergeCell ref="X3:AB3"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
     <mergeCell ref="CA3:CE3"/>
     <mergeCell ref="CF3:CJ3"/>
     <mergeCell ref="CK3:CO3"/>
@@ -6805,21 +6817,6 @@
     <mergeCell ref="AM3:AQ3"/>
     <mergeCell ref="AR3:AV3"/>
     <mergeCell ref="AW3:BA3"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="I3:M3"/>
-    <mergeCell ref="N3:R3"/>
-    <mergeCell ref="S3:W3"/>
-    <mergeCell ref="X3:AB3"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="I22:CO22"/>
-    <mergeCell ref="I14:CO14"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E2:F2"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D35">
     <cfRule type="dataBar" priority="17">
@@ -6835,43 +6832,39 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I7 CP7:DP7 I14 I22 BM29:DP34 I29:BL35 I4:DP6 CP13:DP28 CP10:DP10 BQ11:DP12 BQ8:DP9 BQ10:CH10 BQ13:CO13 I8:BP13 I23:CO28 I15:CO21">
-    <cfRule type="expression" dxfId="2" priority="36">
+  <conditionalFormatting sqref="I4:DP6 I7 CP7:DP7 BQ8:DP9 I8:BP13 BQ10:CH10 CP10:DP10 BQ11:DP12 BQ13:CO13 CP13:DP28 I14 I15:CO21 I22 I23:CO28 BM29:DP34 I29:BL35">
+    <cfRule type="expression" dxfId="8" priority="36">
       <formula>AND(TODAY()&gt;=I$4,TODAY()&lt;J$4)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I6:DP6 I7 CP7:DP7 I14 I22 BM29:DP34 I29:BL35 CP13:DP28 CP10:DP10 BQ11:DP12 BQ8:DP9 BQ10:CH10 BQ13:CO13 I8:BP13 I23:CO28 I15:CO21">
-    <cfRule type="expression" dxfId="1" priority="30">
+  <conditionalFormatting sqref="I6:DP6 I7 CP7:DP7 BQ8:DP9 I8:BP13 BQ10:CH10 CP10:DP10 BQ11:DP12 BQ13:CO13 CP13:DP28 I14 I15:CO21 I22 I23:CO28 BM29:DP34 I29:BL35">
+    <cfRule type="expression" dxfId="7" priority="30">
       <formula>AND(task_start&lt;=I$4,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$4)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="31" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="31" stopIfTrue="1">
       <formula>AND(task_end&gt;=I$4,task_start&lt;J$4)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="CJ10:CO10">
-    <cfRule type="expression" dxfId="8" priority="38">
-      <formula>AND(TODAY()&gt;=CI$4,TODAY()&lt;CJ$4)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="CJ10:CO10">
-    <cfRule type="expression" dxfId="7" priority="42">
-      <formula>AND(task_start&lt;=CI$4,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=CI$4)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="43" stopIfTrue="1">
-      <formula>AND(task_end&gt;=CI$4,task_start&lt;CJ$4)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BW20">
     <cfRule type="expression" dxfId="5" priority="45">
       <formula>AND(TODAY()&gt;=BY$4,TODAY()&lt;BZ$4)</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BW20">
     <cfRule type="expression" dxfId="4" priority="48">
       <formula>AND(task_start&lt;=BY$4,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=BY$4)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="3" priority="49" stopIfTrue="1">
       <formula>AND(task_end&gt;=BY$4,task_start&lt;BZ$4)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="CJ10:CO10">
+    <cfRule type="expression" dxfId="2" priority="38">
+      <formula>AND(TODAY()&gt;=CI$4,TODAY()&lt;CJ$4)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="42">
+      <formula>AND(task_start&lt;=CI$4,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=CI$4)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="43" stopIfTrue="1">
+      <formula>AND(task_end&gt;=CI$4,task_start&lt;CJ$4)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">
@@ -6910,6 +6903,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="24" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2d714a3296df14eba7a100bb665443ca">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49549bf45bfbbfb6cffed527380e77e1" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -7197,15 +7199,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -7227,6 +7220,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F80F839-78EF-4FF4-A673-3CC84279C232}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7247,14 +7248,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
   <ds:schemaRefs>

--- a/Capstone/Fase 1/Grupales/Carta Gantt.xlsx
+++ b/Capstone/Fase 1/Grupales/Carta Gantt.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B94A89-79E5-46F0-B1C8-6CAA1A02CF22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7B1C228-8095-4DA4-A7F0-EB296F0D98D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1303,6 +1303,39 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="41" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="8">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="8" applyBorder="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="8" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="8" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="3" xfId="9">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="12" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="169" fontId="0" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1313,39 +1346,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="42" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="12" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="8">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="8" applyBorder="1">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="8" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="8" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="3" xfId="9">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2038,164 +2038,164 @@
         <v>1</v>
       </c>
       <c r="B2" s="28"/>
-      <c r="C2" s="98" t="s">
+      <c r="C2" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="99"/>
-      <c r="E2" s="102">
+      <c r="D2" s="94"/>
+      <c r="E2" s="97">
         <f>DATE(2025,8,12)</f>
         <v>45881</v>
       </c>
-      <c r="F2" s="102"/>
+      <c r="F2" s="97"/>
     </row>
     <row r="3" spans="1:121" s="26" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="100" t="s">
+      <c r="C3" s="95" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="101"/>
+      <c r="D3" s="96"/>
       <c r="E3" s="61">
         <v>1</v>
       </c>
       <c r="H3" s="62"/>
-      <c r="I3" s="88">
+      <c r="I3" s="99">
         <f>I4</f>
         <v>45880</v>
       </c>
-      <c r="J3" s="88"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="88"/>
-      <c r="M3" s="88"/>
-      <c r="N3" s="88">
+      <c r="J3" s="99"/>
+      <c r="K3" s="99"/>
+      <c r="L3" s="99"/>
+      <c r="M3" s="99"/>
+      <c r="N3" s="99">
         <f>N4</f>
         <v>45887</v>
       </c>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88">
+      <c r="O3" s="99"/>
+      <c r="P3" s="99"/>
+      <c r="Q3" s="99"/>
+      <c r="R3" s="99"/>
+      <c r="S3" s="99">
         <f>S4</f>
         <v>45894</v>
       </c>
-      <c r="T3" s="88"/>
-      <c r="U3" s="88"/>
-      <c r="V3" s="88"/>
-      <c r="W3" s="88"/>
-      <c r="X3" s="88">
+      <c r="T3" s="99"/>
+      <c r="U3" s="99"/>
+      <c r="V3" s="99"/>
+      <c r="W3" s="99"/>
+      <c r="X3" s="99">
         <f>X4</f>
         <v>45901</v>
       </c>
-      <c r="Y3" s="88"/>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="88"/>
-      <c r="AB3" s="88"/>
-      <c r="AC3" s="88">
+      <c r="Y3" s="99"/>
+      <c r="Z3" s="99"/>
+      <c r="AA3" s="99"/>
+      <c r="AB3" s="99"/>
+      <c r="AC3" s="99">
         <f t="shared" ref="AC3" si="0">AC4</f>
         <v>45908</v>
       </c>
-      <c r="AD3" s="88"/>
-      <c r="AE3" s="88"/>
-      <c r="AF3" s="88"/>
-      <c r="AG3" s="88"/>
-      <c r="AH3" s="88">
+      <c r="AD3" s="99"/>
+      <c r="AE3" s="99"/>
+      <c r="AF3" s="99"/>
+      <c r="AG3" s="99"/>
+      <c r="AH3" s="99">
         <f t="shared" ref="AH3" si="1">AH4</f>
         <v>45915</v>
       </c>
-      <c r="AI3" s="88"/>
-      <c r="AJ3" s="88"/>
-      <c r="AK3" s="88"/>
-      <c r="AL3" s="88"/>
-      <c r="AM3" s="88">
+      <c r="AI3" s="99"/>
+      <c r="AJ3" s="99"/>
+      <c r="AK3" s="99"/>
+      <c r="AL3" s="99"/>
+      <c r="AM3" s="99">
         <f t="shared" ref="AM3" si="2">AM4</f>
         <v>45922</v>
       </c>
-      <c r="AN3" s="88"/>
-      <c r="AO3" s="88"/>
-      <c r="AP3" s="88"/>
-      <c r="AQ3" s="88"/>
-      <c r="AR3" s="88">
+      <c r="AN3" s="99"/>
+      <c r="AO3" s="99"/>
+      <c r="AP3" s="99"/>
+      <c r="AQ3" s="99"/>
+      <c r="AR3" s="99">
         <f>AR4</f>
         <v>45929</v>
       </c>
-      <c r="AS3" s="88"/>
-      <c r="AT3" s="88"/>
-      <c r="AU3" s="88"/>
-      <c r="AV3" s="88"/>
-      <c r="AW3" s="88">
+      <c r="AS3" s="99"/>
+      <c r="AT3" s="99"/>
+      <c r="AU3" s="99"/>
+      <c r="AV3" s="99"/>
+      <c r="AW3" s="99">
         <f t="shared" ref="AW3" si="3">AW4</f>
         <v>45936</v>
       </c>
-      <c r="AX3" s="88"/>
-      <c r="AY3" s="88"/>
-      <c r="AZ3" s="88"/>
-      <c r="BA3" s="88"/>
-      <c r="BB3" s="88">
+      <c r="AX3" s="99"/>
+      <c r="AY3" s="99"/>
+      <c r="AZ3" s="99"/>
+      <c r="BA3" s="99"/>
+      <c r="BB3" s="99">
         <f t="shared" ref="BB3" si="4">BB4</f>
         <v>45943</v>
       </c>
-      <c r="BC3" s="88"/>
-      <c r="BD3" s="88"/>
-      <c r="BE3" s="88"/>
-      <c r="BF3" s="88"/>
-      <c r="BG3" s="88">
+      <c r="BC3" s="99"/>
+      <c r="BD3" s="99"/>
+      <c r="BE3" s="99"/>
+      <c r="BF3" s="99"/>
+      <c r="BG3" s="99">
         <f t="shared" ref="BG3" si="5">BG4</f>
         <v>45950</v>
       </c>
-      <c r="BH3" s="88"/>
-      <c r="BI3" s="88"/>
-      <c r="BJ3" s="88"/>
-      <c r="BK3" s="88"/>
-      <c r="BL3" s="88">
+      <c r="BH3" s="99"/>
+      <c r="BI3" s="99"/>
+      <c r="BJ3" s="99"/>
+      <c r="BK3" s="99"/>
+      <c r="BL3" s="99">
         <f t="shared" ref="BL3" si="6">BL4</f>
         <v>45957</v>
       </c>
-      <c r="BM3" s="88"/>
-      <c r="BN3" s="88"/>
-      <c r="BO3" s="88"/>
-      <c r="BP3" s="88"/>
-      <c r="BQ3" s="88">
+      <c r="BM3" s="99"/>
+      <c r="BN3" s="99"/>
+      <c r="BO3" s="99"/>
+      <c r="BP3" s="99"/>
+      <c r="BQ3" s="99">
         <f t="shared" ref="BQ3" si="7">BQ4</f>
         <v>45964</v>
       </c>
-      <c r="BR3" s="88"/>
-      <c r="BS3" s="88"/>
-      <c r="BT3" s="88"/>
-      <c r="BU3" s="88"/>
-      <c r="BV3" s="88">
+      <c r="BR3" s="99"/>
+      <c r="BS3" s="99"/>
+      <c r="BT3" s="99"/>
+      <c r="BU3" s="99"/>
+      <c r="BV3" s="99">
         <f t="shared" ref="BV3" si="8">BV4</f>
         <v>45971</v>
       </c>
-      <c r="BW3" s="88"/>
-      <c r="BX3" s="88"/>
-      <c r="BY3" s="88"/>
-      <c r="BZ3" s="88"/>
-      <c r="CA3" s="88">
+      <c r="BW3" s="99"/>
+      <c r="BX3" s="99"/>
+      <c r="BY3" s="99"/>
+      <c r="BZ3" s="99"/>
+      <c r="CA3" s="99">
         <f t="shared" ref="CA3" si="9">CA4</f>
         <v>45978</v>
       </c>
-      <c r="CB3" s="88"/>
-      <c r="CC3" s="88"/>
-      <c r="CD3" s="88"/>
-      <c r="CE3" s="88"/>
-      <c r="CF3" s="88">
+      <c r="CB3" s="99"/>
+      <c r="CC3" s="99"/>
+      <c r="CD3" s="99"/>
+      <c r="CE3" s="99"/>
+      <c r="CF3" s="99">
         <f t="shared" ref="CF3" si="10">CF4</f>
         <v>45985</v>
       </c>
-      <c r="CG3" s="88"/>
-      <c r="CH3" s="88"/>
-      <c r="CI3" s="88"/>
-      <c r="CJ3" s="88"/>
-      <c r="CK3" s="88">
+      <c r="CG3" s="99"/>
+      <c r="CH3" s="99"/>
+      <c r="CI3" s="99"/>
+      <c r="CJ3" s="99"/>
+      <c r="CK3" s="99">
         <f t="shared" ref="CK3" si="11">CK4</f>
         <v>45992</v>
       </c>
-      <c r="CL3" s="88"/>
-      <c r="CM3" s="88"/>
-      <c r="CN3" s="88"/>
-      <c r="CO3" s="89"/>
+      <c r="CL3" s="99"/>
+      <c r="CM3" s="99"/>
+      <c r="CN3" s="99"/>
+      <c r="CO3" s="100"/>
       <c r="CP3" s="84"/>
       <c r="CQ3" s="74"/>
       <c r="CR3" s="74"/>
@@ -3030,91 +3030,91 @@
         <f t="shared" ref="H7:H28" si="25">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v/>
       </c>
-      <c r="I7" s="90"/>
-      <c r="J7" s="91"/>
-      <c r="K7" s="91"/>
-      <c r="L7" s="91"/>
-      <c r="M7" s="91"/>
-      <c r="N7" s="91"/>
-      <c r="O7" s="91"/>
-      <c r="P7" s="91"/>
-      <c r="Q7" s="91"/>
-      <c r="R7" s="91"/>
-      <c r="S7" s="91"/>
-      <c r="T7" s="91"/>
-      <c r="U7" s="91"/>
-      <c r="V7" s="91"/>
-      <c r="W7" s="91"/>
-      <c r="X7" s="91"/>
-      <c r="Y7" s="91"/>
-      <c r="Z7" s="91"/>
-      <c r="AA7" s="91"/>
-      <c r="AB7" s="91"/>
-      <c r="AC7" s="91"/>
-      <c r="AD7" s="91"/>
-      <c r="AE7" s="91"/>
-      <c r="AF7" s="91"/>
-      <c r="AG7" s="91"/>
-      <c r="AH7" s="91"/>
-      <c r="AI7" s="91"/>
-      <c r="AJ7" s="91"/>
-      <c r="AK7" s="91"/>
-      <c r="AL7" s="91"/>
-      <c r="AM7" s="91"/>
-      <c r="AN7" s="91"/>
-      <c r="AO7" s="91"/>
-      <c r="AP7" s="91"/>
-      <c r="AQ7" s="91"/>
-      <c r="AR7" s="91"/>
-      <c r="AS7" s="91"/>
-      <c r="AT7" s="91"/>
-      <c r="AU7" s="91"/>
-      <c r="AV7" s="91"/>
-      <c r="AW7" s="91"/>
-      <c r="AX7" s="91"/>
-      <c r="AY7" s="91"/>
-      <c r="AZ7" s="91"/>
-      <c r="BA7" s="91"/>
-      <c r="BB7" s="91"/>
-      <c r="BC7" s="91"/>
-      <c r="BD7" s="91"/>
-      <c r="BE7" s="91"/>
-      <c r="BF7" s="91"/>
-      <c r="BG7" s="91"/>
-      <c r="BH7" s="91"/>
-      <c r="BI7" s="91"/>
-      <c r="BJ7" s="91"/>
-      <c r="BK7" s="91"/>
-      <c r="BL7" s="91"/>
-      <c r="BM7" s="91"/>
-      <c r="BN7" s="91"/>
-      <c r="BO7" s="91"/>
-      <c r="BP7" s="91"/>
-      <c r="BQ7" s="91"/>
-      <c r="BR7" s="91"/>
-      <c r="BS7" s="91"/>
-      <c r="BT7" s="91"/>
-      <c r="BU7" s="91"/>
-      <c r="BV7" s="91"/>
-      <c r="BW7" s="91"/>
-      <c r="BX7" s="91"/>
-      <c r="BY7" s="91"/>
-      <c r="BZ7" s="91"/>
-      <c r="CA7" s="91"/>
-      <c r="CB7" s="91"/>
-      <c r="CC7" s="91"/>
-      <c r="CD7" s="91"/>
-      <c r="CE7" s="91"/>
-      <c r="CF7" s="91"/>
-      <c r="CG7" s="91"/>
-      <c r="CH7" s="91"/>
-      <c r="CI7" s="91"/>
-      <c r="CJ7" s="91"/>
-      <c r="CK7" s="91"/>
-      <c r="CL7" s="91"/>
-      <c r="CM7" s="91"/>
-      <c r="CN7" s="91"/>
-      <c r="CO7" s="91"/>
+      <c r="I7" s="101"/>
+      <c r="J7" s="102"/>
+      <c r="K7" s="102"/>
+      <c r="L7" s="102"/>
+      <c r="M7" s="102"/>
+      <c r="N7" s="102"/>
+      <c r="O7" s="102"/>
+      <c r="P7" s="102"/>
+      <c r="Q7" s="102"/>
+      <c r="R7" s="102"/>
+      <c r="S7" s="102"/>
+      <c r="T7" s="102"/>
+      <c r="U7" s="102"/>
+      <c r="V7" s="102"/>
+      <c r="W7" s="102"/>
+      <c r="X7" s="102"/>
+      <c r="Y7" s="102"/>
+      <c r="Z7" s="102"/>
+      <c r="AA7" s="102"/>
+      <c r="AB7" s="102"/>
+      <c r="AC7" s="102"/>
+      <c r="AD7" s="102"/>
+      <c r="AE7" s="102"/>
+      <c r="AF7" s="102"/>
+      <c r="AG7" s="102"/>
+      <c r="AH7" s="102"/>
+      <c r="AI7" s="102"/>
+      <c r="AJ7" s="102"/>
+      <c r="AK7" s="102"/>
+      <c r="AL7" s="102"/>
+      <c r="AM7" s="102"/>
+      <c r="AN7" s="102"/>
+      <c r="AO7" s="102"/>
+      <c r="AP7" s="102"/>
+      <c r="AQ7" s="102"/>
+      <c r="AR7" s="102"/>
+      <c r="AS7" s="102"/>
+      <c r="AT7" s="102"/>
+      <c r="AU7" s="102"/>
+      <c r="AV7" s="102"/>
+      <c r="AW7" s="102"/>
+      <c r="AX7" s="102"/>
+      <c r="AY7" s="102"/>
+      <c r="AZ7" s="102"/>
+      <c r="BA7" s="102"/>
+      <c r="BB7" s="102"/>
+      <c r="BC7" s="102"/>
+      <c r="BD7" s="102"/>
+      <c r="BE7" s="102"/>
+      <c r="BF7" s="102"/>
+      <c r="BG7" s="102"/>
+      <c r="BH7" s="102"/>
+      <c r="BI7" s="102"/>
+      <c r="BJ7" s="102"/>
+      <c r="BK7" s="102"/>
+      <c r="BL7" s="102"/>
+      <c r="BM7" s="102"/>
+      <c r="BN7" s="102"/>
+      <c r="BO7" s="102"/>
+      <c r="BP7" s="102"/>
+      <c r="BQ7" s="102"/>
+      <c r="BR7" s="102"/>
+      <c r="BS7" s="102"/>
+      <c r="BT7" s="102"/>
+      <c r="BU7" s="102"/>
+      <c r="BV7" s="102"/>
+      <c r="BW7" s="102"/>
+      <c r="BX7" s="102"/>
+      <c r="BY7" s="102"/>
+      <c r="BZ7" s="102"/>
+      <c r="CA7" s="102"/>
+      <c r="CB7" s="102"/>
+      <c r="CC7" s="102"/>
+      <c r="CD7" s="102"/>
+      <c r="CE7" s="102"/>
+      <c r="CF7" s="102"/>
+      <c r="CG7" s="102"/>
+      <c r="CH7" s="102"/>
+      <c r="CI7" s="102"/>
+      <c r="CJ7" s="102"/>
+      <c r="CK7" s="102"/>
+      <c r="CL7" s="102"/>
+      <c r="CM7" s="102"/>
+      <c r="CN7" s="102"/>
+      <c r="CO7" s="102"/>
       <c r="CP7" s="87"/>
       <c r="CQ7" s="78"/>
       <c r="CR7" s="78"/>
@@ -3148,10 +3148,10 @@
       <c r="A8" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="92" t="s">
+      <c r="B8" s="98" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="92"/>
+      <c r="C8" s="98"/>
       <c r="D8" s="13">
         <v>1</v>
       </c>
@@ -3282,10 +3282,10 @@
     </row>
     <row r="9" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="24"/>
-      <c r="B9" s="92" t="s">
+      <c r="B9" s="98" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="92"/>
+      <c r="C9" s="98"/>
       <c r="D9" s="13">
         <v>1</v>
       </c>
@@ -3413,10 +3413,10 @@
     </row>
     <row r="10" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="23"/>
-      <c r="B10" s="92" t="s">
+      <c r="B10" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="92"/>
+      <c r="C10" s="98"/>
       <c r="D10" s="13">
         <v>1</v>
       </c>
@@ -3547,10 +3547,10 @@
     </row>
     <row r="11" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="23"/>
-      <c r="B11" s="92" t="s">
+      <c r="B11" s="98" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="92"/>
+      <c r="C11" s="98"/>
       <c r="D11" s="13">
         <v>1</v>
       </c>
@@ -3678,10 +3678,10 @@
     </row>
     <row r="12" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="23"/>
-      <c r="B12" s="92" t="s">
+      <c r="B12" s="98" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="92"/>
+      <c r="C12" s="98"/>
       <c r="D12" s="13">
         <v>1</v>
       </c>
@@ -3810,12 +3810,12 @@
     </row>
     <row r="13" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="23"/>
-      <c r="B13" s="92" t="s">
+      <c r="B13" s="98" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="92"/>
+      <c r="C13" s="98"/>
       <c r="D13" s="13">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E13" s="41">
         <v>45912</v>
@@ -3955,91 +3955,91 @@
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="I14" s="95"/>
-      <c r="J14" s="96"/>
-      <c r="K14" s="96"/>
-      <c r="L14" s="96"/>
-      <c r="M14" s="96"/>
-      <c r="N14" s="96"/>
-      <c r="O14" s="96"/>
-      <c r="P14" s="96"/>
-      <c r="Q14" s="96"/>
-      <c r="R14" s="96"/>
-      <c r="S14" s="96"/>
-      <c r="T14" s="96"/>
-      <c r="U14" s="96"/>
-      <c r="V14" s="96"/>
-      <c r="W14" s="96"/>
-      <c r="X14" s="96"/>
-      <c r="Y14" s="96"/>
-      <c r="Z14" s="96"/>
-      <c r="AA14" s="96"/>
-      <c r="AB14" s="96"/>
-      <c r="AC14" s="96"/>
-      <c r="AD14" s="96"/>
-      <c r="AE14" s="96"/>
-      <c r="AF14" s="96"/>
-      <c r="AG14" s="96"/>
-      <c r="AH14" s="96"/>
-      <c r="AI14" s="96"/>
-      <c r="AJ14" s="96"/>
-      <c r="AK14" s="96"/>
-      <c r="AL14" s="96"/>
-      <c r="AM14" s="96"/>
-      <c r="AN14" s="96"/>
-      <c r="AO14" s="96"/>
-      <c r="AP14" s="96"/>
-      <c r="AQ14" s="96"/>
-      <c r="AR14" s="96"/>
-      <c r="AS14" s="96"/>
-      <c r="AT14" s="96"/>
-      <c r="AU14" s="96"/>
-      <c r="AV14" s="96"/>
-      <c r="AW14" s="96"/>
-      <c r="AX14" s="96"/>
-      <c r="AY14" s="96"/>
-      <c r="AZ14" s="96"/>
-      <c r="BA14" s="96"/>
-      <c r="BB14" s="96"/>
-      <c r="BC14" s="96"/>
-      <c r="BD14" s="96"/>
-      <c r="BE14" s="96"/>
-      <c r="BF14" s="96"/>
-      <c r="BG14" s="96"/>
-      <c r="BH14" s="96"/>
-      <c r="BI14" s="96"/>
-      <c r="BJ14" s="96"/>
-      <c r="BK14" s="96"/>
-      <c r="BL14" s="96"/>
-      <c r="BM14" s="96"/>
-      <c r="BN14" s="96"/>
-      <c r="BO14" s="96"/>
-      <c r="BP14" s="96"/>
-      <c r="BQ14" s="96"/>
-      <c r="BR14" s="96"/>
-      <c r="BS14" s="96"/>
-      <c r="BT14" s="96"/>
-      <c r="BU14" s="96"/>
-      <c r="BV14" s="96"/>
-      <c r="BW14" s="96"/>
-      <c r="BX14" s="96"/>
-      <c r="BY14" s="96"/>
-      <c r="BZ14" s="96"/>
-      <c r="CA14" s="96"/>
-      <c r="CB14" s="96"/>
-      <c r="CC14" s="96"/>
-      <c r="CD14" s="96"/>
-      <c r="CE14" s="96"/>
-      <c r="CF14" s="96"/>
-      <c r="CG14" s="96"/>
-      <c r="CH14" s="96"/>
-      <c r="CI14" s="96"/>
-      <c r="CJ14" s="96"/>
-      <c r="CK14" s="96"/>
-      <c r="CL14" s="96"/>
-      <c r="CM14" s="96"/>
-      <c r="CN14" s="96"/>
-      <c r="CO14" s="97"/>
+      <c r="I14" s="90"/>
+      <c r="J14" s="91"/>
+      <c r="K14" s="91"/>
+      <c r="L14" s="91"/>
+      <c r="M14" s="91"/>
+      <c r="N14" s="91"/>
+      <c r="O14" s="91"/>
+      <c r="P14" s="91"/>
+      <c r="Q14" s="91"/>
+      <c r="R14" s="91"/>
+      <c r="S14" s="91"/>
+      <c r="T14" s="91"/>
+      <c r="U14" s="91"/>
+      <c r="V14" s="91"/>
+      <c r="W14" s="91"/>
+      <c r="X14" s="91"/>
+      <c r="Y14" s="91"/>
+      <c r="Z14" s="91"/>
+      <c r="AA14" s="91"/>
+      <c r="AB14" s="91"/>
+      <c r="AC14" s="91"/>
+      <c r="AD14" s="91"/>
+      <c r="AE14" s="91"/>
+      <c r="AF14" s="91"/>
+      <c r="AG14" s="91"/>
+      <c r="AH14" s="91"/>
+      <c r="AI14" s="91"/>
+      <c r="AJ14" s="91"/>
+      <c r="AK14" s="91"/>
+      <c r="AL14" s="91"/>
+      <c r="AM14" s="91"/>
+      <c r="AN14" s="91"/>
+      <c r="AO14" s="91"/>
+      <c r="AP14" s="91"/>
+      <c r="AQ14" s="91"/>
+      <c r="AR14" s="91"/>
+      <c r="AS14" s="91"/>
+      <c r="AT14" s="91"/>
+      <c r="AU14" s="91"/>
+      <c r="AV14" s="91"/>
+      <c r="AW14" s="91"/>
+      <c r="AX14" s="91"/>
+      <c r="AY14" s="91"/>
+      <c r="AZ14" s="91"/>
+      <c r="BA14" s="91"/>
+      <c r="BB14" s="91"/>
+      <c r="BC14" s="91"/>
+      <c r="BD14" s="91"/>
+      <c r="BE14" s="91"/>
+      <c r="BF14" s="91"/>
+      <c r="BG14" s="91"/>
+      <c r="BH14" s="91"/>
+      <c r="BI14" s="91"/>
+      <c r="BJ14" s="91"/>
+      <c r="BK14" s="91"/>
+      <c r="BL14" s="91"/>
+      <c r="BM14" s="91"/>
+      <c r="BN14" s="91"/>
+      <c r="BO14" s="91"/>
+      <c r="BP14" s="91"/>
+      <c r="BQ14" s="91"/>
+      <c r="BR14" s="91"/>
+      <c r="BS14" s="91"/>
+      <c r="BT14" s="91"/>
+      <c r="BU14" s="91"/>
+      <c r="BV14" s="91"/>
+      <c r="BW14" s="91"/>
+      <c r="BX14" s="91"/>
+      <c r="BY14" s="91"/>
+      <c r="BZ14" s="91"/>
+      <c r="CA14" s="91"/>
+      <c r="CB14" s="91"/>
+      <c r="CC14" s="91"/>
+      <c r="CD14" s="91"/>
+      <c r="CE14" s="91"/>
+      <c r="CF14" s="91"/>
+      <c r="CG14" s="91"/>
+      <c r="CH14" s="91"/>
+      <c r="CI14" s="91"/>
+      <c r="CJ14" s="91"/>
+      <c r="CK14" s="91"/>
+      <c r="CL14" s="91"/>
+      <c r="CM14" s="91"/>
+      <c r="CN14" s="91"/>
+      <c r="CO14" s="92"/>
       <c r="CP14" s="86"/>
       <c r="CQ14"/>
       <c r="CR14"/>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="C17" s="30"/>
       <c r="D17" s="16">
-        <v>0.2</v>
+        <v>0.38</v>
       </c>
       <c r="E17" s="42">
         <v>45926</v>
@@ -5002,91 +5002,91 @@
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="I22" s="93"/>
-      <c r="J22" s="94"/>
-      <c r="K22" s="94"/>
-      <c r="L22" s="94"/>
-      <c r="M22" s="94"/>
-      <c r="N22" s="94"/>
-      <c r="O22" s="94"/>
-      <c r="P22" s="94"/>
-      <c r="Q22" s="94"/>
-      <c r="R22" s="94"/>
-      <c r="S22" s="94"/>
-      <c r="T22" s="94"/>
-      <c r="U22" s="94"/>
-      <c r="V22" s="94"/>
-      <c r="W22" s="94"/>
-      <c r="X22" s="94"/>
-      <c r="Y22" s="94"/>
-      <c r="Z22" s="94"/>
-      <c r="AA22" s="94"/>
-      <c r="AB22" s="94"/>
-      <c r="AC22" s="94"/>
-      <c r="AD22" s="94"/>
-      <c r="AE22" s="94"/>
-      <c r="AF22" s="94"/>
-      <c r="AG22" s="94"/>
-      <c r="AH22" s="94"/>
-      <c r="AI22" s="94"/>
-      <c r="AJ22" s="94"/>
-      <c r="AK22" s="94"/>
-      <c r="AL22" s="94"/>
-      <c r="AM22" s="94"/>
-      <c r="AN22" s="94"/>
-      <c r="AO22" s="94"/>
-      <c r="AP22" s="94"/>
-      <c r="AQ22" s="94"/>
-      <c r="AR22" s="94"/>
-      <c r="AS22" s="94"/>
-      <c r="AT22" s="94"/>
-      <c r="AU22" s="94"/>
-      <c r="AV22" s="94"/>
-      <c r="AW22" s="94"/>
-      <c r="AX22" s="94"/>
-      <c r="AY22" s="94"/>
-      <c r="AZ22" s="94"/>
-      <c r="BA22" s="94"/>
-      <c r="BB22" s="94"/>
-      <c r="BC22" s="94"/>
-      <c r="BD22" s="94"/>
-      <c r="BE22" s="94"/>
-      <c r="BF22" s="94"/>
-      <c r="BG22" s="94"/>
-      <c r="BH22" s="94"/>
-      <c r="BI22" s="94"/>
-      <c r="BJ22" s="94"/>
-      <c r="BK22" s="94"/>
-      <c r="BL22" s="94"/>
-      <c r="BM22" s="94"/>
-      <c r="BN22" s="94"/>
-      <c r="BO22" s="94"/>
-      <c r="BP22" s="94"/>
-      <c r="BQ22" s="94"/>
-      <c r="BR22" s="94"/>
-      <c r="BS22" s="94"/>
-      <c r="BT22" s="94"/>
-      <c r="BU22" s="94"/>
-      <c r="BV22" s="94"/>
-      <c r="BW22" s="94"/>
-      <c r="BX22" s="94"/>
-      <c r="BY22" s="94"/>
-      <c r="BZ22" s="94"/>
-      <c r="CA22" s="94"/>
-      <c r="CB22" s="94"/>
-      <c r="CC22" s="94"/>
-      <c r="CD22" s="94"/>
-      <c r="CE22" s="94"/>
-      <c r="CF22" s="94"/>
-      <c r="CG22" s="94"/>
-      <c r="CH22" s="94"/>
-      <c r="CI22" s="94"/>
-      <c r="CJ22" s="94"/>
-      <c r="CK22" s="94"/>
-      <c r="CL22" s="94"/>
-      <c r="CM22" s="94"/>
-      <c r="CN22" s="94"/>
-      <c r="CO22" s="94"/>
+      <c r="I22" s="88"/>
+      <c r="J22" s="89"/>
+      <c r="K22" s="89"/>
+      <c r="L22" s="89"/>
+      <c r="M22" s="89"/>
+      <c r="N22" s="89"/>
+      <c r="O22" s="89"/>
+      <c r="P22" s="89"/>
+      <c r="Q22" s="89"/>
+      <c r="R22" s="89"/>
+      <c r="S22" s="89"/>
+      <c r="T22" s="89"/>
+      <c r="U22" s="89"/>
+      <c r="V22" s="89"/>
+      <c r="W22" s="89"/>
+      <c r="X22" s="89"/>
+      <c r="Y22" s="89"/>
+      <c r="Z22" s="89"/>
+      <c r="AA22" s="89"/>
+      <c r="AB22" s="89"/>
+      <c r="AC22" s="89"/>
+      <c r="AD22" s="89"/>
+      <c r="AE22" s="89"/>
+      <c r="AF22" s="89"/>
+      <c r="AG22" s="89"/>
+      <c r="AH22" s="89"/>
+      <c r="AI22" s="89"/>
+      <c r="AJ22" s="89"/>
+      <c r="AK22" s="89"/>
+      <c r="AL22" s="89"/>
+      <c r="AM22" s="89"/>
+      <c r="AN22" s="89"/>
+      <c r="AO22" s="89"/>
+      <c r="AP22" s="89"/>
+      <c r="AQ22" s="89"/>
+      <c r="AR22" s="89"/>
+      <c r="AS22" s="89"/>
+      <c r="AT22" s="89"/>
+      <c r="AU22" s="89"/>
+      <c r="AV22" s="89"/>
+      <c r="AW22" s="89"/>
+      <c r="AX22" s="89"/>
+      <c r="AY22" s="89"/>
+      <c r="AZ22" s="89"/>
+      <c r="BA22" s="89"/>
+      <c r="BB22" s="89"/>
+      <c r="BC22" s="89"/>
+      <c r="BD22" s="89"/>
+      <c r="BE22" s="89"/>
+      <c r="BF22" s="89"/>
+      <c r="BG22" s="89"/>
+      <c r="BH22" s="89"/>
+      <c r="BI22" s="89"/>
+      <c r="BJ22" s="89"/>
+      <c r="BK22" s="89"/>
+      <c r="BL22" s="89"/>
+      <c r="BM22" s="89"/>
+      <c r="BN22" s="89"/>
+      <c r="BO22" s="89"/>
+      <c r="BP22" s="89"/>
+      <c r="BQ22" s="89"/>
+      <c r="BR22" s="89"/>
+      <c r="BS22" s="89"/>
+      <c r="BT22" s="89"/>
+      <c r="BU22" s="89"/>
+      <c r="BV22" s="89"/>
+      <c r="BW22" s="89"/>
+      <c r="BX22" s="89"/>
+      <c r="BY22" s="89"/>
+      <c r="BZ22" s="89"/>
+      <c r="CA22" s="89"/>
+      <c r="CB22" s="89"/>
+      <c r="CC22" s="89"/>
+      <c r="CD22" s="89"/>
+      <c r="CE22" s="89"/>
+      <c r="CF22" s="89"/>
+      <c r="CG22" s="89"/>
+      <c r="CH22" s="89"/>
+      <c r="CI22" s="89"/>
+      <c r="CJ22" s="89"/>
+      <c r="CK22" s="89"/>
+      <c r="CL22" s="89"/>
+      <c r="CM22" s="89"/>
+      <c r="CN22" s="89"/>
+      <c r="CO22" s="89"/>
       <c r="CP22" s="86"/>
       <c r="CQ22"/>
       <c r="CR22"/>
@@ -6788,6 +6788,19 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="CF3:CJ3"/>
+    <mergeCell ref="CK3:CO3"/>
+    <mergeCell ref="I7:CO7"/>
+    <mergeCell ref="BB3:BF3"/>
+    <mergeCell ref="BG3:BK3"/>
+    <mergeCell ref="BL3:BP3"/>
+    <mergeCell ref="BQ3:BU3"/>
+    <mergeCell ref="BV3:BZ3"/>
+    <mergeCell ref="AC3:AG3"/>
+    <mergeCell ref="AH3:AL3"/>
+    <mergeCell ref="AM3:AQ3"/>
+    <mergeCell ref="AR3:AV3"/>
+    <mergeCell ref="AW3:BA3"/>
     <mergeCell ref="I22:CO22"/>
     <mergeCell ref="I14:CO14"/>
     <mergeCell ref="C2:D2"/>
@@ -6804,19 +6817,6 @@
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="CA3:CE3"/>
-    <mergeCell ref="CF3:CJ3"/>
-    <mergeCell ref="CK3:CO3"/>
-    <mergeCell ref="I7:CO7"/>
-    <mergeCell ref="BB3:BF3"/>
-    <mergeCell ref="BG3:BK3"/>
-    <mergeCell ref="BL3:BP3"/>
-    <mergeCell ref="BQ3:BU3"/>
-    <mergeCell ref="BV3:BZ3"/>
-    <mergeCell ref="AC3:AG3"/>
-    <mergeCell ref="AH3:AL3"/>
-    <mergeCell ref="AM3:AQ3"/>
-    <mergeCell ref="AR3:AV3"/>
-    <mergeCell ref="AW3:BA3"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D35">
     <cfRule type="dataBar" priority="17">
@@ -6903,15 +6903,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="24" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2d714a3296df14eba7a100bb665443ca">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49549bf45bfbbfb6cffed527380e77e1" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -7199,6 +7190,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -7220,14 +7220,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F80F839-78EF-4FF4-A673-3CC84279C232}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7248,6 +7240,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
   <ds:schemaRefs>

--- a/Capstone/Fase 1/Grupales/Carta Gantt.xlsx
+++ b/Capstone/Fase 1/Grupales/Carta Gantt.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7B1C228-8095-4DA4-A7F0-EB296F0D98D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF7B829F-2271-4064-9E93-AFEFBB24DB9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Carta Gatt" sheetId="11" r:id="rId1"/>
@@ -1303,6 +1303,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="41" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="42" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="42" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1335,18 +1347,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="12" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="42" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="42" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -2038,164 +2038,164 @@
         <v>1</v>
       </c>
       <c r="B2" s="28"/>
-      <c r="C2" s="93" t="s">
+      <c r="C2" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="94"/>
-      <c r="E2" s="97">
+      <c r="D2" s="98"/>
+      <c r="E2" s="101">
         <f>DATE(2025,8,12)</f>
         <v>45881</v>
       </c>
-      <c r="F2" s="97"/>
+      <c r="F2" s="101"/>
     </row>
     <row r="3" spans="1:121" s="26" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="95" t="s">
+      <c r="C3" s="99" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="96"/>
+      <c r="D3" s="100"/>
       <c r="E3" s="61">
         <v>1</v>
       </c>
       <c r="H3" s="62"/>
-      <c r="I3" s="99">
+      <c r="I3" s="88">
         <f>I4</f>
         <v>45880</v>
       </c>
-      <c r="J3" s="99"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="99"/>
-      <c r="M3" s="99"/>
-      <c r="N3" s="99">
+      <c r="J3" s="88"/>
+      <c r="K3" s="88"/>
+      <c r="L3" s="88"/>
+      <c r="M3" s="88"/>
+      <c r="N3" s="88">
         <f>N4</f>
         <v>45887</v>
       </c>
-      <c r="O3" s="99"/>
-      <c r="P3" s="99"/>
-      <c r="Q3" s="99"/>
-      <c r="R3" s="99"/>
-      <c r="S3" s="99">
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88">
         <f>S4</f>
         <v>45894</v>
       </c>
-      <c r="T3" s="99"/>
-      <c r="U3" s="99"/>
-      <c r="V3" s="99"/>
-      <c r="W3" s="99"/>
-      <c r="X3" s="99">
+      <c r="T3" s="88"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="W3" s="88"/>
+      <c r="X3" s="88">
         <f>X4</f>
         <v>45901</v>
       </c>
-      <c r="Y3" s="99"/>
-      <c r="Z3" s="99"/>
-      <c r="AA3" s="99"/>
-      <c r="AB3" s="99"/>
-      <c r="AC3" s="99">
+      <c r="Y3" s="88"/>
+      <c r="Z3" s="88"/>
+      <c r="AA3" s="88"/>
+      <c r="AB3" s="88"/>
+      <c r="AC3" s="88">
         <f t="shared" ref="AC3" si="0">AC4</f>
         <v>45908</v>
       </c>
-      <c r="AD3" s="99"/>
-      <c r="AE3" s="99"/>
-      <c r="AF3" s="99"/>
-      <c r="AG3" s="99"/>
-      <c r="AH3" s="99">
+      <c r="AD3" s="88"/>
+      <c r="AE3" s="88"/>
+      <c r="AF3" s="88"/>
+      <c r="AG3" s="88"/>
+      <c r="AH3" s="88">
         <f t="shared" ref="AH3" si="1">AH4</f>
         <v>45915</v>
       </c>
-      <c r="AI3" s="99"/>
-      <c r="AJ3" s="99"/>
-      <c r="AK3" s="99"/>
-      <c r="AL3" s="99"/>
-      <c r="AM3" s="99">
+      <c r="AI3" s="88"/>
+      <c r="AJ3" s="88"/>
+      <c r="AK3" s="88"/>
+      <c r="AL3" s="88"/>
+      <c r="AM3" s="88">
         <f t="shared" ref="AM3" si="2">AM4</f>
         <v>45922</v>
       </c>
-      <c r="AN3" s="99"/>
-      <c r="AO3" s="99"/>
-      <c r="AP3" s="99"/>
-      <c r="AQ3" s="99"/>
-      <c r="AR3" s="99">
+      <c r="AN3" s="88"/>
+      <c r="AO3" s="88"/>
+      <c r="AP3" s="88"/>
+      <c r="AQ3" s="88"/>
+      <c r="AR3" s="88">
         <f>AR4</f>
         <v>45929</v>
       </c>
-      <c r="AS3" s="99"/>
-      <c r="AT3" s="99"/>
-      <c r="AU3" s="99"/>
-      <c r="AV3" s="99"/>
-      <c r="AW3" s="99">
+      <c r="AS3" s="88"/>
+      <c r="AT3" s="88"/>
+      <c r="AU3" s="88"/>
+      <c r="AV3" s="88"/>
+      <c r="AW3" s="88">
         <f t="shared" ref="AW3" si="3">AW4</f>
         <v>45936</v>
       </c>
-      <c r="AX3" s="99"/>
-      <c r="AY3" s="99"/>
-      <c r="AZ3" s="99"/>
-      <c r="BA3" s="99"/>
-      <c r="BB3" s="99">
+      <c r="AX3" s="88"/>
+      <c r="AY3" s="88"/>
+      <c r="AZ3" s="88"/>
+      <c r="BA3" s="88"/>
+      <c r="BB3" s="88">
         <f t="shared" ref="BB3" si="4">BB4</f>
         <v>45943</v>
       </c>
-      <c r="BC3" s="99"/>
-      <c r="BD3" s="99"/>
-      <c r="BE3" s="99"/>
-      <c r="BF3" s="99"/>
-      <c r="BG3" s="99">
+      <c r="BC3" s="88"/>
+      <c r="BD3" s="88"/>
+      <c r="BE3" s="88"/>
+      <c r="BF3" s="88"/>
+      <c r="BG3" s="88">
         <f t="shared" ref="BG3" si="5">BG4</f>
         <v>45950</v>
       </c>
-      <c r="BH3" s="99"/>
-      <c r="BI3" s="99"/>
-      <c r="BJ3" s="99"/>
-      <c r="BK3" s="99"/>
-      <c r="BL3" s="99">
+      <c r="BH3" s="88"/>
+      <c r="BI3" s="88"/>
+      <c r="BJ3" s="88"/>
+      <c r="BK3" s="88"/>
+      <c r="BL3" s="88">
         <f t="shared" ref="BL3" si="6">BL4</f>
         <v>45957</v>
       </c>
-      <c r="BM3" s="99"/>
-      <c r="BN3" s="99"/>
-      <c r="BO3" s="99"/>
-      <c r="BP3" s="99"/>
-      <c r="BQ3" s="99">
+      <c r="BM3" s="88"/>
+      <c r="BN3" s="88"/>
+      <c r="BO3" s="88"/>
+      <c r="BP3" s="88"/>
+      <c r="BQ3" s="88">
         <f t="shared" ref="BQ3" si="7">BQ4</f>
         <v>45964</v>
       </c>
-      <c r="BR3" s="99"/>
-      <c r="BS3" s="99"/>
-      <c r="BT3" s="99"/>
-      <c r="BU3" s="99"/>
-      <c r="BV3" s="99">
+      <c r="BR3" s="88"/>
+      <c r="BS3" s="88"/>
+      <c r="BT3" s="88"/>
+      <c r="BU3" s="88"/>
+      <c r="BV3" s="88">
         <f t="shared" ref="BV3" si="8">BV4</f>
         <v>45971</v>
       </c>
-      <c r="BW3" s="99"/>
-      <c r="BX3" s="99"/>
-      <c r="BY3" s="99"/>
-      <c r="BZ3" s="99"/>
-      <c r="CA3" s="99">
+      <c r="BW3" s="88"/>
+      <c r="BX3" s="88"/>
+      <c r="BY3" s="88"/>
+      <c r="BZ3" s="88"/>
+      <c r="CA3" s="88">
         <f t="shared" ref="CA3" si="9">CA4</f>
         <v>45978</v>
       </c>
-      <c r="CB3" s="99"/>
-      <c r="CC3" s="99"/>
-      <c r="CD3" s="99"/>
-      <c r="CE3" s="99"/>
-      <c r="CF3" s="99">
+      <c r="CB3" s="88"/>
+      <c r="CC3" s="88"/>
+      <c r="CD3" s="88"/>
+      <c r="CE3" s="88"/>
+      <c r="CF3" s="88">
         <f t="shared" ref="CF3" si="10">CF4</f>
         <v>45985</v>
       </c>
-      <c r="CG3" s="99"/>
-      <c r="CH3" s="99"/>
-      <c r="CI3" s="99"/>
-      <c r="CJ3" s="99"/>
-      <c r="CK3" s="99">
+      <c r="CG3" s="88"/>
+      <c r="CH3" s="88"/>
+      <c r="CI3" s="88"/>
+      <c r="CJ3" s="88"/>
+      <c r="CK3" s="88">
         <f t="shared" ref="CK3" si="11">CK4</f>
         <v>45992</v>
       </c>
-      <c r="CL3" s="99"/>
-      <c r="CM3" s="99"/>
-      <c r="CN3" s="99"/>
-      <c r="CO3" s="100"/>
+      <c r="CL3" s="88"/>
+      <c r="CM3" s="88"/>
+      <c r="CN3" s="88"/>
+      <c r="CO3" s="89"/>
       <c r="CP3" s="84"/>
       <c r="CQ3" s="74"/>
       <c r="CR3" s="74"/>
@@ -3030,91 +3030,91 @@
         <f t="shared" ref="H7:H28" si="25">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v/>
       </c>
-      <c r="I7" s="101"/>
-      <c r="J7" s="102"/>
-      <c r="K7" s="102"/>
-      <c r="L7" s="102"/>
-      <c r="M7" s="102"/>
-      <c r="N7" s="102"/>
-      <c r="O7" s="102"/>
-      <c r="P7" s="102"/>
-      <c r="Q7" s="102"/>
-      <c r="R7" s="102"/>
-      <c r="S7" s="102"/>
-      <c r="T7" s="102"/>
-      <c r="U7" s="102"/>
-      <c r="V7" s="102"/>
-      <c r="W7" s="102"/>
-      <c r="X7" s="102"/>
-      <c r="Y7" s="102"/>
-      <c r="Z7" s="102"/>
-      <c r="AA7" s="102"/>
-      <c r="AB7" s="102"/>
-      <c r="AC7" s="102"/>
-      <c r="AD7" s="102"/>
-      <c r="AE7" s="102"/>
-      <c r="AF7" s="102"/>
-      <c r="AG7" s="102"/>
-      <c r="AH7" s="102"/>
-      <c r="AI7" s="102"/>
-      <c r="AJ7" s="102"/>
-      <c r="AK7" s="102"/>
-      <c r="AL7" s="102"/>
-      <c r="AM7" s="102"/>
-      <c r="AN7" s="102"/>
-      <c r="AO7" s="102"/>
-      <c r="AP7" s="102"/>
-      <c r="AQ7" s="102"/>
-      <c r="AR7" s="102"/>
-      <c r="AS7" s="102"/>
-      <c r="AT7" s="102"/>
-      <c r="AU7" s="102"/>
-      <c r="AV7" s="102"/>
-      <c r="AW7" s="102"/>
-      <c r="AX7" s="102"/>
-      <c r="AY7" s="102"/>
-      <c r="AZ7" s="102"/>
-      <c r="BA7" s="102"/>
-      <c r="BB7" s="102"/>
-      <c r="BC7" s="102"/>
-      <c r="BD7" s="102"/>
-      <c r="BE7" s="102"/>
-      <c r="BF7" s="102"/>
-      <c r="BG7" s="102"/>
-      <c r="BH7" s="102"/>
-      <c r="BI7" s="102"/>
-      <c r="BJ7" s="102"/>
-      <c r="BK7" s="102"/>
-      <c r="BL7" s="102"/>
-      <c r="BM7" s="102"/>
-      <c r="BN7" s="102"/>
-      <c r="BO7" s="102"/>
-      <c r="BP7" s="102"/>
-      <c r="BQ7" s="102"/>
-      <c r="BR7" s="102"/>
-      <c r="BS7" s="102"/>
-      <c r="BT7" s="102"/>
-      <c r="BU7" s="102"/>
-      <c r="BV7" s="102"/>
-      <c r="BW7" s="102"/>
-      <c r="BX7" s="102"/>
-      <c r="BY7" s="102"/>
-      <c r="BZ7" s="102"/>
-      <c r="CA7" s="102"/>
-      <c r="CB7" s="102"/>
-      <c r="CC7" s="102"/>
-      <c r="CD7" s="102"/>
-      <c r="CE7" s="102"/>
-      <c r="CF7" s="102"/>
-      <c r="CG7" s="102"/>
-      <c r="CH7" s="102"/>
-      <c r="CI7" s="102"/>
-      <c r="CJ7" s="102"/>
-      <c r="CK7" s="102"/>
-      <c r="CL7" s="102"/>
-      <c r="CM7" s="102"/>
-      <c r="CN7" s="102"/>
-      <c r="CO7" s="102"/>
+      <c r="I7" s="90"/>
+      <c r="J7" s="91"/>
+      <c r="K7" s="91"/>
+      <c r="L7" s="91"/>
+      <c r="M7" s="91"/>
+      <c r="N7" s="91"/>
+      <c r="O7" s="91"/>
+      <c r="P7" s="91"/>
+      <c r="Q7" s="91"/>
+      <c r="R7" s="91"/>
+      <c r="S7" s="91"/>
+      <c r="T7" s="91"/>
+      <c r="U7" s="91"/>
+      <c r="V7" s="91"/>
+      <c r="W7" s="91"/>
+      <c r="X7" s="91"/>
+      <c r="Y7" s="91"/>
+      <c r="Z7" s="91"/>
+      <c r="AA7" s="91"/>
+      <c r="AB7" s="91"/>
+      <c r="AC7" s="91"/>
+      <c r="AD7" s="91"/>
+      <c r="AE7" s="91"/>
+      <c r="AF7" s="91"/>
+      <c r="AG7" s="91"/>
+      <c r="AH7" s="91"/>
+      <c r="AI7" s="91"/>
+      <c r="AJ7" s="91"/>
+      <c r="AK7" s="91"/>
+      <c r="AL7" s="91"/>
+      <c r="AM7" s="91"/>
+      <c r="AN7" s="91"/>
+      <c r="AO7" s="91"/>
+      <c r="AP7" s="91"/>
+      <c r="AQ7" s="91"/>
+      <c r="AR7" s="91"/>
+      <c r="AS7" s="91"/>
+      <c r="AT7" s="91"/>
+      <c r="AU7" s="91"/>
+      <c r="AV7" s="91"/>
+      <c r="AW7" s="91"/>
+      <c r="AX7" s="91"/>
+      <c r="AY7" s="91"/>
+      <c r="AZ7" s="91"/>
+      <c r="BA7" s="91"/>
+      <c r="BB7" s="91"/>
+      <c r="BC7" s="91"/>
+      <c r="BD7" s="91"/>
+      <c r="BE7" s="91"/>
+      <c r="BF7" s="91"/>
+      <c r="BG7" s="91"/>
+      <c r="BH7" s="91"/>
+      <c r="BI7" s="91"/>
+      <c r="BJ7" s="91"/>
+      <c r="BK7" s="91"/>
+      <c r="BL7" s="91"/>
+      <c r="BM7" s="91"/>
+      <c r="BN7" s="91"/>
+      <c r="BO7" s="91"/>
+      <c r="BP7" s="91"/>
+      <c r="BQ7" s="91"/>
+      <c r="BR7" s="91"/>
+      <c r="BS7" s="91"/>
+      <c r="BT7" s="91"/>
+      <c r="BU7" s="91"/>
+      <c r="BV7" s="91"/>
+      <c r="BW7" s="91"/>
+      <c r="BX7" s="91"/>
+      <c r="BY7" s="91"/>
+      <c r="BZ7" s="91"/>
+      <c r="CA7" s="91"/>
+      <c r="CB7" s="91"/>
+      <c r="CC7" s="91"/>
+      <c r="CD7" s="91"/>
+      <c r="CE7" s="91"/>
+      <c r="CF7" s="91"/>
+      <c r="CG7" s="91"/>
+      <c r="CH7" s="91"/>
+      <c r="CI7" s="91"/>
+      <c r="CJ7" s="91"/>
+      <c r="CK7" s="91"/>
+      <c r="CL7" s="91"/>
+      <c r="CM7" s="91"/>
+      <c r="CN7" s="91"/>
+      <c r="CO7" s="91"/>
       <c r="CP7" s="87"/>
       <c r="CQ7" s="78"/>
       <c r="CR7" s="78"/>
@@ -3148,10 +3148,10 @@
       <c r="A8" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="98" t="s">
+      <c r="B8" s="102" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="98"/>
+      <c r="C8" s="102"/>
       <c r="D8" s="13">
         <v>1</v>
       </c>
@@ -3282,10 +3282,10 @@
     </row>
     <row r="9" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="24"/>
-      <c r="B9" s="98" t="s">
+      <c r="B9" s="102" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="98"/>
+      <c r="C9" s="102"/>
       <c r="D9" s="13">
         <v>1</v>
       </c>
@@ -3413,10 +3413,10 @@
     </row>
     <row r="10" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="23"/>
-      <c r="B10" s="98" t="s">
+      <c r="B10" s="102" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="98"/>
+      <c r="C10" s="102"/>
       <c r="D10" s="13">
         <v>1</v>
       </c>
@@ -3547,10 +3547,10 @@
     </row>
     <row r="11" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="23"/>
-      <c r="B11" s="98" t="s">
+      <c r="B11" s="102" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="98"/>
+      <c r="C11" s="102"/>
       <c r="D11" s="13">
         <v>1</v>
       </c>
@@ -3678,10 +3678,10 @@
     </row>
     <row r="12" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="23"/>
-      <c r="B12" s="98" t="s">
+      <c r="B12" s="102" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="98"/>
+      <c r="C12" s="102"/>
       <c r="D12" s="13">
         <v>1</v>
       </c>
@@ -3810,12 +3810,12 @@
     </row>
     <row r="13" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="23"/>
-      <c r="B13" s="98" t="s">
+      <c r="B13" s="102" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="98"/>
+      <c r="C13" s="102"/>
       <c r="D13" s="13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E13" s="41">
         <v>45912</v>
@@ -3955,91 +3955,91 @@
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="I14" s="90"/>
-      <c r="J14" s="91"/>
-      <c r="K14" s="91"/>
-      <c r="L14" s="91"/>
-      <c r="M14" s="91"/>
-      <c r="N14" s="91"/>
-      <c r="O14" s="91"/>
-      <c r="P14" s="91"/>
-      <c r="Q14" s="91"/>
-      <c r="R14" s="91"/>
-      <c r="S14" s="91"/>
-      <c r="T14" s="91"/>
-      <c r="U14" s="91"/>
-      <c r="V14" s="91"/>
-      <c r="W14" s="91"/>
-      <c r="X14" s="91"/>
-      <c r="Y14" s="91"/>
-      <c r="Z14" s="91"/>
-      <c r="AA14" s="91"/>
-      <c r="AB14" s="91"/>
-      <c r="AC14" s="91"/>
-      <c r="AD14" s="91"/>
-      <c r="AE14" s="91"/>
-      <c r="AF14" s="91"/>
-      <c r="AG14" s="91"/>
-      <c r="AH14" s="91"/>
-      <c r="AI14" s="91"/>
-      <c r="AJ14" s="91"/>
-      <c r="AK14" s="91"/>
-      <c r="AL14" s="91"/>
-      <c r="AM14" s="91"/>
-      <c r="AN14" s="91"/>
-      <c r="AO14" s="91"/>
-      <c r="AP14" s="91"/>
-      <c r="AQ14" s="91"/>
-      <c r="AR14" s="91"/>
-      <c r="AS14" s="91"/>
-      <c r="AT14" s="91"/>
-      <c r="AU14" s="91"/>
-      <c r="AV14" s="91"/>
-      <c r="AW14" s="91"/>
-      <c r="AX14" s="91"/>
-      <c r="AY14" s="91"/>
-      <c r="AZ14" s="91"/>
-      <c r="BA14" s="91"/>
-      <c r="BB14" s="91"/>
-      <c r="BC14" s="91"/>
-      <c r="BD14" s="91"/>
-      <c r="BE14" s="91"/>
-      <c r="BF14" s="91"/>
-      <c r="BG14" s="91"/>
-      <c r="BH14" s="91"/>
-      <c r="BI14" s="91"/>
-      <c r="BJ14" s="91"/>
-      <c r="BK14" s="91"/>
-      <c r="BL14" s="91"/>
-      <c r="BM14" s="91"/>
-      <c r="BN14" s="91"/>
-      <c r="BO14" s="91"/>
-      <c r="BP14" s="91"/>
-      <c r="BQ14" s="91"/>
-      <c r="BR14" s="91"/>
-      <c r="BS14" s="91"/>
-      <c r="BT14" s="91"/>
-      <c r="BU14" s="91"/>
-      <c r="BV14" s="91"/>
-      <c r="BW14" s="91"/>
-      <c r="BX14" s="91"/>
-      <c r="BY14" s="91"/>
-      <c r="BZ14" s="91"/>
-      <c r="CA14" s="91"/>
-      <c r="CB14" s="91"/>
-      <c r="CC14" s="91"/>
-      <c r="CD14" s="91"/>
-      <c r="CE14" s="91"/>
-      <c r="CF14" s="91"/>
-      <c r="CG14" s="91"/>
-      <c r="CH14" s="91"/>
-      <c r="CI14" s="91"/>
-      <c r="CJ14" s="91"/>
-      <c r="CK14" s="91"/>
-      <c r="CL14" s="91"/>
-      <c r="CM14" s="91"/>
-      <c r="CN14" s="91"/>
-      <c r="CO14" s="92"/>
+      <c r="I14" s="94"/>
+      <c r="J14" s="95"/>
+      <c r="K14" s="95"/>
+      <c r="L14" s="95"/>
+      <c r="M14" s="95"/>
+      <c r="N14" s="95"/>
+      <c r="O14" s="95"/>
+      <c r="P14" s="95"/>
+      <c r="Q14" s="95"/>
+      <c r="R14" s="95"/>
+      <c r="S14" s="95"/>
+      <c r="T14" s="95"/>
+      <c r="U14" s="95"/>
+      <c r="V14" s="95"/>
+      <c r="W14" s="95"/>
+      <c r="X14" s="95"/>
+      <c r="Y14" s="95"/>
+      <c r="Z14" s="95"/>
+      <c r="AA14" s="95"/>
+      <c r="AB14" s="95"/>
+      <c r="AC14" s="95"/>
+      <c r="AD14" s="95"/>
+      <c r="AE14" s="95"/>
+      <c r="AF14" s="95"/>
+      <c r="AG14" s="95"/>
+      <c r="AH14" s="95"/>
+      <c r="AI14" s="95"/>
+      <c r="AJ14" s="95"/>
+      <c r="AK14" s="95"/>
+      <c r="AL14" s="95"/>
+      <c r="AM14" s="95"/>
+      <c r="AN14" s="95"/>
+      <c r="AO14" s="95"/>
+      <c r="AP14" s="95"/>
+      <c r="AQ14" s="95"/>
+      <c r="AR14" s="95"/>
+      <c r="AS14" s="95"/>
+      <c r="AT14" s="95"/>
+      <c r="AU14" s="95"/>
+      <c r="AV14" s="95"/>
+      <c r="AW14" s="95"/>
+      <c r="AX14" s="95"/>
+      <c r="AY14" s="95"/>
+      <c r="AZ14" s="95"/>
+      <c r="BA14" s="95"/>
+      <c r="BB14" s="95"/>
+      <c r="BC14" s="95"/>
+      <c r="BD14" s="95"/>
+      <c r="BE14" s="95"/>
+      <c r="BF14" s="95"/>
+      <c r="BG14" s="95"/>
+      <c r="BH14" s="95"/>
+      <c r="BI14" s="95"/>
+      <c r="BJ14" s="95"/>
+      <c r="BK14" s="95"/>
+      <c r="BL14" s="95"/>
+      <c r="BM14" s="95"/>
+      <c r="BN14" s="95"/>
+      <c r="BO14" s="95"/>
+      <c r="BP14" s="95"/>
+      <c r="BQ14" s="95"/>
+      <c r="BR14" s="95"/>
+      <c r="BS14" s="95"/>
+      <c r="BT14" s="95"/>
+      <c r="BU14" s="95"/>
+      <c r="BV14" s="95"/>
+      <c r="BW14" s="95"/>
+      <c r="BX14" s="95"/>
+      <c r="BY14" s="95"/>
+      <c r="BZ14" s="95"/>
+      <c r="CA14" s="95"/>
+      <c r="CB14" s="95"/>
+      <c r="CC14" s="95"/>
+      <c r="CD14" s="95"/>
+      <c r="CE14" s="95"/>
+      <c r="CF14" s="95"/>
+      <c r="CG14" s="95"/>
+      <c r="CH14" s="95"/>
+      <c r="CI14" s="95"/>
+      <c r="CJ14" s="95"/>
+      <c r="CK14" s="95"/>
+      <c r="CL14" s="95"/>
+      <c r="CM14" s="95"/>
+      <c r="CN14" s="95"/>
+      <c r="CO14" s="96"/>
       <c r="CP14" s="86"/>
       <c r="CQ14"/>
       <c r="CR14"/>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="C16" s="30"/>
       <c r="D16" s="16">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="E16" s="42">
         <v>45922</v>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="C17" s="30"/>
       <c r="D17" s="16">
-        <v>0.38</v>
+        <v>0.6</v>
       </c>
       <c r="E17" s="42">
         <v>45926</v>
@@ -5002,91 +5002,91 @@
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="I22" s="88"/>
-      <c r="J22" s="89"/>
-      <c r="K22" s="89"/>
-      <c r="L22" s="89"/>
-      <c r="M22" s="89"/>
-      <c r="N22" s="89"/>
-      <c r="O22" s="89"/>
-      <c r="P22" s="89"/>
-      <c r="Q22" s="89"/>
-      <c r="R22" s="89"/>
-      <c r="S22" s="89"/>
-      <c r="T22" s="89"/>
-      <c r="U22" s="89"/>
-      <c r="V22" s="89"/>
-      <c r="W22" s="89"/>
-      <c r="X22" s="89"/>
-      <c r="Y22" s="89"/>
-      <c r="Z22" s="89"/>
-      <c r="AA22" s="89"/>
-      <c r="AB22" s="89"/>
-      <c r="AC22" s="89"/>
-      <c r="AD22" s="89"/>
-      <c r="AE22" s="89"/>
-      <c r="AF22" s="89"/>
-      <c r="AG22" s="89"/>
-      <c r="AH22" s="89"/>
-      <c r="AI22" s="89"/>
-      <c r="AJ22" s="89"/>
-      <c r="AK22" s="89"/>
-      <c r="AL22" s="89"/>
-      <c r="AM22" s="89"/>
-      <c r="AN22" s="89"/>
-      <c r="AO22" s="89"/>
-      <c r="AP22" s="89"/>
-      <c r="AQ22" s="89"/>
-      <c r="AR22" s="89"/>
-      <c r="AS22" s="89"/>
-      <c r="AT22" s="89"/>
-      <c r="AU22" s="89"/>
-      <c r="AV22" s="89"/>
-      <c r="AW22" s="89"/>
-      <c r="AX22" s="89"/>
-      <c r="AY22" s="89"/>
-      <c r="AZ22" s="89"/>
-      <c r="BA22" s="89"/>
-      <c r="BB22" s="89"/>
-      <c r="BC22" s="89"/>
-      <c r="BD22" s="89"/>
-      <c r="BE22" s="89"/>
-      <c r="BF22" s="89"/>
-      <c r="BG22" s="89"/>
-      <c r="BH22" s="89"/>
-      <c r="BI22" s="89"/>
-      <c r="BJ22" s="89"/>
-      <c r="BK22" s="89"/>
-      <c r="BL22" s="89"/>
-      <c r="BM22" s="89"/>
-      <c r="BN22" s="89"/>
-      <c r="BO22" s="89"/>
-      <c r="BP22" s="89"/>
-      <c r="BQ22" s="89"/>
-      <c r="BR22" s="89"/>
-      <c r="BS22" s="89"/>
-      <c r="BT22" s="89"/>
-      <c r="BU22" s="89"/>
-      <c r="BV22" s="89"/>
-      <c r="BW22" s="89"/>
-      <c r="BX22" s="89"/>
-      <c r="BY22" s="89"/>
-      <c r="BZ22" s="89"/>
-      <c r="CA22" s="89"/>
-      <c r="CB22" s="89"/>
-      <c r="CC22" s="89"/>
-      <c r="CD22" s="89"/>
-      <c r="CE22" s="89"/>
-      <c r="CF22" s="89"/>
-      <c r="CG22" s="89"/>
-      <c r="CH22" s="89"/>
-      <c r="CI22" s="89"/>
-      <c r="CJ22" s="89"/>
-      <c r="CK22" s="89"/>
-      <c r="CL22" s="89"/>
-      <c r="CM22" s="89"/>
-      <c r="CN22" s="89"/>
-      <c r="CO22" s="89"/>
+      <c r="I22" s="92"/>
+      <c r="J22" s="93"/>
+      <c r="K22" s="93"/>
+      <c r="L22" s="93"/>
+      <c r="M22" s="93"/>
+      <c r="N22" s="93"/>
+      <c r="O22" s="93"/>
+      <c r="P22" s="93"/>
+      <c r="Q22" s="93"/>
+      <c r="R22" s="93"/>
+      <c r="S22" s="93"/>
+      <c r="T22" s="93"/>
+      <c r="U22" s="93"/>
+      <c r="V22" s="93"/>
+      <c r="W22" s="93"/>
+      <c r="X22" s="93"/>
+      <c r="Y22" s="93"/>
+      <c r="Z22" s="93"/>
+      <c r="AA22" s="93"/>
+      <c r="AB22" s="93"/>
+      <c r="AC22" s="93"/>
+      <c r="AD22" s="93"/>
+      <c r="AE22" s="93"/>
+      <c r="AF22" s="93"/>
+      <c r="AG22" s="93"/>
+      <c r="AH22" s="93"/>
+      <c r="AI22" s="93"/>
+      <c r="AJ22" s="93"/>
+      <c r="AK22" s="93"/>
+      <c r="AL22" s="93"/>
+      <c r="AM22" s="93"/>
+      <c r="AN22" s="93"/>
+      <c r="AO22" s="93"/>
+      <c r="AP22" s="93"/>
+      <c r="AQ22" s="93"/>
+      <c r="AR22" s="93"/>
+      <c r="AS22" s="93"/>
+      <c r="AT22" s="93"/>
+      <c r="AU22" s="93"/>
+      <c r="AV22" s="93"/>
+      <c r="AW22" s="93"/>
+      <c r="AX22" s="93"/>
+      <c r="AY22" s="93"/>
+      <c r="AZ22" s="93"/>
+      <c r="BA22" s="93"/>
+      <c r="BB22" s="93"/>
+      <c r="BC22" s="93"/>
+      <c r="BD22" s="93"/>
+      <c r="BE22" s="93"/>
+      <c r="BF22" s="93"/>
+      <c r="BG22" s="93"/>
+      <c r="BH22" s="93"/>
+      <c r="BI22" s="93"/>
+      <c r="BJ22" s="93"/>
+      <c r="BK22" s="93"/>
+      <c r="BL22" s="93"/>
+      <c r="BM22" s="93"/>
+      <c r="BN22" s="93"/>
+      <c r="BO22" s="93"/>
+      <c r="BP22" s="93"/>
+      <c r="BQ22" s="93"/>
+      <c r="BR22" s="93"/>
+      <c r="BS22" s="93"/>
+      <c r="BT22" s="93"/>
+      <c r="BU22" s="93"/>
+      <c r="BV22" s="93"/>
+      <c r="BW22" s="93"/>
+      <c r="BX22" s="93"/>
+      <c r="BY22" s="93"/>
+      <c r="BZ22" s="93"/>
+      <c r="CA22" s="93"/>
+      <c r="CB22" s="93"/>
+      <c r="CC22" s="93"/>
+      <c r="CD22" s="93"/>
+      <c r="CE22" s="93"/>
+      <c r="CF22" s="93"/>
+      <c r="CG22" s="93"/>
+      <c r="CH22" s="93"/>
+      <c r="CI22" s="93"/>
+      <c r="CJ22" s="93"/>
+      <c r="CK22" s="93"/>
+      <c r="CL22" s="93"/>
+      <c r="CM22" s="93"/>
+      <c r="CN22" s="93"/>
+      <c r="CO22" s="93"/>
       <c r="CP22" s="86"/>
       <c r="CQ22"/>
       <c r="CR22"/>
@@ -6788,19 +6788,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="CF3:CJ3"/>
-    <mergeCell ref="CK3:CO3"/>
-    <mergeCell ref="I7:CO7"/>
-    <mergeCell ref="BB3:BF3"/>
-    <mergeCell ref="BG3:BK3"/>
-    <mergeCell ref="BL3:BP3"/>
-    <mergeCell ref="BQ3:BU3"/>
-    <mergeCell ref="BV3:BZ3"/>
-    <mergeCell ref="AC3:AG3"/>
-    <mergeCell ref="AH3:AL3"/>
-    <mergeCell ref="AM3:AQ3"/>
-    <mergeCell ref="AR3:AV3"/>
-    <mergeCell ref="AW3:BA3"/>
     <mergeCell ref="I22:CO22"/>
     <mergeCell ref="I14:CO14"/>
     <mergeCell ref="C2:D2"/>
@@ -6817,6 +6804,19 @@
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="CA3:CE3"/>
+    <mergeCell ref="CF3:CJ3"/>
+    <mergeCell ref="CK3:CO3"/>
+    <mergeCell ref="I7:CO7"/>
+    <mergeCell ref="BB3:BF3"/>
+    <mergeCell ref="BG3:BK3"/>
+    <mergeCell ref="BL3:BP3"/>
+    <mergeCell ref="BQ3:BU3"/>
+    <mergeCell ref="BV3:BZ3"/>
+    <mergeCell ref="AC3:AG3"/>
+    <mergeCell ref="AH3:AL3"/>
+    <mergeCell ref="AM3:AQ3"/>
+    <mergeCell ref="AR3:AV3"/>
+    <mergeCell ref="AW3:BA3"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D35">
     <cfRule type="dataBar" priority="17">
@@ -7191,15 +7191,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
@@ -7217,6 +7208,15 @@
     <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7241,14 +7241,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -7258,4 +7250,12 @@
     <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Capstone/Fase 1/Grupales/Carta Gantt.xlsx
+++ b/Capstone/Fase 1/Grupales/Carta Gantt.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF7B829F-2271-4064-9E93-AFEFBB24DB9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5602A59B-C963-41E5-8259-2A8CD39AEB17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Carta Gatt" sheetId="11" r:id="rId1"/>
@@ -1303,6 +1303,39 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="41" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="8">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="8" applyBorder="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="8" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="8" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="3" xfId="9">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="12" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="169" fontId="0" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1314,39 +1347,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="42" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="8">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="8" applyBorder="1">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="8" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="8" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="3" xfId="9">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="12" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -2038,164 +2038,164 @@
         <v>1</v>
       </c>
       <c r="B2" s="28"/>
-      <c r="C2" s="97" t="s">
+      <c r="C2" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="98"/>
-      <c r="E2" s="101">
+      <c r="D2" s="94"/>
+      <c r="E2" s="97">
         <f>DATE(2025,8,12)</f>
         <v>45881</v>
       </c>
-      <c r="F2" s="101"/>
+      <c r="F2" s="97"/>
     </row>
     <row r="3" spans="1:121" s="26" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="99" t="s">
+      <c r="C3" s="95" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="100"/>
+      <c r="D3" s="96"/>
       <c r="E3" s="61">
         <v>1</v>
       </c>
       <c r="H3" s="62"/>
-      <c r="I3" s="88">
+      <c r="I3" s="99">
         <f>I4</f>
         <v>45880</v>
       </c>
-      <c r="J3" s="88"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="88"/>
-      <c r="M3" s="88"/>
-      <c r="N3" s="88">
+      <c r="J3" s="99"/>
+      <c r="K3" s="99"/>
+      <c r="L3" s="99"/>
+      <c r="M3" s="99"/>
+      <c r="N3" s="99">
         <f>N4</f>
         <v>45887</v>
       </c>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88">
+      <c r="O3" s="99"/>
+      <c r="P3" s="99"/>
+      <c r="Q3" s="99"/>
+      <c r="R3" s="99"/>
+      <c r="S3" s="99">
         <f>S4</f>
         <v>45894</v>
       </c>
-      <c r="T3" s="88"/>
-      <c r="U3" s="88"/>
-      <c r="V3" s="88"/>
-      <c r="W3" s="88"/>
-      <c r="X3" s="88">
+      <c r="T3" s="99"/>
+      <c r="U3" s="99"/>
+      <c r="V3" s="99"/>
+      <c r="W3" s="99"/>
+      <c r="X3" s="99">
         <f>X4</f>
         <v>45901</v>
       </c>
-      <c r="Y3" s="88"/>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="88"/>
-      <c r="AB3" s="88"/>
-      <c r="AC3" s="88">
+      <c r="Y3" s="99"/>
+      <c r="Z3" s="99"/>
+      <c r="AA3" s="99"/>
+      <c r="AB3" s="99"/>
+      <c r="AC3" s="99">
         <f t="shared" ref="AC3" si="0">AC4</f>
         <v>45908</v>
       </c>
-      <c r="AD3" s="88"/>
-      <c r="AE3" s="88"/>
-      <c r="AF3" s="88"/>
-      <c r="AG3" s="88"/>
-      <c r="AH3" s="88">
+      <c r="AD3" s="99"/>
+      <c r="AE3" s="99"/>
+      <c r="AF3" s="99"/>
+      <c r="AG3" s="99"/>
+      <c r="AH3" s="99">
         <f t="shared" ref="AH3" si="1">AH4</f>
         <v>45915</v>
       </c>
-      <c r="AI3" s="88"/>
-      <c r="AJ3" s="88"/>
-      <c r="AK3" s="88"/>
-      <c r="AL3" s="88"/>
-      <c r="AM3" s="88">
+      <c r="AI3" s="99"/>
+      <c r="AJ3" s="99"/>
+      <c r="AK3" s="99"/>
+      <c r="AL3" s="99"/>
+      <c r="AM3" s="99">
         <f t="shared" ref="AM3" si="2">AM4</f>
         <v>45922</v>
       </c>
-      <c r="AN3" s="88"/>
-      <c r="AO3" s="88"/>
-      <c r="AP3" s="88"/>
-      <c r="AQ3" s="88"/>
-      <c r="AR3" s="88">
+      <c r="AN3" s="99"/>
+      <c r="AO3" s="99"/>
+      <c r="AP3" s="99"/>
+      <c r="AQ3" s="99"/>
+      <c r="AR3" s="99">
         <f>AR4</f>
         <v>45929</v>
       </c>
-      <c r="AS3" s="88"/>
-      <c r="AT3" s="88"/>
-      <c r="AU3" s="88"/>
-      <c r="AV3" s="88"/>
-      <c r="AW3" s="88">
+      <c r="AS3" s="99"/>
+      <c r="AT3" s="99"/>
+      <c r="AU3" s="99"/>
+      <c r="AV3" s="99"/>
+      <c r="AW3" s="99">
         <f t="shared" ref="AW3" si="3">AW4</f>
         <v>45936</v>
       </c>
-      <c r="AX3" s="88"/>
-      <c r="AY3" s="88"/>
-      <c r="AZ3" s="88"/>
-      <c r="BA3" s="88"/>
-      <c r="BB3" s="88">
+      <c r="AX3" s="99"/>
+      <c r="AY3" s="99"/>
+      <c r="AZ3" s="99"/>
+      <c r="BA3" s="99"/>
+      <c r="BB3" s="99">
         <f t="shared" ref="BB3" si="4">BB4</f>
         <v>45943</v>
       </c>
-      <c r="BC3" s="88"/>
-      <c r="BD3" s="88"/>
-      <c r="BE3" s="88"/>
-      <c r="BF3" s="88"/>
-      <c r="BG3" s="88">
+      <c r="BC3" s="99"/>
+      <c r="BD3" s="99"/>
+      <c r="BE3" s="99"/>
+      <c r="BF3" s="99"/>
+      <c r="BG3" s="99">
         <f t="shared" ref="BG3" si="5">BG4</f>
         <v>45950</v>
       </c>
-      <c r="BH3" s="88"/>
-      <c r="BI3" s="88"/>
-      <c r="BJ3" s="88"/>
-      <c r="BK3" s="88"/>
-      <c r="BL3" s="88">
+      <c r="BH3" s="99"/>
+      <c r="BI3" s="99"/>
+      <c r="BJ3" s="99"/>
+      <c r="BK3" s="99"/>
+      <c r="BL3" s="99">
         <f t="shared" ref="BL3" si="6">BL4</f>
         <v>45957</v>
       </c>
-      <c r="BM3" s="88"/>
-      <c r="BN3" s="88"/>
-      <c r="BO3" s="88"/>
-      <c r="BP3" s="88"/>
-      <c r="BQ3" s="88">
+      <c r="BM3" s="99"/>
+      <c r="BN3" s="99"/>
+      <c r="BO3" s="99"/>
+      <c r="BP3" s="99"/>
+      <c r="BQ3" s="99">
         <f t="shared" ref="BQ3" si="7">BQ4</f>
         <v>45964</v>
       </c>
-      <c r="BR3" s="88"/>
-      <c r="BS3" s="88"/>
-      <c r="BT3" s="88"/>
-      <c r="BU3" s="88"/>
-      <c r="BV3" s="88">
+      <c r="BR3" s="99"/>
+      <c r="BS3" s="99"/>
+      <c r="BT3" s="99"/>
+      <c r="BU3" s="99"/>
+      <c r="BV3" s="99">
         <f t="shared" ref="BV3" si="8">BV4</f>
         <v>45971</v>
       </c>
-      <c r="BW3" s="88"/>
-      <c r="BX3" s="88"/>
-      <c r="BY3" s="88"/>
-      <c r="BZ3" s="88"/>
-      <c r="CA3" s="88">
+      <c r="BW3" s="99"/>
+      <c r="BX3" s="99"/>
+      <c r="BY3" s="99"/>
+      <c r="BZ3" s="99"/>
+      <c r="CA3" s="99">
         <f t="shared" ref="CA3" si="9">CA4</f>
         <v>45978</v>
       </c>
-      <c r="CB3" s="88"/>
-      <c r="CC3" s="88"/>
-      <c r="CD3" s="88"/>
-      <c r="CE3" s="88"/>
-      <c r="CF3" s="88">
+      <c r="CB3" s="99"/>
+      <c r="CC3" s="99"/>
+      <c r="CD3" s="99"/>
+      <c r="CE3" s="99"/>
+      <c r="CF3" s="99">
         <f t="shared" ref="CF3" si="10">CF4</f>
         <v>45985</v>
       </c>
-      <c r="CG3" s="88"/>
-      <c r="CH3" s="88"/>
-      <c r="CI3" s="88"/>
-      <c r="CJ3" s="88"/>
-      <c r="CK3" s="88">
+      <c r="CG3" s="99"/>
+      <c r="CH3" s="99"/>
+      <c r="CI3" s="99"/>
+      <c r="CJ3" s="99"/>
+      <c r="CK3" s="99">
         <f t="shared" ref="CK3" si="11">CK4</f>
         <v>45992</v>
       </c>
-      <c r="CL3" s="88"/>
-      <c r="CM3" s="88"/>
-      <c r="CN3" s="88"/>
-      <c r="CO3" s="89"/>
+      <c r="CL3" s="99"/>
+      <c r="CM3" s="99"/>
+      <c r="CN3" s="99"/>
+      <c r="CO3" s="100"/>
       <c r="CP3" s="84"/>
       <c r="CQ3" s="74"/>
       <c r="CR3" s="74"/>
@@ -3030,91 +3030,91 @@
         <f t="shared" ref="H7:H28" si="25">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v/>
       </c>
-      <c r="I7" s="90"/>
-      <c r="J7" s="91"/>
-      <c r="K7" s="91"/>
-      <c r="L7" s="91"/>
-      <c r="M7" s="91"/>
-      <c r="N7" s="91"/>
-      <c r="O7" s="91"/>
-      <c r="P7" s="91"/>
-      <c r="Q7" s="91"/>
-      <c r="R7" s="91"/>
-      <c r="S7" s="91"/>
-      <c r="T7" s="91"/>
-      <c r="U7" s="91"/>
-      <c r="V7" s="91"/>
-      <c r="W7" s="91"/>
-      <c r="X7" s="91"/>
-      <c r="Y7" s="91"/>
-      <c r="Z7" s="91"/>
-      <c r="AA7" s="91"/>
-      <c r="AB7" s="91"/>
-      <c r="AC7" s="91"/>
-      <c r="AD7" s="91"/>
-      <c r="AE7" s="91"/>
-      <c r="AF7" s="91"/>
-      <c r="AG7" s="91"/>
-      <c r="AH7" s="91"/>
-      <c r="AI7" s="91"/>
-      <c r="AJ7" s="91"/>
-      <c r="AK7" s="91"/>
-      <c r="AL7" s="91"/>
-      <c r="AM7" s="91"/>
-      <c r="AN7" s="91"/>
-      <c r="AO7" s="91"/>
-      <c r="AP7" s="91"/>
-      <c r="AQ7" s="91"/>
-      <c r="AR7" s="91"/>
-      <c r="AS7" s="91"/>
-      <c r="AT7" s="91"/>
-      <c r="AU7" s="91"/>
-      <c r="AV7" s="91"/>
-      <c r="AW7" s="91"/>
-      <c r="AX7" s="91"/>
-      <c r="AY7" s="91"/>
-      <c r="AZ7" s="91"/>
-      <c r="BA7" s="91"/>
-      <c r="BB7" s="91"/>
-      <c r="BC7" s="91"/>
-      <c r="BD7" s="91"/>
-      <c r="BE7" s="91"/>
-      <c r="BF7" s="91"/>
-      <c r="BG7" s="91"/>
-      <c r="BH7" s="91"/>
-      <c r="BI7" s="91"/>
-      <c r="BJ7" s="91"/>
-      <c r="BK7" s="91"/>
-      <c r="BL7" s="91"/>
-      <c r="BM7" s="91"/>
-      <c r="BN7" s="91"/>
-      <c r="BO7" s="91"/>
-      <c r="BP7" s="91"/>
-      <c r="BQ7" s="91"/>
-      <c r="BR7" s="91"/>
-      <c r="BS7" s="91"/>
-      <c r="BT7" s="91"/>
-      <c r="BU7" s="91"/>
-      <c r="BV7" s="91"/>
-      <c r="BW7" s="91"/>
-      <c r="BX7" s="91"/>
-      <c r="BY7" s="91"/>
-      <c r="BZ7" s="91"/>
-      <c r="CA7" s="91"/>
-      <c r="CB7" s="91"/>
-      <c r="CC7" s="91"/>
-      <c r="CD7" s="91"/>
-      <c r="CE7" s="91"/>
-      <c r="CF7" s="91"/>
-      <c r="CG7" s="91"/>
-      <c r="CH7" s="91"/>
-      <c r="CI7" s="91"/>
-      <c r="CJ7" s="91"/>
-      <c r="CK7" s="91"/>
-      <c r="CL7" s="91"/>
-      <c r="CM7" s="91"/>
-      <c r="CN7" s="91"/>
-      <c r="CO7" s="91"/>
+      <c r="I7" s="101"/>
+      <c r="J7" s="102"/>
+      <c r="K7" s="102"/>
+      <c r="L7" s="102"/>
+      <c r="M7" s="102"/>
+      <c r="N7" s="102"/>
+      <c r="O7" s="102"/>
+      <c r="P7" s="102"/>
+      <c r="Q7" s="102"/>
+      <c r="R7" s="102"/>
+      <c r="S7" s="102"/>
+      <c r="T7" s="102"/>
+      <c r="U7" s="102"/>
+      <c r="V7" s="102"/>
+      <c r="W7" s="102"/>
+      <c r="X7" s="102"/>
+      <c r="Y7" s="102"/>
+      <c r="Z7" s="102"/>
+      <c r="AA7" s="102"/>
+      <c r="AB7" s="102"/>
+      <c r="AC7" s="102"/>
+      <c r="AD7" s="102"/>
+      <c r="AE7" s="102"/>
+      <c r="AF7" s="102"/>
+      <c r="AG7" s="102"/>
+      <c r="AH7" s="102"/>
+      <c r="AI7" s="102"/>
+      <c r="AJ7" s="102"/>
+      <c r="AK7" s="102"/>
+      <c r="AL7" s="102"/>
+      <c r="AM7" s="102"/>
+      <c r="AN7" s="102"/>
+      <c r="AO7" s="102"/>
+      <c r="AP7" s="102"/>
+      <c r="AQ7" s="102"/>
+      <c r="AR7" s="102"/>
+      <c r="AS7" s="102"/>
+      <c r="AT7" s="102"/>
+      <c r="AU7" s="102"/>
+      <c r="AV7" s="102"/>
+      <c r="AW7" s="102"/>
+      <c r="AX7" s="102"/>
+      <c r="AY7" s="102"/>
+      <c r="AZ7" s="102"/>
+      <c r="BA7" s="102"/>
+      <c r="BB7" s="102"/>
+      <c r="BC7" s="102"/>
+      <c r="BD7" s="102"/>
+      <c r="BE7" s="102"/>
+      <c r="BF7" s="102"/>
+      <c r="BG7" s="102"/>
+      <c r="BH7" s="102"/>
+      <c r="BI7" s="102"/>
+      <c r="BJ7" s="102"/>
+      <c r="BK7" s="102"/>
+      <c r="BL7" s="102"/>
+      <c r="BM7" s="102"/>
+      <c r="BN7" s="102"/>
+      <c r="BO7" s="102"/>
+      <c r="BP7" s="102"/>
+      <c r="BQ7" s="102"/>
+      <c r="BR7" s="102"/>
+      <c r="BS7" s="102"/>
+      <c r="BT7" s="102"/>
+      <c r="BU7" s="102"/>
+      <c r="BV7" s="102"/>
+      <c r="BW7" s="102"/>
+      <c r="BX7" s="102"/>
+      <c r="BY7" s="102"/>
+      <c r="BZ7" s="102"/>
+      <c r="CA7" s="102"/>
+      <c r="CB7" s="102"/>
+      <c r="CC7" s="102"/>
+      <c r="CD7" s="102"/>
+      <c r="CE7" s="102"/>
+      <c r="CF7" s="102"/>
+      <c r="CG7" s="102"/>
+      <c r="CH7" s="102"/>
+      <c r="CI7" s="102"/>
+      <c r="CJ7" s="102"/>
+      <c r="CK7" s="102"/>
+      <c r="CL7" s="102"/>
+      <c r="CM7" s="102"/>
+      <c r="CN7" s="102"/>
+      <c r="CO7" s="102"/>
       <c r="CP7" s="87"/>
       <c r="CQ7" s="78"/>
       <c r="CR7" s="78"/>
@@ -3148,10 +3148,10 @@
       <c r="A8" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="102" t="s">
+      <c r="B8" s="98" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="102"/>
+      <c r="C8" s="98"/>
       <c r="D8" s="13">
         <v>1</v>
       </c>
@@ -3282,10 +3282,10 @@
     </row>
     <row r="9" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="24"/>
-      <c r="B9" s="102" t="s">
+      <c r="B9" s="98" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="102"/>
+      <c r="C9" s="98"/>
       <c r="D9" s="13">
         <v>1</v>
       </c>
@@ -3413,10 +3413,10 @@
     </row>
     <row r="10" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="23"/>
-      <c r="B10" s="102" t="s">
+      <c r="B10" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="102"/>
+      <c r="C10" s="98"/>
       <c r="D10" s="13">
         <v>1</v>
       </c>
@@ -3547,10 +3547,10 @@
     </row>
     <row r="11" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="23"/>
-      <c r="B11" s="102" t="s">
+      <c r="B11" s="98" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="102"/>
+      <c r="C11" s="98"/>
       <c r="D11" s="13">
         <v>1</v>
       </c>
@@ -3678,10 +3678,10 @@
     </row>
     <row r="12" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="23"/>
-      <c r="B12" s="102" t="s">
+      <c r="B12" s="98" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="102"/>
+      <c r="C12" s="98"/>
       <c r="D12" s="13">
         <v>1</v>
       </c>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="13" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="23"/>
-      <c r="B13" s="102" t="s">
+      <c r="B13" s="98" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="102"/>
+      <c r="C13" s="98"/>
       <c r="D13" s="13">
         <v>1</v>
       </c>
@@ -3955,91 +3955,91 @@
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="I14" s="94"/>
-      <c r="J14" s="95"/>
-      <c r="K14" s="95"/>
-      <c r="L14" s="95"/>
-      <c r="M14" s="95"/>
-      <c r="N14" s="95"/>
-      <c r="O14" s="95"/>
-      <c r="P14" s="95"/>
-      <c r="Q14" s="95"/>
-      <c r="R14" s="95"/>
-      <c r="S14" s="95"/>
-      <c r="T14" s="95"/>
-      <c r="U14" s="95"/>
-      <c r="V14" s="95"/>
-      <c r="W14" s="95"/>
-      <c r="X14" s="95"/>
-      <c r="Y14" s="95"/>
-      <c r="Z14" s="95"/>
-      <c r="AA14" s="95"/>
-      <c r="AB14" s="95"/>
-      <c r="AC14" s="95"/>
-      <c r="AD14" s="95"/>
-      <c r="AE14" s="95"/>
-      <c r="AF14" s="95"/>
-      <c r="AG14" s="95"/>
-      <c r="AH14" s="95"/>
-      <c r="AI14" s="95"/>
-      <c r="AJ14" s="95"/>
-      <c r="AK14" s="95"/>
-      <c r="AL14" s="95"/>
-      <c r="AM14" s="95"/>
-      <c r="AN14" s="95"/>
-      <c r="AO14" s="95"/>
-      <c r="AP14" s="95"/>
-      <c r="AQ14" s="95"/>
-      <c r="AR14" s="95"/>
-      <c r="AS14" s="95"/>
-      <c r="AT14" s="95"/>
-      <c r="AU14" s="95"/>
-      <c r="AV14" s="95"/>
-      <c r="AW14" s="95"/>
-      <c r="AX14" s="95"/>
-      <c r="AY14" s="95"/>
-      <c r="AZ14" s="95"/>
-      <c r="BA14" s="95"/>
-      <c r="BB14" s="95"/>
-      <c r="BC14" s="95"/>
-      <c r="BD14" s="95"/>
-      <c r="BE14" s="95"/>
-      <c r="BF14" s="95"/>
-      <c r="BG14" s="95"/>
-      <c r="BH14" s="95"/>
-      <c r="BI14" s="95"/>
-      <c r="BJ14" s="95"/>
-      <c r="BK14" s="95"/>
-      <c r="BL14" s="95"/>
-      <c r="BM14" s="95"/>
-      <c r="BN14" s="95"/>
-      <c r="BO14" s="95"/>
-      <c r="BP14" s="95"/>
-      <c r="BQ14" s="95"/>
-      <c r="BR14" s="95"/>
-      <c r="BS14" s="95"/>
-      <c r="BT14" s="95"/>
-      <c r="BU14" s="95"/>
-      <c r="BV14" s="95"/>
-      <c r="BW14" s="95"/>
-      <c r="BX14" s="95"/>
-      <c r="BY14" s="95"/>
-      <c r="BZ14" s="95"/>
-      <c r="CA14" s="95"/>
-      <c r="CB14" s="95"/>
-      <c r="CC14" s="95"/>
-      <c r="CD14" s="95"/>
-      <c r="CE14" s="95"/>
-      <c r="CF14" s="95"/>
-      <c r="CG14" s="95"/>
-      <c r="CH14" s="95"/>
-      <c r="CI14" s="95"/>
-      <c r="CJ14" s="95"/>
-      <c r="CK14" s="95"/>
-      <c r="CL14" s="95"/>
-      <c r="CM14" s="95"/>
-      <c r="CN14" s="95"/>
-      <c r="CO14" s="96"/>
+      <c r="I14" s="90"/>
+      <c r="J14" s="91"/>
+      <c r="K14" s="91"/>
+      <c r="L14" s="91"/>
+      <c r="M14" s="91"/>
+      <c r="N14" s="91"/>
+      <c r="O14" s="91"/>
+      <c r="P14" s="91"/>
+      <c r="Q14" s="91"/>
+      <c r="R14" s="91"/>
+      <c r="S14" s="91"/>
+      <c r="T14" s="91"/>
+      <c r="U14" s="91"/>
+      <c r="V14" s="91"/>
+      <c r="W14" s="91"/>
+      <c r="X14" s="91"/>
+      <c r="Y14" s="91"/>
+      <c r="Z14" s="91"/>
+      <c r="AA14" s="91"/>
+      <c r="AB14" s="91"/>
+      <c r="AC14" s="91"/>
+      <c r="AD14" s="91"/>
+      <c r="AE14" s="91"/>
+      <c r="AF14" s="91"/>
+      <c r="AG14" s="91"/>
+      <c r="AH14" s="91"/>
+      <c r="AI14" s="91"/>
+      <c r="AJ14" s="91"/>
+      <c r="AK14" s="91"/>
+      <c r="AL14" s="91"/>
+      <c r="AM14" s="91"/>
+      <c r="AN14" s="91"/>
+      <c r="AO14" s="91"/>
+      <c r="AP14" s="91"/>
+      <c r="AQ14" s="91"/>
+      <c r="AR14" s="91"/>
+      <c r="AS14" s="91"/>
+      <c r="AT14" s="91"/>
+      <c r="AU14" s="91"/>
+      <c r="AV14" s="91"/>
+      <c r="AW14" s="91"/>
+      <c r="AX14" s="91"/>
+      <c r="AY14" s="91"/>
+      <c r="AZ14" s="91"/>
+      <c r="BA14" s="91"/>
+      <c r="BB14" s="91"/>
+      <c r="BC14" s="91"/>
+      <c r="BD14" s="91"/>
+      <c r="BE14" s="91"/>
+      <c r="BF14" s="91"/>
+      <c r="BG14" s="91"/>
+      <c r="BH14" s="91"/>
+      <c r="BI14" s="91"/>
+      <c r="BJ14" s="91"/>
+      <c r="BK14" s="91"/>
+      <c r="BL14" s="91"/>
+      <c r="BM14" s="91"/>
+      <c r="BN14" s="91"/>
+      <c r="BO14" s="91"/>
+      <c r="BP14" s="91"/>
+      <c r="BQ14" s="91"/>
+      <c r="BR14" s="91"/>
+      <c r="BS14" s="91"/>
+      <c r="BT14" s="91"/>
+      <c r="BU14" s="91"/>
+      <c r="BV14" s="91"/>
+      <c r="BW14" s="91"/>
+      <c r="BX14" s="91"/>
+      <c r="BY14" s="91"/>
+      <c r="BZ14" s="91"/>
+      <c r="CA14" s="91"/>
+      <c r="CB14" s="91"/>
+      <c r="CC14" s="91"/>
+      <c r="CD14" s="91"/>
+      <c r="CE14" s="91"/>
+      <c r="CF14" s="91"/>
+      <c r="CG14" s="91"/>
+      <c r="CH14" s="91"/>
+      <c r="CI14" s="91"/>
+      <c r="CJ14" s="91"/>
+      <c r="CK14" s="91"/>
+      <c r="CL14" s="91"/>
+      <c r="CM14" s="91"/>
+      <c r="CN14" s="91"/>
+      <c r="CO14" s="92"/>
       <c r="CP14" s="86"/>
       <c r="CQ14"/>
       <c r="CR14"/>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="C16" s="30"/>
       <c r="D16" s="16">
-        <v>0.3</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="E16" s="42">
         <v>45922</v>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="C17" s="30"/>
       <c r="D17" s="16">
-        <v>0.6</v>
+        <v>0.85</v>
       </c>
       <c r="E17" s="42">
         <v>45926</v>
@@ -5002,91 +5002,91 @@
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="I22" s="92"/>
-      <c r="J22" s="93"/>
-      <c r="K22" s="93"/>
-      <c r="L22" s="93"/>
-      <c r="M22" s="93"/>
-      <c r="N22" s="93"/>
-      <c r="O22" s="93"/>
-      <c r="P22" s="93"/>
-      <c r="Q22" s="93"/>
-      <c r="R22" s="93"/>
-      <c r="S22" s="93"/>
-      <c r="T22" s="93"/>
-      <c r="U22" s="93"/>
-      <c r="V22" s="93"/>
-      <c r="W22" s="93"/>
-      <c r="X22" s="93"/>
-      <c r="Y22" s="93"/>
-      <c r="Z22" s="93"/>
-      <c r="AA22" s="93"/>
-      <c r="AB22" s="93"/>
-      <c r="AC22" s="93"/>
-      <c r="AD22" s="93"/>
-      <c r="AE22" s="93"/>
-      <c r="AF22" s="93"/>
-      <c r="AG22" s="93"/>
-      <c r="AH22" s="93"/>
-      <c r="AI22" s="93"/>
-      <c r="AJ22" s="93"/>
-      <c r="AK22" s="93"/>
-      <c r="AL22" s="93"/>
-      <c r="AM22" s="93"/>
-      <c r="AN22" s="93"/>
-      <c r="AO22" s="93"/>
-      <c r="AP22" s="93"/>
-      <c r="AQ22" s="93"/>
-      <c r="AR22" s="93"/>
-      <c r="AS22" s="93"/>
-      <c r="AT22" s="93"/>
-      <c r="AU22" s="93"/>
-      <c r="AV22" s="93"/>
-      <c r="AW22" s="93"/>
-      <c r="AX22" s="93"/>
-      <c r="AY22" s="93"/>
-      <c r="AZ22" s="93"/>
-      <c r="BA22" s="93"/>
-      <c r="BB22" s="93"/>
-      <c r="BC22" s="93"/>
-      <c r="BD22" s="93"/>
-      <c r="BE22" s="93"/>
-      <c r="BF22" s="93"/>
-      <c r="BG22" s="93"/>
-      <c r="BH22" s="93"/>
-      <c r="BI22" s="93"/>
-      <c r="BJ22" s="93"/>
-      <c r="BK22" s="93"/>
-      <c r="BL22" s="93"/>
-      <c r="BM22" s="93"/>
-      <c r="BN22" s="93"/>
-      <c r="BO22" s="93"/>
-      <c r="BP22" s="93"/>
-      <c r="BQ22" s="93"/>
-      <c r="BR22" s="93"/>
-      <c r="BS22" s="93"/>
-      <c r="BT22" s="93"/>
-      <c r="BU22" s="93"/>
-      <c r="BV22" s="93"/>
-      <c r="BW22" s="93"/>
-      <c r="BX22" s="93"/>
-      <c r="BY22" s="93"/>
-      <c r="BZ22" s="93"/>
-      <c r="CA22" s="93"/>
-      <c r="CB22" s="93"/>
-      <c r="CC22" s="93"/>
-      <c r="CD22" s="93"/>
-      <c r="CE22" s="93"/>
-      <c r="CF22" s="93"/>
-      <c r="CG22" s="93"/>
-      <c r="CH22" s="93"/>
-      <c r="CI22" s="93"/>
-      <c r="CJ22" s="93"/>
-      <c r="CK22" s="93"/>
-      <c r="CL22" s="93"/>
-      <c r="CM22" s="93"/>
-      <c r="CN22" s="93"/>
-      <c r="CO22" s="93"/>
+      <c r="I22" s="88"/>
+      <c r="J22" s="89"/>
+      <c r="K22" s="89"/>
+      <c r="L22" s="89"/>
+      <c r="M22" s="89"/>
+      <c r="N22" s="89"/>
+      <c r="O22" s="89"/>
+      <c r="P22" s="89"/>
+      <c r="Q22" s="89"/>
+      <c r="R22" s="89"/>
+      <c r="S22" s="89"/>
+      <c r="T22" s="89"/>
+      <c r="U22" s="89"/>
+      <c r="V22" s="89"/>
+      <c r="W22" s="89"/>
+      <c r="X22" s="89"/>
+      <c r="Y22" s="89"/>
+      <c r="Z22" s="89"/>
+      <c r="AA22" s="89"/>
+      <c r="AB22" s="89"/>
+      <c r="AC22" s="89"/>
+      <c r="AD22" s="89"/>
+      <c r="AE22" s="89"/>
+      <c r="AF22" s="89"/>
+      <c r="AG22" s="89"/>
+      <c r="AH22" s="89"/>
+      <c r="AI22" s="89"/>
+      <c r="AJ22" s="89"/>
+      <c r="AK22" s="89"/>
+      <c r="AL22" s="89"/>
+      <c r="AM22" s="89"/>
+      <c r="AN22" s="89"/>
+      <c r="AO22" s="89"/>
+      <c r="AP22" s="89"/>
+      <c r="AQ22" s="89"/>
+      <c r="AR22" s="89"/>
+      <c r="AS22" s="89"/>
+      <c r="AT22" s="89"/>
+      <c r="AU22" s="89"/>
+      <c r="AV22" s="89"/>
+      <c r="AW22" s="89"/>
+      <c r="AX22" s="89"/>
+      <c r="AY22" s="89"/>
+      <c r="AZ22" s="89"/>
+      <c r="BA22" s="89"/>
+      <c r="BB22" s="89"/>
+      <c r="BC22" s="89"/>
+      <c r="BD22" s="89"/>
+      <c r="BE22" s="89"/>
+      <c r="BF22" s="89"/>
+      <c r="BG22" s="89"/>
+      <c r="BH22" s="89"/>
+      <c r="BI22" s="89"/>
+      <c r="BJ22" s="89"/>
+      <c r="BK22" s="89"/>
+      <c r="BL22" s="89"/>
+      <c r="BM22" s="89"/>
+      <c r="BN22" s="89"/>
+      <c r="BO22" s="89"/>
+      <c r="BP22" s="89"/>
+      <c r="BQ22" s="89"/>
+      <c r="BR22" s="89"/>
+      <c r="BS22" s="89"/>
+      <c r="BT22" s="89"/>
+      <c r="BU22" s="89"/>
+      <c r="BV22" s="89"/>
+      <c r="BW22" s="89"/>
+      <c r="BX22" s="89"/>
+      <c r="BY22" s="89"/>
+      <c r="BZ22" s="89"/>
+      <c r="CA22" s="89"/>
+      <c r="CB22" s="89"/>
+      <c r="CC22" s="89"/>
+      <c r="CD22" s="89"/>
+      <c r="CE22" s="89"/>
+      <c r="CF22" s="89"/>
+      <c r="CG22" s="89"/>
+      <c r="CH22" s="89"/>
+      <c r="CI22" s="89"/>
+      <c r="CJ22" s="89"/>
+      <c r="CK22" s="89"/>
+      <c r="CL22" s="89"/>
+      <c r="CM22" s="89"/>
+      <c r="CN22" s="89"/>
+      <c r="CO22" s="89"/>
       <c r="CP22" s="86"/>
       <c r="CQ22"/>
       <c r="CR22"/>
@@ -6788,6 +6788,19 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="CF3:CJ3"/>
+    <mergeCell ref="CK3:CO3"/>
+    <mergeCell ref="I7:CO7"/>
+    <mergeCell ref="BB3:BF3"/>
+    <mergeCell ref="BG3:BK3"/>
+    <mergeCell ref="BL3:BP3"/>
+    <mergeCell ref="BQ3:BU3"/>
+    <mergeCell ref="BV3:BZ3"/>
+    <mergeCell ref="AC3:AG3"/>
+    <mergeCell ref="AH3:AL3"/>
+    <mergeCell ref="AM3:AQ3"/>
+    <mergeCell ref="AR3:AV3"/>
+    <mergeCell ref="AW3:BA3"/>
     <mergeCell ref="I22:CO22"/>
     <mergeCell ref="I14:CO14"/>
     <mergeCell ref="C2:D2"/>
@@ -6804,19 +6817,6 @@
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="CA3:CE3"/>
-    <mergeCell ref="CF3:CJ3"/>
-    <mergeCell ref="CK3:CO3"/>
-    <mergeCell ref="I7:CO7"/>
-    <mergeCell ref="BB3:BF3"/>
-    <mergeCell ref="BG3:BK3"/>
-    <mergeCell ref="BL3:BP3"/>
-    <mergeCell ref="BQ3:BU3"/>
-    <mergeCell ref="BV3:BZ3"/>
-    <mergeCell ref="AC3:AG3"/>
-    <mergeCell ref="AH3:AL3"/>
-    <mergeCell ref="AM3:AQ3"/>
-    <mergeCell ref="AR3:AV3"/>
-    <mergeCell ref="AW3:BA3"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D35">
     <cfRule type="dataBar" priority="17">
@@ -7191,6 +7191,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
@@ -7208,15 +7217,6 @@
     <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7241,6 +7241,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -7250,12 +7258,4 @@
     <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Capstone/Fase 1/Grupales/Carta Gantt.xlsx
+++ b/Capstone/Fase 1/Grupales/Carta Gantt.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5602A59B-C963-41E5-8259-2A8CD39AEB17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{876B3C3D-515C-4E43-95BF-FD300A8C7BDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1303,6 +1303,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="41" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="42" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="42" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1335,18 +1347,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="12" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="42" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="42" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -2038,164 +2038,164 @@
         <v>1</v>
       </c>
       <c r="B2" s="28"/>
-      <c r="C2" s="93" t="s">
+      <c r="C2" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="94"/>
-      <c r="E2" s="97">
+      <c r="D2" s="98"/>
+      <c r="E2" s="101">
         <f>DATE(2025,8,12)</f>
         <v>45881</v>
       </c>
-      <c r="F2" s="97"/>
+      <c r="F2" s="101"/>
     </row>
     <row r="3" spans="1:121" s="26" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="95" t="s">
+      <c r="C3" s="99" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="96"/>
+      <c r="D3" s="100"/>
       <c r="E3" s="61">
         <v>1</v>
       </c>
       <c r="H3" s="62"/>
-      <c r="I3" s="99">
+      <c r="I3" s="88">
         <f>I4</f>
         <v>45880</v>
       </c>
-      <c r="J3" s="99"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="99"/>
-      <c r="M3" s="99"/>
-      <c r="N3" s="99">
+      <c r="J3" s="88"/>
+      <c r="K3" s="88"/>
+      <c r="L3" s="88"/>
+      <c r="M3" s="88"/>
+      <c r="N3" s="88">
         <f>N4</f>
         <v>45887</v>
       </c>
-      <c r="O3" s="99"/>
-      <c r="P3" s="99"/>
-      <c r="Q3" s="99"/>
-      <c r="R3" s="99"/>
-      <c r="S3" s="99">
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88">
         <f>S4</f>
         <v>45894</v>
       </c>
-      <c r="T3" s="99"/>
-      <c r="U3" s="99"/>
-      <c r="V3" s="99"/>
-      <c r="W3" s="99"/>
-      <c r="X3" s="99">
+      <c r="T3" s="88"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="W3" s="88"/>
+      <c r="X3" s="88">
         <f>X4</f>
         <v>45901</v>
       </c>
-      <c r="Y3" s="99"/>
-      <c r="Z3" s="99"/>
-      <c r="AA3" s="99"/>
-      <c r="AB3" s="99"/>
-      <c r="AC3" s="99">
+      <c r="Y3" s="88"/>
+      <c r="Z3" s="88"/>
+      <c r="AA3" s="88"/>
+      <c r="AB3" s="88"/>
+      <c r="AC3" s="88">
         <f t="shared" ref="AC3" si="0">AC4</f>
         <v>45908</v>
       </c>
-      <c r="AD3" s="99"/>
-      <c r="AE3" s="99"/>
-      <c r="AF3" s="99"/>
-      <c r="AG3" s="99"/>
-      <c r="AH3" s="99">
+      <c r="AD3" s="88"/>
+      <c r="AE3" s="88"/>
+      <c r="AF3" s="88"/>
+      <c r="AG3" s="88"/>
+      <c r="AH3" s="88">
         <f t="shared" ref="AH3" si="1">AH4</f>
         <v>45915</v>
       </c>
-      <c r="AI3" s="99"/>
-      <c r="AJ3" s="99"/>
-      <c r="AK3" s="99"/>
-      <c r="AL3" s="99"/>
-      <c r="AM3" s="99">
+      <c r="AI3" s="88"/>
+      <c r="AJ3" s="88"/>
+      <c r="AK3" s="88"/>
+      <c r="AL3" s="88"/>
+      <c r="AM3" s="88">
         <f t="shared" ref="AM3" si="2">AM4</f>
         <v>45922</v>
       </c>
-      <c r="AN3" s="99"/>
-      <c r="AO3" s="99"/>
-      <c r="AP3" s="99"/>
-      <c r="AQ3" s="99"/>
-      <c r="AR3" s="99">
+      <c r="AN3" s="88"/>
+      <c r="AO3" s="88"/>
+      <c r="AP3" s="88"/>
+      <c r="AQ3" s="88"/>
+      <c r="AR3" s="88">
         <f>AR4</f>
         <v>45929</v>
       </c>
-      <c r="AS3" s="99"/>
-      <c r="AT3" s="99"/>
-      <c r="AU3" s="99"/>
-      <c r="AV3" s="99"/>
-      <c r="AW3" s="99">
+      <c r="AS3" s="88"/>
+      <c r="AT3" s="88"/>
+      <c r="AU3" s="88"/>
+      <c r="AV3" s="88"/>
+      <c r="AW3" s="88">
         <f t="shared" ref="AW3" si="3">AW4</f>
         <v>45936</v>
       </c>
-      <c r="AX3" s="99"/>
-      <c r="AY3" s="99"/>
-      <c r="AZ3" s="99"/>
-      <c r="BA3" s="99"/>
-      <c r="BB3" s="99">
+      <c r="AX3" s="88"/>
+      <c r="AY3" s="88"/>
+      <c r="AZ3" s="88"/>
+      <c r="BA3" s="88"/>
+      <c r="BB3" s="88">
         <f t="shared" ref="BB3" si="4">BB4</f>
         <v>45943</v>
       </c>
-      <c r="BC3" s="99"/>
-      <c r="BD3" s="99"/>
-      <c r="BE3" s="99"/>
-      <c r="BF3" s="99"/>
-      <c r="BG3" s="99">
+      <c r="BC3" s="88"/>
+      <c r="BD3" s="88"/>
+      <c r="BE3" s="88"/>
+      <c r="BF3" s="88"/>
+      <c r="BG3" s="88">
         <f t="shared" ref="BG3" si="5">BG4</f>
         <v>45950</v>
       </c>
-      <c r="BH3" s="99"/>
-      <c r="BI3" s="99"/>
-      <c r="BJ3" s="99"/>
-      <c r="BK3" s="99"/>
-      <c r="BL3" s="99">
+      <c r="BH3" s="88"/>
+      <c r="BI3" s="88"/>
+      <c r="BJ3" s="88"/>
+      <c r="BK3" s="88"/>
+      <c r="BL3" s="88">
         <f t="shared" ref="BL3" si="6">BL4</f>
         <v>45957</v>
       </c>
-      <c r="BM3" s="99"/>
-      <c r="BN3" s="99"/>
-      <c r="BO3" s="99"/>
-      <c r="BP3" s="99"/>
-      <c r="BQ3" s="99">
+      <c r="BM3" s="88"/>
+      <c r="BN3" s="88"/>
+      <c r="BO3" s="88"/>
+      <c r="BP3" s="88"/>
+      <c r="BQ3" s="88">
         <f t="shared" ref="BQ3" si="7">BQ4</f>
         <v>45964</v>
       </c>
-      <c r="BR3" s="99"/>
-      <c r="BS3" s="99"/>
-      <c r="BT3" s="99"/>
-      <c r="BU3" s="99"/>
-      <c r="BV3" s="99">
+      <c r="BR3" s="88"/>
+      <c r="BS3" s="88"/>
+      <c r="BT3" s="88"/>
+      <c r="BU3" s="88"/>
+      <c r="BV3" s="88">
         <f t="shared" ref="BV3" si="8">BV4</f>
         <v>45971</v>
       </c>
-      <c r="BW3" s="99"/>
-      <c r="BX3" s="99"/>
-      <c r="BY3" s="99"/>
-      <c r="BZ3" s="99"/>
-      <c r="CA3" s="99">
+      <c r="BW3" s="88"/>
+      <c r="BX3" s="88"/>
+      <c r="BY3" s="88"/>
+      <c r="BZ3" s="88"/>
+      <c r="CA3" s="88">
         <f t="shared" ref="CA3" si="9">CA4</f>
         <v>45978</v>
       </c>
-      <c r="CB3" s="99"/>
-      <c r="CC3" s="99"/>
-      <c r="CD3" s="99"/>
-      <c r="CE3" s="99"/>
-      <c r="CF3" s="99">
+      <c r="CB3" s="88"/>
+      <c r="CC3" s="88"/>
+      <c r="CD3" s="88"/>
+      <c r="CE3" s="88"/>
+      <c r="CF3" s="88">
         <f t="shared" ref="CF3" si="10">CF4</f>
         <v>45985</v>
       </c>
-      <c r="CG3" s="99"/>
-      <c r="CH3" s="99"/>
-      <c r="CI3" s="99"/>
-      <c r="CJ3" s="99"/>
-      <c r="CK3" s="99">
+      <c r="CG3" s="88"/>
+      <c r="CH3" s="88"/>
+      <c r="CI3" s="88"/>
+      <c r="CJ3" s="88"/>
+      <c r="CK3" s="88">
         <f t="shared" ref="CK3" si="11">CK4</f>
         <v>45992</v>
       </c>
-      <c r="CL3" s="99"/>
-      <c r="CM3" s="99"/>
-      <c r="CN3" s="99"/>
-      <c r="CO3" s="100"/>
+      <c r="CL3" s="88"/>
+      <c r="CM3" s="88"/>
+      <c r="CN3" s="88"/>
+      <c r="CO3" s="89"/>
       <c r="CP3" s="84"/>
       <c r="CQ3" s="74"/>
       <c r="CR3" s="74"/>
@@ -3030,91 +3030,91 @@
         <f t="shared" ref="H7:H28" si="25">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v/>
       </c>
-      <c r="I7" s="101"/>
-      <c r="J7" s="102"/>
-      <c r="K7" s="102"/>
-      <c r="L7" s="102"/>
-      <c r="M7" s="102"/>
-      <c r="N7" s="102"/>
-      <c r="O7" s="102"/>
-      <c r="P7" s="102"/>
-      <c r="Q7" s="102"/>
-      <c r="R7" s="102"/>
-      <c r="S7" s="102"/>
-      <c r="T7" s="102"/>
-      <c r="U7" s="102"/>
-      <c r="V7" s="102"/>
-      <c r="W7" s="102"/>
-      <c r="X7" s="102"/>
-      <c r="Y7" s="102"/>
-      <c r="Z7" s="102"/>
-      <c r="AA7" s="102"/>
-      <c r="AB7" s="102"/>
-      <c r="AC7" s="102"/>
-      <c r="AD7" s="102"/>
-      <c r="AE7" s="102"/>
-      <c r="AF7" s="102"/>
-      <c r="AG7" s="102"/>
-      <c r="AH7" s="102"/>
-      <c r="AI7" s="102"/>
-      <c r="AJ7" s="102"/>
-      <c r="AK7" s="102"/>
-      <c r="AL7" s="102"/>
-      <c r="AM7" s="102"/>
-      <c r="AN7" s="102"/>
-      <c r="AO7" s="102"/>
-      <c r="AP7" s="102"/>
-      <c r="AQ7" s="102"/>
-      <c r="AR7" s="102"/>
-      <c r="AS7" s="102"/>
-      <c r="AT7" s="102"/>
-      <c r="AU7" s="102"/>
-      <c r="AV7" s="102"/>
-      <c r="AW7" s="102"/>
-      <c r="AX7" s="102"/>
-      <c r="AY7" s="102"/>
-      <c r="AZ7" s="102"/>
-      <c r="BA7" s="102"/>
-      <c r="BB7" s="102"/>
-      <c r="BC7" s="102"/>
-      <c r="BD7" s="102"/>
-      <c r="BE7" s="102"/>
-      <c r="BF7" s="102"/>
-      <c r="BG7" s="102"/>
-      <c r="BH7" s="102"/>
-      <c r="BI7" s="102"/>
-      <c r="BJ7" s="102"/>
-      <c r="BK7" s="102"/>
-      <c r="BL7" s="102"/>
-      <c r="BM7" s="102"/>
-      <c r="BN7" s="102"/>
-      <c r="BO7" s="102"/>
-      <c r="BP7" s="102"/>
-      <c r="BQ7" s="102"/>
-      <c r="BR7" s="102"/>
-      <c r="BS7" s="102"/>
-      <c r="BT7" s="102"/>
-      <c r="BU7" s="102"/>
-      <c r="BV7" s="102"/>
-      <c r="BW7" s="102"/>
-      <c r="BX7" s="102"/>
-      <c r="BY7" s="102"/>
-      <c r="BZ7" s="102"/>
-      <c r="CA7" s="102"/>
-      <c r="CB7" s="102"/>
-      <c r="CC7" s="102"/>
-      <c r="CD7" s="102"/>
-      <c r="CE7" s="102"/>
-      <c r="CF7" s="102"/>
-      <c r="CG7" s="102"/>
-      <c r="CH7" s="102"/>
-      <c r="CI7" s="102"/>
-      <c r="CJ7" s="102"/>
-      <c r="CK7" s="102"/>
-      <c r="CL7" s="102"/>
-      <c r="CM7" s="102"/>
-      <c r="CN7" s="102"/>
-      <c r="CO7" s="102"/>
+      <c r="I7" s="90"/>
+      <c r="J7" s="91"/>
+      <c r="K7" s="91"/>
+      <c r="L7" s="91"/>
+      <c r="M7" s="91"/>
+      <c r="N7" s="91"/>
+      <c r="O7" s="91"/>
+      <c r="P7" s="91"/>
+      <c r="Q7" s="91"/>
+      <c r="R7" s="91"/>
+      <c r="S7" s="91"/>
+      <c r="T7" s="91"/>
+      <c r="U7" s="91"/>
+      <c r="V7" s="91"/>
+      <c r="W7" s="91"/>
+      <c r="X7" s="91"/>
+      <c r="Y7" s="91"/>
+      <c r="Z7" s="91"/>
+      <c r="AA7" s="91"/>
+      <c r="AB7" s="91"/>
+      <c r="AC7" s="91"/>
+      <c r="AD7" s="91"/>
+      <c r="AE7" s="91"/>
+      <c r="AF7" s="91"/>
+      <c r="AG7" s="91"/>
+      <c r="AH7" s="91"/>
+      <c r="AI7" s="91"/>
+      <c r="AJ7" s="91"/>
+      <c r="AK7" s="91"/>
+      <c r="AL7" s="91"/>
+      <c r="AM7" s="91"/>
+      <c r="AN7" s="91"/>
+      <c r="AO7" s="91"/>
+      <c r="AP7" s="91"/>
+      <c r="AQ7" s="91"/>
+      <c r="AR7" s="91"/>
+      <c r="AS7" s="91"/>
+      <c r="AT7" s="91"/>
+      <c r="AU7" s="91"/>
+      <c r="AV7" s="91"/>
+      <c r="AW7" s="91"/>
+      <c r="AX7" s="91"/>
+      <c r="AY7" s="91"/>
+      <c r="AZ7" s="91"/>
+      <c r="BA7" s="91"/>
+      <c r="BB7" s="91"/>
+      <c r="BC7" s="91"/>
+      <c r="BD7" s="91"/>
+      <c r="BE7" s="91"/>
+      <c r="BF7" s="91"/>
+      <c r="BG7" s="91"/>
+      <c r="BH7" s="91"/>
+      <c r="BI7" s="91"/>
+      <c r="BJ7" s="91"/>
+      <c r="BK7" s="91"/>
+      <c r="BL7" s="91"/>
+      <c r="BM7" s="91"/>
+      <c r="BN7" s="91"/>
+      <c r="BO7" s="91"/>
+      <c r="BP7" s="91"/>
+      <c r="BQ7" s="91"/>
+      <c r="BR7" s="91"/>
+      <c r="BS7" s="91"/>
+      <c r="BT7" s="91"/>
+      <c r="BU7" s="91"/>
+      <c r="BV7" s="91"/>
+      <c r="BW7" s="91"/>
+      <c r="BX7" s="91"/>
+      <c r="BY7" s="91"/>
+      <c r="BZ7" s="91"/>
+      <c r="CA7" s="91"/>
+      <c r="CB7" s="91"/>
+      <c r="CC7" s="91"/>
+      <c r="CD7" s="91"/>
+      <c r="CE7" s="91"/>
+      <c r="CF7" s="91"/>
+      <c r="CG7" s="91"/>
+      <c r="CH7" s="91"/>
+      <c r="CI7" s="91"/>
+      <c r="CJ7" s="91"/>
+      <c r="CK7" s="91"/>
+      <c r="CL7" s="91"/>
+      <c r="CM7" s="91"/>
+      <c r="CN7" s="91"/>
+      <c r="CO7" s="91"/>
       <c r="CP7" s="87"/>
       <c r="CQ7" s="78"/>
       <c r="CR7" s="78"/>
@@ -3148,10 +3148,10 @@
       <c r="A8" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="98" t="s">
+      <c r="B8" s="102" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="98"/>
+      <c r="C8" s="102"/>
       <c r="D8" s="13">
         <v>1</v>
       </c>
@@ -3282,10 +3282,10 @@
     </row>
     <row r="9" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="24"/>
-      <c r="B9" s="98" t="s">
+      <c r="B9" s="102" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="98"/>
+      <c r="C9" s="102"/>
       <c r="D9" s="13">
         <v>1</v>
       </c>
@@ -3413,10 +3413,10 @@
     </row>
     <row r="10" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="23"/>
-      <c r="B10" s="98" t="s">
+      <c r="B10" s="102" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="98"/>
+      <c r="C10" s="102"/>
       <c r="D10" s="13">
         <v>1</v>
       </c>
@@ -3547,10 +3547,10 @@
     </row>
     <row r="11" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="23"/>
-      <c r="B11" s="98" t="s">
+      <c r="B11" s="102" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="98"/>
+      <c r="C11" s="102"/>
       <c r="D11" s="13">
         <v>1</v>
       </c>
@@ -3678,10 +3678,10 @@
     </row>
     <row r="12" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="23"/>
-      <c r="B12" s="98" t="s">
+      <c r="B12" s="102" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="98"/>
+      <c r="C12" s="102"/>
       <c r="D12" s="13">
         <v>1</v>
       </c>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="13" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="23"/>
-      <c r="B13" s="98" t="s">
+      <c r="B13" s="102" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="98"/>
+      <c r="C13" s="102"/>
       <c r="D13" s="13">
         <v>1</v>
       </c>
@@ -3955,91 +3955,91 @@
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="I14" s="90"/>
-      <c r="J14" s="91"/>
-      <c r="K14" s="91"/>
-      <c r="L14" s="91"/>
-      <c r="M14" s="91"/>
-      <c r="N14" s="91"/>
-      <c r="O14" s="91"/>
-      <c r="P14" s="91"/>
-      <c r="Q14" s="91"/>
-      <c r="R14" s="91"/>
-      <c r="S14" s="91"/>
-      <c r="T14" s="91"/>
-      <c r="U14" s="91"/>
-      <c r="V14" s="91"/>
-      <c r="W14" s="91"/>
-      <c r="X14" s="91"/>
-      <c r="Y14" s="91"/>
-      <c r="Z14" s="91"/>
-      <c r="AA14" s="91"/>
-      <c r="AB14" s="91"/>
-      <c r="AC14" s="91"/>
-      <c r="AD14" s="91"/>
-      <c r="AE14" s="91"/>
-      <c r="AF14" s="91"/>
-      <c r="AG14" s="91"/>
-      <c r="AH14" s="91"/>
-      <c r="AI14" s="91"/>
-      <c r="AJ14" s="91"/>
-      <c r="AK14" s="91"/>
-      <c r="AL14" s="91"/>
-      <c r="AM14" s="91"/>
-      <c r="AN14" s="91"/>
-      <c r="AO14" s="91"/>
-      <c r="AP14" s="91"/>
-      <c r="AQ14" s="91"/>
-      <c r="AR14" s="91"/>
-      <c r="AS14" s="91"/>
-      <c r="AT14" s="91"/>
-      <c r="AU14" s="91"/>
-      <c r="AV14" s="91"/>
-      <c r="AW14" s="91"/>
-      <c r="AX14" s="91"/>
-      <c r="AY14" s="91"/>
-      <c r="AZ14" s="91"/>
-      <c r="BA14" s="91"/>
-      <c r="BB14" s="91"/>
-      <c r="BC14" s="91"/>
-      <c r="BD14" s="91"/>
-      <c r="BE14" s="91"/>
-      <c r="BF14" s="91"/>
-      <c r="BG14" s="91"/>
-      <c r="BH14" s="91"/>
-      <c r="BI14" s="91"/>
-      <c r="BJ14" s="91"/>
-      <c r="BK14" s="91"/>
-      <c r="BL14" s="91"/>
-      <c r="BM14" s="91"/>
-      <c r="BN14" s="91"/>
-      <c r="BO14" s="91"/>
-      <c r="BP14" s="91"/>
-      <c r="BQ14" s="91"/>
-      <c r="BR14" s="91"/>
-      <c r="BS14" s="91"/>
-      <c r="BT14" s="91"/>
-      <c r="BU14" s="91"/>
-      <c r="BV14" s="91"/>
-      <c r="BW14" s="91"/>
-      <c r="BX14" s="91"/>
-      <c r="BY14" s="91"/>
-      <c r="BZ14" s="91"/>
-      <c r="CA14" s="91"/>
-      <c r="CB14" s="91"/>
-      <c r="CC14" s="91"/>
-      <c r="CD14" s="91"/>
-      <c r="CE14" s="91"/>
-      <c r="CF14" s="91"/>
-      <c r="CG14" s="91"/>
-      <c r="CH14" s="91"/>
-      <c r="CI14" s="91"/>
-      <c r="CJ14" s="91"/>
-      <c r="CK14" s="91"/>
-      <c r="CL14" s="91"/>
-      <c r="CM14" s="91"/>
-      <c r="CN14" s="91"/>
-      <c r="CO14" s="92"/>
+      <c r="I14" s="94"/>
+      <c r="J14" s="95"/>
+      <c r="K14" s="95"/>
+      <c r="L14" s="95"/>
+      <c r="M14" s="95"/>
+      <c r="N14" s="95"/>
+      <c r="O14" s="95"/>
+      <c r="P14" s="95"/>
+      <c r="Q14" s="95"/>
+      <c r="R14" s="95"/>
+      <c r="S14" s="95"/>
+      <c r="T14" s="95"/>
+      <c r="U14" s="95"/>
+      <c r="V14" s="95"/>
+      <c r="W14" s="95"/>
+      <c r="X14" s="95"/>
+      <c r="Y14" s="95"/>
+      <c r="Z14" s="95"/>
+      <c r="AA14" s="95"/>
+      <c r="AB14" s="95"/>
+      <c r="AC14" s="95"/>
+      <c r="AD14" s="95"/>
+      <c r="AE14" s="95"/>
+      <c r="AF14" s="95"/>
+      <c r="AG14" s="95"/>
+      <c r="AH14" s="95"/>
+      <c r="AI14" s="95"/>
+      <c r="AJ14" s="95"/>
+      <c r="AK14" s="95"/>
+      <c r="AL14" s="95"/>
+      <c r="AM14" s="95"/>
+      <c r="AN14" s="95"/>
+      <c r="AO14" s="95"/>
+      <c r="AP14" s="95"/>
+      <c r="AQ14" s="95"/>
+      <c r="AR14" s="95"/>
+      <c r="AS14" s="95"/>
+      <c r="AT14" s="95"/>
+      <c r="AU14" s="95"/>
+      <c r="AV14" s="95"/>
+      <c r="AW14" s="95"/>
+      <c r="AX14" s="95"/>
+      <c r="AY14" s="95"/>
+      <c r="AZ14" s="95"/>
+      <c r="BA14" s="95"/>
+      <c r="BB14" s="95"/>
+      <c r="BC14" s="95"/>
+      <c r="BD14" s="95"/>
+      <c r="BE14" s="95"/>
+      <c r="BF14" s="95"/>
+      <c r="BG14" s="95"/>
+      <c r="BH14" s="95"/>
+      <c r="BI14" s="95"/>
+      <c r="BJ14" s="95"/>
+      <c r="BK14" s="95"/>
+      <c r="BL14" s="95"/>
+      <c r="BM14" s="95"/>
+      <c r="BN14" s="95"/>
+      <c r="BO14" s="95"/>
+      <c r="BP14" s="95"/>
+      <c r="BQ14" s="95"/>
+      <c r="BR14" s="95"/>
+      <c r="BS14" s="95"/>
+      <c r="BT14" s="95"/>
+      <c r="BU14" s="95"/>
+      <c r="BV14" s="95"/>
+      <c r="BW14" s="95"/>
+      <c r="BX14" s="95"/>
+      <c r="BY14" s="95"/>
+      <c r="BZ14" s="95"/>
+      <c r="CA14" s="95"/>
+      <c r="CB14" s="95"/>
+      <c r="CC14" s="95"/>
+      <c r="CD14" s="95"/>
+      <c r="CE14" s="95"/>
+      <c r="CF14" s="95"/>
+      <c r="CG14" s="95"/>
+      <c r="CH14" s="95"/>
+      <c r="CI14" s="95"/>
+      <c r="CJ14" s="95"/>
+      <c r="CK14" s="95"/>
+      <c r="CL14" s="95"/>
+      <c r="CM14" s="95"/>
+      <c r="CN14" s="95"/>
+      <c r="CO14" s="96"/>
       <c r="CP14" s="86"/>
       <c r="CQ14"/>
       <c r="CR14"/>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="C16" s="30"/>
       <c r="D16" s="16">
-        <v>0.55000000000000004</v>
+        <v>0.95</v>
       </c>
       <c r="E16" s="42">
         <v>45922</v>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="C17" s="30"/>
       <c r="D17" s="16">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="E17" s="42">
         <v>45926</v>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="C18" s="30"/>
       <c r="D18" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" s="42">
         <v>45964</v>
@@ -5002,91 +5002,91 @@
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="I22" s="88"/>
-      <c r="J22" s="89"/>
-      <c r="K22" s="89"/>
-      <c r="L22" s="89"/>
-      <c r="M22" s="89"/>
-      <c r="N22" s="89"/>
-      <c r="O22" s="89"/>
-      <c r="P22" s="89"/>
-      <c r="Q22" s="89"/>
-      <c r="R22" s="89"/>
-      <c r="S22" s="89"/>
-      <c r="T22" s="89"/>
-      <c r="U22" s="89"/>
-      <c r="V22" s="89"/>
-      <c r="W22" s="89"/>
-      <c r="X22" s="89"/>
-      <c r="Y22" s="89"/>
-      <c r="Z22" s="89"/>
-      <c r="AA22" s="89"/>
-      <c r="AB22" s="89"/>
-      <c r="AC22" s="89"/>
-      <c r="AD22" s="89"/>
-      <c r="AE22" s="89"/>
-      <c r="AF22" s="89"/>
-      <c r="AG22" s="89"/>
-      <c r="AH22" s="89"/>
-      <c r="AI22" s="89"/>
-      <c r="AJ22" s="89"/>
-      <c r="AK22" s="89"/>
-      <c r="AL22" s="89"/>
-      <c r="AM22" s="89"/>
-      <c r="AN22" s="89"/>
-      <c r="AO22" s="89"/>
-      <c r="AP22" s="89"/>
-      <c r="AQ22" s="89"/>
-      <c r="AR22" s="89"/>
-      <c r="AS22" s="89"/>
-      <c r="AT22" s="89"/>
-      <c r="AU22" s="89"/>
-      <c r="AV22" s="89"/>
-      <c r="AW22" s="89"/>
-      <c r="AX22" s="89"/>
-      <c r="AY22" s="89"/>
-      <c r="AZ22" s="89"/>
-      <c r="BA22" s="89"/>
-      <c r="BB22" s="89"/>
-      <c r="BC22" s="89"/>
-      <c r="BD22" s="89"/>
-      <c r="BE22" s="89"/>
-      <c r="BF22" s="89"/>
-      <c r="BG22" s="89"/>
-      <c r="BH22" s="89"/>
-      <c r="BI22" s="89"/>
-      <c r="BJ22" s="89"/>
-      <c r="BK22" s="89"/>
-      <c r="BL22" s="89"/>
-      <c r="BM22" s="89"/>
-      <c r="BN22" s="89"/>
-      <c r="BO22" s="89"/>
-      <c r="BP22" s="89"/>
-      <c r="BQ22" s="89"/>
-      <c r="BR22" s="89"/>
-      <c r="BS22" s="89"/>
-      <c r="BT22" s="89"/>
-      <c r="BU22" s="89"/>
-      <c r="BV22" s="89"/>
-      <c r="BW22" s="89"/>
-      <c r="BX22" s="89"/>
-      <c r="BY22" s="89"/>
-      <c r="BZ22" s="89"/>
-      <c r="CA22" s="89"/>
-      <c r="CB22" s="89"/>
-      <c r="CC22" s="89"/>
-      <c r="CD22" s="89"/>
-      <c r="CE22" s="89"/>
-      <c r="CF22" s="89"/>
-      <c r="CG22" s="89"/>
-      <c r="CH22" s="89"/>
-      <c r="CI22" s="89"/>
-      <c r="CJ22" s="89"/>
-      <c r="CK22" s="89"/>
-      <c r="CL22" s="89"/>
-      <c r="CM22" s="89"/>
-      <c r="CN22" s="89"/>
-      <c r="CO22" s="89"/>
+      <c r="I22" s="92"/>
+      <c r="J22" s="93"/>
+      <c r="K22" s="93"/>
+      <c r="L22" s="93"/>
+      <c r="M22" s="93"/>
+      <c r="N22" s="93"/>
+      <c r="O22" s="93"/>
+      <c r="P22" s="93"/>
+      <c r="Q22" s="93"/>
+      <c r="R22" s="93"/>
+      <c r="S22" s="93"/>
+      <c r="T22" s="93"/>
+      <c r="U22" s="93"/>
+      <c r="V22" s="93"/>
+      <c r="W22" s="93"/>
+      <c r="X22" s="93"/>
+      <c r="Y22" s="93"/>
+      <c r="Z22" s="93"/>
+      <c r="AA22" s="93"/>
+      <c r="AB22" s="93"/>
+      <c r="AC22" s="93"/>
+      <c r="AD22" s="93"/>
+      <c r="AE22" s="93"/>
+      <c r="AF22" s="93"/>
+      <c r="AG22" s="93"/>
+      <c r="AH22" s="93"/>
+      <c r="AI22" s="93"/>
+      <c r="AJ22" s="93"/>
+      <c r="AK22" s="93"/>
+      <c r="AL22" s="93"/>
+      <c r="AM22" s="93"/>
+      <c r="AN22" s="93"/>
+      <c r="AO22" s="93"/>
+      <c r="AP22" s="93"/>
+      <c r="AQ22" s="93"/>
+      <c r="AR22" s="93"/>
+      <c r="AS22" s="93"/>
+      <c r="AT22" s="93"/>
+      <c r="AU22" s="93"/>
+      <c r="AV22" s="93"/>
+      <c r="AW22" s="93"/>
+      <c r="AX22" s="93"/>
+      <c r="AY22" s="93"/>
+      <c r="AZ22" s="93"/>
+      <c r="BA22" s="93"/>
+      <c r="BB22" s="93"/>
+      <c r="BC22" s="93"/>
+      <c r="BD22" s="93"/>
+      <c r="BE22" s="93"/>
+      <c r="BF22" s="93"/>
+      <c r="BG22" s="93"/>
+      <c r="BH22" s="93"/>
+      <c r="BI22" s="93"/>
+      <c r="BJ22" s="93"/>
+      <c r="BK22" s="93"/>
+      <c r="BL22" s="93"/>
+      <c r="BM22" s="93"/>
+      <c r="BN22" s="93"/>
+      <c r="BO22" s="93"/>
+      <c r="BP22" s="93"/>
+      <c r="BQ22" s="93"/>
+      <c r="BR22" s="93"/>
+      <c r="BS22" s="93"/>
+      <c r="BT22" s="93"/>
+      <c r="BU22" s="93"/>
+      <c r="BV22" s="93"/>
+      <c r="BW22" s="93"/>
+      <c r="BX22" s="93"/>
+      <c r="BY22" s="93"/>
+      <c r="BZ22" s="93"/>
+      <c r="CA22" s="93"/>
+      <c r="CB22" s="93"/>
+      <c r="CC22" s="93"/>
+      <c r="CD22" s="93"/>
+      <c r="CE22" s="93"/>
+      <c r="CF22" s="93"/>
+      <c r="CG22" s="93"/>
+      <c r="CH22" s="93"/>
+      <c r="CI22" s="93"/>
+      <c r="CJ22" s="93"/>
+      <c r="CK22" s="93"/>
+      <c r="CL22" s="93"/>
+      <c r="CM22" s="93"/>
+      <c r="CN22" s="93"/>
+      <c r="CO22" s="93"/>
       <c r="CP22" s="86"/>
       <c r="CQ22"/>
       <c r="CR22"/>
@@ -6788,19 +6788,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="CF3:CJ3"/>
-    <mergeCell ref="CK3:CO3"/>
-    <mergeCell ref="I7:CO7"/>
-    <mergeCell ref="BB3:BF3"/>
-    <mergeCell ref="BG3:BK3"/>
-    <mergeCell ref="BL3:BP3"/>
-    <mergeCell ref="BQ3:BU3"/>
-    <mergeCell ref="BV3:BZ3"/>
-    <mergeCell ref="AC3:AG3"/>
-    <mergeCell ref="AH3:AL3"/>
-    <mergeCell ref="AM3:AQ3"/>
-    <mergeCell ref="AR3:AV3"/>
-    <mergeCell ref="AW3:BA3"/>
     <mergeCell ref="I22:CO22"/>
     <mergeCell ref="I14:CO14"/>
     <mergeCell ref="C2:D2"/>
@@ -6817,6 +6804,19 @@
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="CA3:CE3"/>
+    <mergeCell ref="CF3:CJ3"/>
+    <mergeCell ref="CK3:CO3"/>
+    <mergeCell ref="I7:CO7"/>
+    <mergeCell ref="BB3:BF3"/>
+    <mergeCell ref="BG3:BK3"/>
+    <mergeCell ref="BL3:BP3"/>
+    <mergeCell ref="BQ3:BU3"/>
+    <mergeCell ref="BV3:BZ3"/>
+    <mergeCell ref="AC3:AG3"/>
+    <mergeCell ref="AH3:AL3"/>
+    <mergeCell ref="AM3:AQ3"/>
+    <mergeCell ref="AR3:AV3"/>
+    <mergeCell ref="AW3:BA3"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D35">
     <cfRule type="dataBar" priority="17">
@@ -7191,15 +7191,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
@@ -7217,6 +7208,15 @@
     <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7241,14 +7241,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -7258,4 +7250,12 @@
     <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Capstone/Fase 1/Grupales/Carta Gantt.xlsx
+++ b/Capstone/Fase 1/Grupales/Carta Gantt.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{876B3C3D-515C-4E43-95BF-FD300A8C7BDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FB45FB6-84BD-48FA-A2B2-A812CF6F465F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1303,6 +1303,39 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="41" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="8">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="8" applyBorder="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="8" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="8" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="3" xfId="9">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="12" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="169" fontId="0" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1314,39 +1347,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="42" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="8">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="8" applyBorder="1">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="8" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="8" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="3" xfId="9">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="12" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -2038,164 +2038,164 @@
         <v>1</v>
       </c>
       <c r="B2" s="28"/>
-      <c r="C2" s="97" t="s">
+      <c r="C2" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="98"/>
-      <c r="E2" s="101">
+      <c r="D2" s="94"/>
+      <c r="E2" s="97">
         <f>DATE(2025,8,12)</f>
         <v>45881</v>
       </c>
-      <c r="F2" s="101"/>
+      <c r="F2" s="97"/>
     </row>
     <row r="3" spans="1:121" s="26" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="99" t="s">
+      <c r="C3" s="95" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="100"/>
+      <c r="D3" s="96"/>
       <c r="E3" s="61">
         <v>1</v>
       </c>
       <c r="H3" s="62"/>
-      <c r="I3" s="88">
+      <c r="I3" s="99">
         <f>I4</f>
         <v>45880</v>
       </c>
-      <c r="J3" s="88"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="88"/>
-      <c r="M3" s="88"/>
-      <c r="N3" s="88">
+      <c r="J3" s="99"/>
+      <c r="K3" s="99"/>
+      <c r="L3" s="99"/>
+      <c r="M3" s="99"/>
+      <c r="N3" s="99">
         <f>N4</f>
         <v>45887</v>
       </c>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88">
+      <c r="O3" s="99"/>
+      <c r="P3" s="99"/>
+      <c r="Q3" s="99"/>
+      <c r="R3" s="99"/>
+      <c r="S3" s="99">
         <f>S4</f>
         <v>45894</v>
       </c>
-      <c r="T3" s="88"/>
-      <c r="U3" s="88"/>
-      <c r="V3" s="88"/>
-      <c r="W3" s="88"/>
-      <c r="X3" s="88">
+      <c r="T3" s="99"/>
+      <c r="U3" s="99"/>
+      <c r="V3" s="99"/>
+      <c r="W3" s="99"/>
+      <c r="X3" s="99">
         <f>X4</f>
         <v>45901</v>
       </c>
-      <c r="Y3" s="88"/>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="88"/>
-      <c r="AB3" s="88"/>
-      <c r="AC3" s="88">
+      <c r="Y3" s="99"/>
+      <c r="Z3" s="99"/>
+      <c r="AA3" s="99"/>
+      <c r="AB3" s="99"/>
+      <c r="AC3" s="99">
         <f t="shared" ref="AC3" si="0">AC4</f>
         <v>45908</v>
       </c>
-      <c r="AD3" s="88"/>
-      <c r="AE3" s="88"/>
-      <c r="AF3" s="88"/>
-      <c r="AG3" s="88"/>
-      <c r="AH3" s="88">
+      <c r="AD3" s="99"/>
+      <c r="AE3" s="99"/>
+      <c r="AF3" s="99"/>
+      <c r="AG3" s="99"/>
+      <c r="AH3" s="99">
         <f t="shared" ref="AH3" si="1">AH4</f>
         <v>45915</v>
       </c>
-      <c r="AI3" s="88"/>
-      <c r="AJ3" s="88"/>
-      <c r="AK3" s="88"/>
-      <c r="AL3" s="88"/>
-      <c r="AM3" s="88">
+      <c r="AI3" s="99"/>
+      <c r="AJ3" s="99"/>
+      <c r="AK3" s="99"/>
+      <c r="AL3" s="99"/>
+      <c r="AM3" s="99">
         <f t="shared" ref="AM3" si="2">AM4</f>
         <v>45922</v>
       </c>
-      <c r="AN3" s="88"/>
-      <c r="AO3" s="88"/>
-      <c r="AP3" s="88"/>
-      <c r="AQ3" s="88"/>
-      <c r="AR3" s="88">
+      <c r="AN3" s="99"/>
+      <c r="AO3" s="99"/>
+      <c r="AP3" s="99"/>
+      <c r="AQ3" s="99"/>
+      <c r="AR3" s="99">
         <f>AR4</f>
         <v>45929</v>
       </c>
-      <c r="AS3" s="88"/>
-      <c r="AT3" s="88"/>
-      <c r="AU3" s="88"/>
-      <c r="AV3" s="88"/>
-      <c r="AW3" s="88">
+      <c r="AS3" s="99"/>
+      <c r="AT3" s="99"/>
+      <c r="AU3" s="99"/>
+      <c r="AV3" s="99"/>
+      <c r="AW3" s="99">
         <f t="shared" ref="AW3" si="3">AW4</f>
         <v>45936</v>
       </c>
-      <c r="AX3" s="88"/>
-      <c r="AY3" s="88"/>
-      <c r="AZ3" s="88"/>
-      <c r="BA3" s="88"/>
-      <c r="BB3" s="88">
+      <c r="AX3" s="99"/>
+      <c r="AY3" s="99"/>
+      <c r="AZ3" s="99"/>
+      <c r="BA3" s="99"/>
+      <c r="BB3" s="99">
         <f t="shared" ref="BB3" si="4">BB4</f>
         <v>45943</v>
       </c>
-      <c r="BC3" s="88"/>
-      <c r="BD3" s="88"/>
-      <c r="BE3" s="88"/>
-      <c r="BF3" s="88"/>
-      <c r="BG3" s="88">
+      <c r="BC3" s="99"/>
+      <c r="BD3" s="99"/>
+      <c r="BE3" s="99"/>
+      <c r="BF3" s="99"/>
+      <c r="BG3" s="99">
         <f t="shared" ref="BG3" si="5">BG4</f>
         <v>45950</v>
       </c>
-      <c r="BH3" s="88"/>
-      <c r="BI3" s="88"/>
-      <c r="BJ3" s="88"/>
-      <c r="BK3" s="88"/>
-      <c r="BL3" s="88">
+      <c r="BH3" s="99"/>
+      <c r="BI3" s="99"/>
+      <c r="BJ3" s="99"/>
+      <c r="BK3" s="99"/>
+      <c r="BL3" s="99">
         <f t="shared" ref="BL3" si="6">BL4</f>
         <v>45957</v>
       </c>
-      <c r="BM3" s="88"/>
-      <c r="BN3" s="88"/>
-      <c r="BO3" s="88"/>
-      <c r="BP3" s="88"/>
-      <c r="BQ3" s="88">
+      <c r="BM3" s="99"/>
+      <c r="BN3" s="99"/>
+      <c r="BO3" s="99"/>
+      <c r="BP3" s="99"/>
+      <c r="BQ3" s="99">
         <f t="shared" ref="BQ3" si="7">BQ4</f>
         <v>45964</v>
       </c>
-      <c r="BR3" s="88"/>
-      <c r="BS3" s="88"/>
-      <c r="BT3" s="88"/>
-      <c r="BU3" s="88"/>
-      <c r="BV3" s="88">
+      <c r="BR3" s="99"/>
+      <c r="BS3" s="99"/>
+      <c r="BT3" s="99"/>
+      <c r="BU3" s="99"/>
+      <c r="BV3" s="99">
         <f t="shared" ref="BV3" si="8">BV4</f>
         <v>45971</v>
       </c>
-      <c r="BW3" s="88"/>
-      <c r="BX3" s="88"/>
-      <c r="BY3" s="88"/>
-      <c r="BZ3" s="88"/>
-      <c r="CA3" s="88">
+      <c r="BW3" s="99"/>
+      <c r="BX3" s="99"/>
+      <c r="BY3" s="99"/>
+      <c r="BZ3" s="99"/>
+      <c r="CA3" s="99">
         <f t="shared" ref="CA3" si="9">CA4</f>
         <v>45978</v>
       </c>
-      <c r="CB3" s="88"/>
-      <c r="CC3" s="88"/>
-      <c r="CD3" s="88"/>
-      <c r="CE3" s="88"/>
-      <c r="CF3" s="88">
+      <c r="CB3" s="99"/>
+      <c r="CC3" s="99"/>
+      <c r="CD3" s="99"/>
+      <c r="CE3" s="99"/>
+      <c r="CF3" s="99">
         <f t="shared" ref="CF3" si="10">CF4</f>
         <v>45985</v>
       </c>
-      <c r="CG3" s="88"/>
-      <c r="CH3" s="88"/>
-      <c r="CI3" s="88"/>
-      <c r="CJ3" s="88"/>
-      <c r="CK3" s="88">
+      <c r="CG3" s="99"/>
+      <c r="CH3" s="99"/>
+      <c r="CI3" s="99"/>
+      <c r="CJ3" s="99"/>
+      <c r="CK3" s="99">
         <f t="shared" ref="CK3" si="11">CK4</f>
         <v>45992</v>
       </c>
-      <c r="CL3" s="88"/>
-      <c r="CM3" s="88"/>
-      <c r="CN3" s="88"/>
-      <c r="CO3" s="89"/>
+      <c r="CL3" s="99"/>
+      <c r="CM3" s="99"/>
+      <c r="CN3" s="99"/>
+      <c r="CO3" s="100"/>
       <c r="CP3" s="84"/>
       <c r="CQ3" s="74"/>
       <c r="CR3" s="74"/>
@@ -3030,91 +3030,91 @@
         <f t="shared" ref="H7:H28" si="25">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v/>
       </c>
-      <c r="I7" s="90"/>
-      <c r="J7" s="91"/>
-      <c r="K7" s="91"/>
-      <c r="L7" s="91"/>
-      <c r="M7" s="91"/>
-      <c r="N7" s="91"/>
-      <c r="O7" s="91"/>
-      <c r="P7" s="91"/>
-      <c r="Q7" s="91"/>
-      <c r="R7" s="91"/>
-      <c r="S7" s="91"/>
-      <c r="T7" s="91"/>
-      <c r="U7" s="91"/>
-      <c r="V7" s="91"/>
-      <c r="W7" s="91"/>
-      <c r="X7" s="91"/>
-      <c r="Y7" s="91"/>
-      <c r="Z7" s="91"/>
-      <c r="AA7" s="91"/>
-      <c r="AB7" s="91"/>
-      <c r="AC7" s="91"/>
-      <c r="AD7" s="91"/>
-      <c r="AE7" s="91"/>
-      <c r="AF7" s="91"/>
-      <c r="AG7" s="91"/>
-      <c r="AH7" s="91"/>
-      <c r="AI7" s="91"/>
-      <c r="AJ7" s="91"/>
-      <c r="AK7" s="91"/>
-      <c r="AL7" s="91"/>
-      <c r="AM7" s="91"/>
-      <c r="AN7" s="91"/>
-      <c r="AO7" s="91"/>
-      <c r="AP7" s="91"/>
-      <c r="AQ7" s="91"/>
-      <c r="AR7" s="91"/>
-      <c r="AS7" s="91"/>
-      <c r="AT7" s="91"/>
-      <c r="AU7" s="91"/>
-      <c r="AV7" s="91"/>
-      <c r="AW7" s="91"/>
-      <c r="AX7" s="91"/>
-      <c r="AY7" s="91"/>
-      <c r="AZ7" s="91"/>
-      <c r="BA7" s="91"/>
-      <c r="BB7" s="91"/>
-      <c r="BC7" s="91"/>
-      <c r="BD7" s="91"/>
-      <c r="BE7" s="91"/>
-      <c r="BF7" s="91"/>
-      <c r="BG7" s="91"/>
-      <c r="BH7" s="91"/>
-      <c r="BI7" s="91"/>
-      <c r="BJ7" s="91"/>
-      <c r="BK7" s="91"/>
-      <c r="BL7" s="91"/>
-      <c r="BM7" s="91"/>
-      <c r="BN7" s="91"/>
-      <c r="BO7" s="91"/>
-      <c r="BP7" s="91"/>
-      <c r="BQ7" s="91"/>
-      <c r="BR7" s="91"/>
-      <c r="BS7" s="91"/>
-      <c r="BT7" s="91"/>
-      <c r="BU7" s="91"/>
-      <c r="BV7" s="91"/>
-      <c r="BW7" s="91"/>
-      <c r="BX7" s="91"/>
-      <c r="BY7" s="91"/>
-      <c r="BZ7" s="91"/>
-      <c r="CA7" s="91"/>
-      <c r="CB7" s="91"/>
-      <c r="CC7" s="91"/>
-      <c r="CD7" s="91"/>
-      <c r="CE7" s="91"/>
-      <c r="CF7" s="91"/>
-      <c r="CG7" s="91"/>
-      <c r="CH7" s="91"/>
-      <c r="CI7" s="91"/>
-      <c r="CJ7" s="91"/>
-      <c r="CK7" s="91"/>
-      <c r="CL7" s="91"/>
-      <c r="CM7" s="91"/>
-      <c r="CN7" s="91"/>
-      <c r="CO7" s="91"/>
+      <c r="I7" s="101"/>
+      <c r="J7" s="102"/>
+      <c r="K7" s="102"/>
+      <c r="L7" s="102"/>
+      <c r="M7" s="102"/>
+      <c r="N7" s="102"/>
+      <c r="O7" s="102"/>
+      <c r="P7" s="102"/>
+      <c r="Q7" s="102"/>
+      <c r="R7" s="102"/>
+      <c r="S7" s="102"/>
+      <c r="T7" s="102"/>
+      <c r="U7" s="102"/>
+      <c r="V7" s="102"/>
+      <c r="W7" s="102"/>
+      <c r="X7" s="102"/>
+      <c r="Y7" s="102"/>
+      <c r="Z7" s="102"/>
+      <c r="AA7" s="102"/>
+      <c r="AB7" s="102"/>
+      <c r="AC7" s="102"/>
+      <c r="AD7" s="102"/>
+      <c r="AE7" s="102"/>
+      <c r="AF7" s="102"/>
+      <c r="AG7" s="102"/>
+      <c r="AH7" s="102"/>
+      <c r="AI7" s="102"/>
+      <c r="AJ7" s="102"/>
+      <c r="AK7" s="102"/>
+      <c r="AL7" s="102"/>
+      <c r="AM7" s="102"/>
+      <c r="AN7" s="102"/>
+      <c r="AO7" s="102"/>
+      <c r="AP7" s="102"/>
+      <c r="AQ7" s="102"/>
+      <c r="AR7" s="102"/>
+      <c r="AS7" s="102"/>
+      <c r="AT7" s="102"/>
+      <c r="AU7" s="102"/>
+      <c r="AV7" s="102"/>
+      <c r="AW7" s="102"/>
+      <c r="AX7" s="102"/>
+      <c r="AY7" s="102"/>
+      <c r="AZ7" s="102"/>
+      <c r="BA7" s="102"/>
+      <c r="BB7" s="102"/>
+      <c r="BC7" s="102"/>
+      <c r="BD7" s="102"/>
+      <c r="BE7" s="102"/>
+      <c r="BF7" s="102"/>
+      <c r="BG7" s="102"/>
+      <c r="BH7" s="102"/>
+      <c r="BI7" s="102"/>
+      <c r="BJ7" s="102"/>
+      <c r="BK7" s="102"/>
+      <c r="BL7" s="102"/>
+      <c r="BM7" s="102"/>
+      <c r="BN7" s="102"/>
+      <c r="BO7" s="102"/>
+      <c r="BP7" s="102"/>
+      <c r="BQ7" s="102"/>
+      <c r="BR7" s="102"/>
+      <c r="BS7" s="102"/>
+      <c r="BT7" s="102"/>
+      <c r="BU7" s="102"/>
+      <c r="BV7" s="102"/>
+      <c r="BW7" s="102"/>
+      <c r="BX7" s="102"/>
+      <c r="BY7" s="102"/>
+      <c r="BZ7" s="102"/>
+      <c r="CA7" s="102"/>
+      <c r="CB7" s="102"/>
+      <c r="CC7" s="102"/>
+      <c r="CD7" s="102"/>
+      <c r="CE7" s="102"/>
+      <c r="CF7" s="102"/>
+      <c r="CG7" s="102"/>
+      <c r="CH7" s="102"/>
+      <c r="CI7" s="102"/>
+      <c r="CJ7" s="102"/>
+      <c r="CK7" s="102"/>
+      <c r="CL7" s="102"/>
+      <c r="CM7" s="102"/>
+      <c r="CN7" s="102"/>
+      <c r="CO7" s="102"/>
       <c r="CP7" s="87"/>
       <c r="CQ7" s="78"/>
       <c r="CR7" s="78"/>
@@ -3148,10 +3148,10 @@
       <c r="A8" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="102" t="s">
+      <c r="B8" s="98" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="102"/>
+      <c r="C8" s="98"/>
       <c r="D8" s="13">
         <v>1</v>
       </c>
@@ -3282,10 +3282,10 @@
     </row>
     <row r="9" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="24"/>
-      <c r="B9" s="102" t="s">
+      <c r="B9" s="98" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="102"/>
+      <c r="C9" s="98"/>
       <c r="D9" s="13">
         <v>1</v>
       </c>
@@ -3413,10 +3413,10 @@
     </row>
     <row r="10" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="23"/>
-      <c r="B10" s="102" t="s">
+      <c r="B10" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="102"/>
+      <c r="C10" s="98"/>
       <c r="D10" s="13">
         <v>1</v>
       </c>
@@ -3547,10 +3547,10 @@
     </row>
     <row r="11" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="23"/>
-      <c r="B11" s="102" t="s">
+      <c r="B11" s="98" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="102"/>
+      <c r="C11" s="98"/>
       <c r="D11" s="13">
         <v>1</v>
       </c>
@@ -3678,10 +3678,10 @@
     </row>
     <row r="12" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="23"/>
-      <c r="B12" s="102" t="s">
+      <c r="B12" s="98" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="102"/>
+      <c r="C12" s="98"/>
       <c r="D12" s="13">
         <v>1</v>
       </c>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="13" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="23"/>
-      <c r="B13" s="102" t="s">
+      <c r="B13" s="98" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="102"/>
+      <c r="C13" s="98"/>
       <c r="D13" s="13">
         <v>1</v>
       </c>
@@ -3955,91 +3955,91 @@
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="I14" s="94"/>
-      <c r="J14" s="95"/>
-      <c r="K14" s="95"/>
-      <c r="L14" s="95"/>
-      <c r="M14" s="95"/>
-      <c r="N14" s="95"/>
-      <c r="O14" s="95"/>
-      <c r="P14" s="95"/>
-      <c r="Q14" s="95"/>
-      <c r="R14" s="95"/>
-      <c r="S14" s="95"/>
-      <c r="T14" s="95"/>
-      <c r="U14" s="95"/>
-      <c r="V14" s="95"/>
-      <c r="W14" s="95"/>
-      <c r="X14" s="95"/>
-      <c r="Y14" s="95"/>
-      <c r="Z14" s="95"/>
-      <c r="AA14" s="95"/>
-      <c r="AB14" s="95"/>
-      <c r="AC14" s="95"/>
-      <c r="AD14" s="95"/>
-      <c r="AE14" s="95"/>
-      <c r="AF14" s="95"/>
-      <c r="AG14" s="95"/>
-      <c r="AH14" s="95"/>
-      <c r="AI14" s="95"/>
-      <c r="AJ14" s="95"/>
-      <c r="AK14" s="95"/>
-      <c r="AL14" s="95"/>
-      <c r="AM14" s="95"/>
-      <c r="AN14" s="95"/>
-      <c r="AO14" s="95"/>
-      <c r="AP14" s="95"/>
-      <c r="AQ14" s="95"/>
-      <c r="AR14" s="95"/>
-      <c r="AS14" s="95"/>
-      <c r="AT14" s="95"/>
-      <c r="AU14" s="95"/>
-      <c r="AV14" s="95"/>
-      <c r="AW14" s="95"/>
-      <c r="AX14" s="95"/>
-      <c r="AY14" s="95"/>
-      <c r="AZ14" s="95"/>
-      <c r="BA14" s="95"/>
-      <c r="BB14" s="95"/>
-      <c r="BC14" s="95"/>
-      <c r="BD14" s="95"/>
-      <c r="BE14" s="95"/>
-      <c r="BF14" s="95"/>
-      <c r="BG14" s="95"/>
-      <c r="BH14" s="95"/>
-      <c r="BI14" s="95"/>
-      <c r="BJ14" s="95"/>
-      <c r="BK14" s="95"/>
-      <c r="BL14" s="95"/>
-      <c r="BM14" s="95"/>
-      <c r="BN14" s="95"/>
-      <c r="BO14" s="95"/>
-      <c r="BP14" s="95"/>
-      <c r="BQ14" s="95"/>
-      <c r="BR14" s="95"/>
-      <c r="BS14" s="95"/>
-      <c r="BT14" s="95"/>
-      <c r="BU14" s="95"/>
-      <c r="BV14" s="95"/>
-      <c r="BW14" s="95"/>
-      <c r="BX14" s="95"/>
-      <c r="BY14" s="95"/>
-      <c r="BZ14" s="95"/>
-      <c r="CA14" s="95"/>
-      <c r="CB14" s="95"/>
-      <c r="CC14" s="95"/>
-      <c r="CD14" s="95"/>
-      <c r="CE14" s="95"/>
-      <c r="CF14" s="95"/>
-      <c r="CG14" s="95"/>
-      <c r="CH14" s="95"/>
-      <c r="CI14" s="95"/>
-      <c r="CJ14" s="95"/>
-      <c r="CK14" s="95"/>
-      <c r="CL14" s="95"/>
-      <c r="CM14" s="95"/>
-      <c r="CN14" s="95"/>
-      <c r="CO14" s="96"/>
+      <c r="I14" s="90"/>
+      <c r="J14" s="91"/>
+      <c r="K14" s="91"/>
+      <c r="L14" s="91"/>
+      <c r="M14" s="91"/>
+      <c r="N14" s="91"/>
+      <c r="O14" s="91"/>
+      <c r="P14" s="91"/>
+      <c r="Q14" s="91"/>
+      <c r="R14" s="91"/>
+      <c r="S14" s="91"/>
+      <c r="T14" s="91"/>
+      <c r="U14" s="91"/>
+      <c r="V14" s="91"/>
+      <c r="W14" s="91"/>
+      <c r="X14" s="91"/>
+      <c r="Y14" s="91"/>
+      <c r="Z14" s="91"/>
+      <c r="AA14" s="91"/>
+      <c r="AB14" s="91"/>
+      <c r="AC14" s="91"/>
+      <c r="AD14" s="91"/>
+      <c r="AE14" s="91"/>
+      <c r="AF14" s="91"/>
+      <c r="AG14" s="91"/>
+      <c r="AH14" s="91"/>
+      <c r="AI14" s="91"/>
+      <c r="AJ14" s="91"/>
+      <c r="AK14" s="91"/>
+      <c r="AL14" s="91"/>
+      <c r="AM14" s="91"/>
+      <c r="AN14" s="91"/>
+      <c r="AO14" s="91"/>
+      <c r="AP14" s="91"/>
+      <c r="AQ14" s="91"/>
+      <c r="AR14" s="91"/>
+      <c r="AS14" s="91"/>
+      <c r="AT14" s="91"/>
+      <c r="AU14" s="91"/>
+      <c r="AV14" s="91"/>
+      <c r="AW14" s="91"/>
+      <c r="AX14" s="91"/>
+      <c r="AY14" s="91"/>
+      <c r="AZ14" s="91"/>
+      <c r="BA14" s="91"/>
+      <c r="BB14" s="91"/>
+      <c r="BC14" s="91"/>
+      <c r="BD14" s="91"/>
+      <c r="BE14" s="91"/>
+      <c r="BF14" s="91"/>
+      <c r="BG14" s="91"/>
+      <c r="BH14" s="91"/>
+      <c r="BI14" s="91"/>
+      <c r="BJ14" s="91"/>
+      <c r="BK14" s="91"/>
+      <c r="BL14" s="91"/>
+      <c r="BM14" s="91"/>
+      <c r="BN14" s="91"/>
+      <c r="BO14" s="91"/>
+      <c r="BP14" s="91"/>
+      <c r="BQ14" s="91"/>
+      <c r="BR14" s="91"/>
+      <c r="BS14" s="91"/>
+      <c r="BT14" s="91"/>
+      <c r="BU14" s="91"/>
+      <c r="BV14" s="91"/>
+      <c r="BW14" s="91"/>
+      <c r="BX14" s="91"/>
+      <c r="BY14" s="91"/>
+      <c r="BZ14" s="91"/>
+      <c r="CA14" s="91"/>
+      <c r="CB14" s="91"/>
+      <c r="CC14" s="91"/>
+      <c r="CD14" s="91"/>
+      <c r="CE14" s="91"/>
+      <c r="CF14" s="91"/>
+      <c r="CG14" s="91"/>
+      <c r="CH14" s="91"/>
+      <c r="CI14" s="91"/>
+      <c r="CJ14" s="91"/>
+      <c r="CK14" s="91"/>
+      <c r="CL14" s="91"/>
+      <c r="CM14" s="91"/>
+      <c r="CN14" s="91"/>
+      <c r="CO14" s="92"/>
       <c r="CP14" s="86"/>
       <c r="CQ14"/>
       <c r="CR14"/>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="C16" s="30"/>
       <c r="D16" s="16">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="E16" s="42">
         <v>45922</v>
@@ -5002,91 +5002,91 @@
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="I22" s="92"/>
-      <c r="J22" s="93"/>
-      <c r="K22" s="93"/>
-      <c r="L22" s="93"/>
-      <c r="M22" s="93"/>
-      <c r="N22" s="93"/>
-      <c r="O22" s="93"/>
-      <c r="P22" s="93"/>
-      <c r="Q22" s="93"/>
-      <c r="R22" s="93"/>
-      <c r="S22" s="93"/>
-      <c r="T22" s="93"/>
-      <c r="U22" s="93"/>
-      <c r="V22" s="93"/>
-      <c r="W22" s="93"/>
-      <c r="X22" s="93"/>
-      <c r="Y22" s="93"/>
-      <c r="Z22" s="93"/>
-      <c r="AA22" s="93"/>
-      <c r="AB22" s="93"/>
-      <c r="AC22" s="93"/>
-      <c r="AD22" s="93"/>
-      <c r="AE22" s="93"/>
-      <c r="AF22" s="93"/>
-      <c r="AG22" s="93"/>
-      <c r="AH22" s="93"/>
-      <c r="AI22" s="93"/>
-      <c r="AJ22" s="93"/>
-      <c r="AK22" s="93"/>
-      <c r="AL22" s="93"/>
-      <c r="AM22" s="93"/>
-      <c r="AN22" s="93"/>
-      <c r="AO22" s="93"/>
-      <c r="AP22" s="93"/>
-      <c r="AQ22" s="93"/>
-      <c r="AR22" s="93"/>
-      <c r="AS22" s="93"/>
-      <c r="AT22" s="93"/>
-      <c r="AU22" s="93"/>
-      <c r="AV22" s="93"/>
-      <c r="AW22" s="93"/>
-      <c r="AX22" s="93"/>
-      <c r="AY22" s="93"/>
-      <c r="AZ22" s="93"/>
-      <c r="BA22" s="93"/>
-      <c r="BB22" s="93"/>
-      <c r="BC22" s="93"/>
-      <c r="BD22" s="93"/>
-      <c r="BE22" s="93"/>
-      <c r="BF22" s="93"/>
-      <c r="BG22" s="93"/>
-      <c r="BH22" s="93"/>
-      <c r="BI22" s="93"/>
-      <c r="BJ22" s="93"/>
-      <c r="BK22" s="93"/>
-      <c r="BL22" s="93"/>
-      <c r="BM22" s="93"/>
-      <c r="BN22" s="93"/>
-      <c r="BO22" s="93"/>
-      <c r="BP22" s="93"/>
-      <c r="BQ22" s="93"/>
-      <c r="BR22" s="93"/>
-      <c r="BS22" s="93"/>
-      <c r="BT22" s="93"/>
-      <c r="BU22" s="93"/>
-      <c r="BV22" s="93"/>
-      <c r="BW22" s="93"/>
-      <c r="BX22" s="93"/>
-      <c r="BY22" s="93"/>
-      <c r="BZ22" s="93"/>
-      <c r="CA22" s="93"/>
-      <c r="CB22" s="93"/>
-      <c r="CC22" s="93"/>
-      <c r="CD22" s="93"/>
-      <c r="CE22" s="93"/>
-      <c r="CF22" s="93"/>
-      <c r="CG22" s="93"/>
-      <c r="CH22" s="93"/>
-      <c r="CI22" s="93"/>
-      <c r="CJ22" s="93"/>
-      <c r="CK22" s="93"/>
-      <c r="CL22" s="93"/>
-      <c r="CM22" s="93"/>
-      <c r="CN22" s="93"/>
-      <c r="CO22" s="93"/>
+      <c r="I22" s="88"/>
+      <c r="J22" s="89"/>
+      <c r="K22" s="89"/>
+      <c r="L22" s="89"/>
+      <c r="M22" s="89"/>
+      <c r="N22" s="89"/>
+      <c r="O22" s="89"/>
+      <c r="P22" s="89"/>
+      <c r="Q22" s="89"/>
+      <c r="R22" s="89"/>
+      <c r="S22" s="89"/>
+      <c r="T22" s="89"/>
+      <c r="U22" s="89"/>
+      <c r="V22" s="89"/>
+      <c r="W22" s="89"/>
+      <c r="X22" s="89"/>
+      <c r="Y22" s="89"/>
+      <c r="Z22" s="89"/>
+      <c r="AA22" s="89"/>
+      <c r="AB22" s="89"/>
+      <c r="AC22" s="89"/>
+      <c r="AD22" s="89"/>
+      <c r="AE22" s="89"/>
+      <c r="AF22" s="89"/>
+      <c r="AG22" s="89"/>
+      <c r="AH22" s="89"/>
+      <c r="AI22" s="89"/>
+      <c r="AJ22" s="89"/>
+      <c r="AK22" s="89"/>
+      <c r="AL22" s="89"/>
+      <c r="AM22" s="89"/>
+      <c r="AN22" s="89"/>
+      <c r="AO22" s="89"/>
+      <c r="AP22" s="89"/>
+      <c r="AQ22" s="89"/>
+      <c r="AR22" s="89"/>
+      <c r="AS22" s="89"/>
+      <c r="AT22" s="89"/>
+      <c r="AU22" s="89"/>
+      <c r="AV22" s="89"/>
+      <c r="AW22" s="89"/>
+      <c r="AX22" s="89"/>
+      <c r="AY22" s="89"/>
+      <c r="AZ22" s="89"/>
+      <c r="BA22" s="89"/>
+      <c r="BB22" s="89"/>
+      <c r="BC22" s="89"/>
+      <c r="BD22" s="89"/>
+      <c r="BE22" s="89"/>
+      <c r="BF22" s="89"/>
+      <c r="BG22" s="89"/>
+      <c r="BH22" s="89"/>
+      <c r="BI22" s="89"/>
+      <c r="BJ22" s="89"/>
+      <c r="BK22" s="89"/>
+      <c r="BL22" s="89"/>
+      <c r="BM22" s="89"/>
+      <c r="BN22" s="89"/>
+      <c r="BO22" s="89"/>
+      <c r="BP22" s="89"/>
+      <c r="BQ22" s="89"/>
+      <c r="BR22" s="89"/>
+      <c r="BS22" s="89"/>
+      <c r="BT22" s="89"/>
+      <c r="BU22" s="89"/>
+      <c r="BV22" s="89"/>
+      <c r="BW22" s="89"/>
+      <c r="BX22" s="89"/>
+      <c r="BY22" s="89"/>
+      <c r="BZ22" s="89"/>
+      <c r="CA22" s="89"/>
+      <c r="CB22" s="89"/>
+      <c r="CC22" s="89"/>
+      <c r="CD22" s="89"/>
+      <c r="CE22" s="89"/>
+      <c r="CF22" s="89"/>
+      <c r="CG22" s="89"/>
+      <c r="CH22" s="89"/>
+      <c r="CI22" s="89"/>
+      <c r="CJ22" s="89"/>
+      <c r="CK22" s="89"/>
+      <c r="CL22" s="89"/>
+      <c r="CM22" s="89"/>
+      <c r="CN22" s="89"/>
+      <c r="CO22" s="89"/>
       <c r="CP22" s="86"/>
       <c r="CQ22"/>
       <c r="CR22"/>
@@ -6788,6 +6788,19 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="CF3:CJ3"/>
+    <mergeCell ref="CK3:CO3"/>
+    <mergeCell ref="I7:CO7"/>
+    <mergeCell ref="BB3:BF3"/>
+    <mergeCell ref="BG3:BK3"/>
+    <mergeCell ref="BL3:BP3"/>
+    <mergeCell ref="BQ3:BU3"/>
+    <mergeCell ref="BV3:BZ3"/>
+    <mergeCell ref="AC3:AG3"/>
+    <mergeCell ref="AH3:AL3"/>
+    <mergeCell ref="AM3:AQ3"/>
+    <mergeCell ref="AR3:AV3"/>
+    <mergeCell ref="AW3:BA3"/>
     <mergeCell ref="I22:CO22"/>
     <mergeCell ref="I14:CO14"/>
     <mergeCell ref="C2:D2"/>
@@ -6804,19 +6817,6 @@
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="CA3:CE3"/>
-    <mergeCell ref="CF3:CJ3"/>
-    <mergeCell ref="CK3:CO3"/>
-    <mergeCell ref="I7:CO7"/>
-    <mergeCell ref="BB3:BF3"/>
-    <mergeCell ref="BG3:BK3"/>
-    <mergeCell ref="BL3:BP3"/>
-    <mergeCell ref="BQ3:BU3"/>
-    <mergeCell ref="BV3:BZ3"/>
-    <mergeCell ref="AC3:AG3"/>
-    <mergeCell ref="AH3:AL3"/>
-    <mergeCell ref="AM3:AQ3"/>
-    <mergeCell ref="AR3:AV3"/>
-    <mergeCell ref="AW3:BA3"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D35">
     <cfRule type="dataBar" priority="17">
@@ -7191,6 +7191,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
@@ -7208,15 +7217,6 @@
     <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7241,6 +7241,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -7250,12 +7258,4 @@
     <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>